--- a/development/MS/spec/MSBB/Panel/MSBBPA0030_SloDlv_H.xlsx
+++ b/development/MS/spec/MSBB/Panel/MSBBPA0030_SloDlv_H.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\mcframeDEV\development\MS\spec\MSBB\Panel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BA8CC10-5147-4944-97C9-91D47273570A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E46DFD2-4993-4FFE-84D7-B28A762EA8BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="821" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -511,10 +511,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>MA.MAUAP0010.Bp</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>MAC_BP_IS_SRCH_TYP.DLV</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -907,6 +903,9 @@
   </si>
   <si>
     <t>SloDlv</t>
+  </si>
+  <si>
+    <t>MS.MSUAP0030.SloDlv</t>
   </si>
 </sst>
 </file>
@@ -2360,26 +2359,107 @@
     <xf numFmtId="0" fontId="30" fillId="18" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="31" fillId="19" borderId="28" xfId="137" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="29" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="19" borderId="30" xfId="138" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="31" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="19" borderId="1" xfId="138" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="19" borderId="31" xfId="138" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="19" borderId="30" xfId="136" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="32" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="33" xfId="138" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="2" xfId="136" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="19" xfId="136" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="34" xfId="138" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="26" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="27" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="26" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="27" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="18" xfId="138" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="2" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="19" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="2" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="19" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="25" xfId="138" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="26" xfId="136" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="27" xfId="136" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="18" xfId="138" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="2" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="35" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="18" xfId="138" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="19" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="34" xfId="138" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="2" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="19" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="36" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="37" xfId="138" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="38" xfId="136" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="39" xfId="136" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="40" xfId="138" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2405,12 +2485,6 @@
     <xf numFmtId="0" fontId="33" fillId="19" borderId="42" xfId="138" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="31" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="18" xfId="138" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2428,81 +2502,6 @@
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="35" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="34" xfId="138" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="26" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="36" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="37" xfId="138" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="38" xfId="136" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="39" xfId="136" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="33" xfId="138" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="2" xfId="136" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="19" xfId="136" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="34" xfId="138" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="26" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="27" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="27" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="25" xfId="138" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="26" xfId="136" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="27" xfId="136" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="19" borderId="28" xfId="137" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="29" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="19" borderId="30" xfId="138" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="19" borderId="1" xfId="138" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="19" borderId="31" xfId="138" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="19" borderId="30" xfId="136" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="32" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="143">
@@ -3111,20 +3110,20 @@
       <c r="B2" s="37"/>
       <c r="C2" s="37"/>
       <c r="D2" s="38" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E2" s="20" t="s">
         <v>78</v>
       </c>
       <c r="F2" s="32" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G2" s="51" t="s">
         <v>83</v>
       </c>
       <c r="H2" s="53"/>
       <c r="I2" s="56" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J2" s="57"/>
       <c r="K2" s="54" t="s">
@@ -3136,13 +3135,13 @@
       <c r="O2" s="51"/>
       <c r="P2" s="39"/>
       <c r="Q2" s="32" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="R2" s="20" t="s">
         <v>85</v>
       </c>
       <c r="S2" s="32" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="T2" s="40"/>
       <c r="U2" s="41"/>
@@ -3175,14 +3174,14 @@
         <v>79</v>
       </c>
       <c r="F3" s="32" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G3" s="51" t="s">
         <v>86</v>
       </c>
       <c r="H3" s="53"/>
       <c r="I3" s="56" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J3" s="57"/>
       <c r="K3" s="54" t="s">
@@ -3198,7 +3197,7 @@
         <v>88</v>
       </c>
       <c r="S3" s="32" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="T3" s="32"/>
       <c r="AM3" s="23"/>
@@ -3219,7 +3218,7 @@
       </c>
       <c r="H4" s="53"/>
       <c r="I4" s="56" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="J4" s="57"/>
       <c r="K4" s="54" t="s">
@@ -3231,7 +3230,7 @@
       <c r="O4" s="51"/>
       <c r="P4" s="39"/>
       <c r="Q4" s="32" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="R4" s="20"/>
       <c r="S4" s="20"/>
@@ -3394,52 +3393,52 @@
       <c r="B8" s="32"/>
       <c r="C8" s="32"/>
       <c r="D8" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="F8" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="E8" s="20" t="s">
-        <v>116</v>
-      </c>
-      <c r="F8" s="20" t="s">
+      <c r="G8" s="17" t="s">
         <v>141</v>
-      </c>
-      <c r="G8" s="17" t="s">
-        <v>142</v>
       </c>
       <c r="H8" s="20"/>
       <c r="I8" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="J8" s="20" t="s">
         <v>143</v>
       </c>
-      <c r="J8" s="20" t="s">
+      <c r="K8" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="K8" s="20" t="s">
+      <c r="L8" s="20" t="s">
         <v>145</v>
       </c>
-      <c r="L8" s="20" t="s">
+      <c r="M8" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="N8" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="O8" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="P8" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q8" s="51" t="s">
         <v>146</v>
-      </c>
-      <c r="M8" s="20" t="s">
-        <v>117</v>
-      </c>
-      <c r="N8" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="O8" s="20" t="s">
-        <v>119</v>
-      </c>
-      <c r="P8" s="20" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q8" s="51" t="s">
-        <v>147</v>
       </c>
       <c r="R8" s="52"/>
       <c r="S8" s="53"/>
       <c r="T8" s="40" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="U8" s="32" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V8" s="32" t="s">
         <v>75</v>
@@ -3448,38 +3447,38 @@
         <v>74</v>
       </c>
       <c r="X8" s="32" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Y8" s="5"/>
       <c r="Z8" s="32" t="s">
         <v>8</v>
       </c>
       <c r="AA8" s="32" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB8" s="32" t="s">
         <v>122</v>
-      </c>
-      <c r="AB8" s="32" t="s">
-        <v>123</v>
       </c>
       <c r="AC8" s="6"/>
       <c r="AD8" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AE8" s="32"/>
       <c r="AF8" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG8" s="32"/>
       <c r="AH8" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AI8" s="32"/>
       <c r="AJ8" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AK8" s="32"/>
       <c r="AL8" s="7"/>
       <c r="AM8" s="20" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="9" spans="1:39" s="1" customFormat="1" ht="60" customHeight="1">
@@ -3489,52 +3488,52 @@
       <c r="B9" s="32"/>
       <c r="C9" s="32"/>
       <c r="D9" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="E9" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="F9" s="48" t="s">
         <v>150</v>
       </c>
-      <c r="F9" s="48" t="s">
+      <c r="G9" s="48" t="s">
         <v>151</v>
       </c>
-      <c r="G9" s="48" t="s">
+      <c r="H9" s="48" t="s">
         <v>152</v>
       </c>
-      <c r="H9" s="48" t="s">
+      <c r="I9" s="20" t="s">
         <v>153</v>
       </c>
-      <c r="I9" s="20" t="s">
+      <c r="J9" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="K9" s="48" t="s">
         <v>154</v>
       </c>
-      <c r="J9" s="48" t="s">
-        <v>125</v>
-      </c>
-      <c r="K9" s="48" t="s">
+      <c r="L9" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="L9" s="20" t="s">
+      <c r="M9" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="M9" s="20" t="s">
+      <c r="N9" s="20" t="s">
         <v>157</v>
-      </c>
-      <c r="N9" s="20" t="s">
-        <v>158</v>
       </c>
       <c r="O9" s="20" t="s">
         <v>81</v>
       </c>
       <c r="P9" s="20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q9" s="20" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R9" s="20" t="s">
         <v>82</v>
       </c>
       <c r="S9" s="20" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="T9" s="49"/>
       <c r="U9" s="4"/>
@@ -3547,30 +3546,30 @@
       <c r="AB9" s="8"/>
       <c r="AC9" s="9"/>
       <c r="AD9" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="AE9" s="32" t="s">
         <v>128</v>
       </c>
-      <c r="AE9" s="32" t="s">
-        <v>129</v>
-      </c>
       <c r="AF9" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="AG9" s="32" t="s">
         <v>128</v>
       </c>
-      <c r="AG9" s="32" t="s">
-        <v>129</v>
-      </c>
       <c r="AH9" s="20" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AI9" s="32"/>
       <c r="AJ9" s="20" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AK9" s="32"/>
       <c r="AL9" s="39" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AM9" s="20" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="10" spans="1:39" s="1" customFormat="1" ht="54">
@@ -3604,28 +3603,28 @@
       <c r="AB10" s="4"/>
       <c r="AC10" s="31"/>
       <c r="AD10" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="AE10" s="20" t="s">
         <v>180</v>
       </c>
-      <c r="AE10" s="20" t="s">
-        <v>181</v>
-      </c>
       <c r="AF10" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="AG10" s="20" t="s">
         <v>180</v>
       </c>
-      <c r="AG10" s="20" t="s">
-        <v>181</v>
-      </c>
       <c r="AH10" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="AI10" s="20" t="s">
         <v>180</v>
       </c>
-      <c r="AI10" s="20" t="s">
-        <v>181</v>
-      </c>
       <c r="AJ10" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="AK10" s="20" t="s">
         <v>180</v>
-      </c>
-      <c r="AK10" s="20" t="s">
-        <v>181</v>
       </c>
       <c r="AL10" s="14"/>
       <c r="AM10" s="10"/>
@@ -3639,7 +3638,7 @@
       </c>
       <c r="C11" s="15"/>
       <c r="D11" s="15" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E11" s="16"/>
       <c r="F11" s="15"/>
@@ -3691,7 +3690,7 @@
         <v>54</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F12" s="32" t="s">
         <v>52</v>
@@ -3705,7 +3704,7 @@
       </c>
       <c r="J12" s="32"/>
       <c r="K12" s="32" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L12" s="32"/>
       <c r="M12" s="32"/>
@@ -3713,7 +3712,7 @@
       <c r="O12" s="32"/>
       <c r="P12" s="32"/>
       <c r="Q12" s="32" t="s">
-        <v>92</v>
+        <v>190</v>
       </c>
       <c r="R12" s="32"/>
       <c r="S12" s="32" t="s">
@@ -3722,7 +3721,7 @@
       <c r="T12" s="32"/>
       <c r="U12" s="32"/>
       <c r="V12" s="32" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W12" s="32" t="s">
         <v>77</v>
@@ -3757,7 +3756,7 @@
         <v>55</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F13" s="32" t="s">
         <v>53</v>
@@ -3813,7 +3812,7 @@
         <v>38</v>
       </c>
       <c r="E14" s="19" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F14" s="32" t="s">
         <v>25</v>
@@ -3871,7 +3870,7 @@
         <v>39</v>
       </c>
       <c r="E15" s="19" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F15" s="32" t="s">
         <v>28</v>
@@ -3929,7 +3928,7 @@
         <v>56</v>
       </c>
       <c r="E16" s="19" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F16" s="32" t="s">
         <v>59</v>
@@ -3941,11 +3940,11 @@
       <c r="I16" s="32"/>
       <c r="J16" s="32"/>
       <c r="K16" s="32" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L16" s="32"/>
       <c r="M16" s="32" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N16" s="32"/>
       <c r="O16" s="32"/>
@@ -3984,10 +3983,10 @@
       <c r="B17" s="32"/>
       <c r="C17" s="32"/>
       <c r="D17" s="32" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F17" s="32" t="s">
         <v>70</v>
@@ -3997,11 +3996,11 @@
       </c>
       <c r="H17" s="32"/>
       <c r="I17" s="32" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J17" s="32"/>
       <c r="K17" s="32" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L17" s="32"/>
       <c r="M17" s="32"/>
@@ -4009,22 +4008,22 @@
       <c r="O17" s="32"/>
       <c r="P17" s="32"/>
       <c r="Q17" s="32" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="R17" s="32"/>
       <c r="S17" s="32" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="T17" s="32"/>
       <c r="U17" s="32"/>
       <c r="V17" s="50" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="W17" s="32" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="X17" s="32" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z17" s="32" t="s">
         <v>11</v>
@@ -4055,7 +4054,7 @@
         <v>72</v>
       </c>
       <c r="E18" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F18" s="32" t="s">
         <v>73</v>
@@ -4063,7 +4062,7 @@
       <c r="G18" s="32"/>
       <c r="H18" s="32"/>
       <c r="I18" s="32" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J18" s="32"/>
       <c r="K18" s="32" t="s">
@@ -4082,7 +4081,7 @@
       <c r="V18" s="32"/>
       <c r="W18" s="32"/>
       <c r="X18" s="32" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Z18" s="32" t="s">
         <v>51</v>
@@ -4113,7 +4112,7 @@
         <v>45</v>
       </c>
       <c r="E19" s="19" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F19" s="32" t="s">
         <v>60</v>
@@ -4123,7 +4122,7 @@
       </c>
       <c r="H19" s="32"/>
       <c r="I19" s="32" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J19" s="32"/>
       <c r="K19" s="32" t="s">
@@ -4171,7 +4170,7 @@
         <v>46</v>
       </c>
       <c r="E20" s="19" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F20" s="32" t="s">
         <v>61</v>
@@ -4179,7 +4178,7 @@
       <c r="G20" s="32"/>
       <c r="H20" s="32"/>
       <c r="I20" s="32" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J20" s="32"/>
       <c r="K20" s="32" t="s">
@@ -4227,7 +4226,7 @@
         <v>40</v>
       </c>
       <c r="E21" s="19" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F21" s="32" t="s">
         <v>63</v>
@@ -4237,7 +4236,7 @@
       </c>
       <c r="H21" s="32"/>
       <c r="I21" s="32" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J21" s="32"/>
       <c r="K21" s="32" t="s">
@@ -4285,7 +4284,7 @@
         <v>41</v>
       </c>
       <c r="E22" s="19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F22" s="32" t="s">
         <v>64</v>
@@ -4295,7 +4294,7 @@
       </c>
       <c r="H22" s="32"/>
       <c r="I22" s="32" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J22" s="32"/>
       <c r="K22" s="32" t="s">
@@ -4314,7 +4313,7 @@
       <c r="V22" s="32"/>
       <c r="W22" s="32"/>
       <c r="X22" s="32" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="Z22" s="32" t="s">
         <v>11</v>
@@ -4345,7 +4344,7 @@
         <v>42</v>
       </c>
       <c r="E23" s="19" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F23" s="32" t="s">
         <v>65</v>
@@ -4355,7 +4354,7 @@
       </c>
       <c r="H23" s="32"/>
       <c r="I23" s="32" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J23" s="32"/>
       <c r="K23" s="32" t="s">
@@ -4374,7 +4373,7 @@
       <c r="V23" s="32"/>
       <c r="W23" s="32"/>
       <c r="X23" s="32" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z23" s="32" t="s">
         <v>11</v>
@@ -4405,7 +4404,7 @@
         <v>43</v>
       </c>
       <c r="E24" s="19" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F24" s="32" t="s">
         <v>66</v>
@@ -4415,7 +4414,7 @@
       </c>
       <c r="H24" s="32"/>
       <c r="I24" s="32" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J24" s="32"/>
       <c r="K24" s="32" t="s">
@@ -4434,7 +4433,7 @@
       <c r="V24" s="32"/>
       <c r="W24" s="32"/>
       <c r="X24" s="32" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Z24" s="32" t="s">
         <v>11</v>
@@ -4465,7 +4464,7 @@
         <v>44</v>
       </c>
       <c r="E25" s="19" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F25" s="32" t="s">
         <v>67</v>
@@ -4475,7 +4474,7 @@
       </c>
       <c r="H25" s="32"/>
       <c r="I25" s="32" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J25" s="32"/>
       <c r="K25" s="32" t="s">
@@ -4494,7 +4493,7 @@
       <c r="V25" s="32"/>
       <c r="W25" s="32"/>
       <c r="X25" s="32" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Z25" s="32" t="s">
         <v>11</v>
@@ -4525,7 +4524,7 @@
         <v>47</v>
       </c>
       <c r="E26" s="19" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F26" s="32" t="s">
         <v>68</v>
@@ -4535,7 +4534,7 @@
       </c>
       <c r="H26" s="32"/>
       <c r="I26" s="32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J26" s="32"/>
       <c r="K26" s="32" t="s">
@@ -4583,7 +4582,7 @@
         <v>48</v>
       </c>
       <c r="E27" s="19" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F27" s="32" t="s">
         <v>69</v>
@@ -4593,7 +4592,7 @@
       </c>
       <c r="H27" s="32"/>
       <c r="I27" s="32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J27" s="32"/>
       <c r="K27" s="32" t="s">
@@ -4641,7 +4640,7 @@
         <v>49</v>
       </c>
       <c r="E28" s="19" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F28" s="32" t="s">
         <v>35</v>
@@ -4651,7 +4650,7 @@
       </c>
       <c r="H28" s="32"/>
       <c r="I28" s="32" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J28" s="32"/>
       <c r="K28" s="32" t="s">
@@ -4699,7 +4698,7 @@
         <v>50</v>
       </c>
       <c r="E29" s="19" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F29" s="32" t="s">
         <v>36</v>
@@ -4709,7 +4708,7 @@
       </c>
       <c r="H29" s="32"/>
       <c r="I29" s="32" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J29" s="32"/>
       <c r="K29" s="32" t="s">
@@ -4752,7 +4751,7 @@
       <c r="B30" s="22"/>
       <c r="C30" s="22"/>
       <c r="D30" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E30" s="8"/>
       <c r="F30" s="8"/>
@@ -4901,65 +4900,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:57" s="26" customFormat="1" ht="38.25" customHeight="1" thickBot="1">
-      <c r="A1" s="98" t="s">
+      <c r="A1" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
-      <c r="V1" s="99"/>
-      <c r="W1" s="99"/>
-      <c r="X1" s="99"/>
-      <c r="Y1" s="99"/>
-      <c r="Z1" s="99"/>
-      <c r="AA1" s="99"/>
-      <c r="AB1" s="99"/>
-      <c r="AC1" s="99"/>
-      <c r="AD1" s="99"/>
-      <c r="AE1" s="99"/>
-      <c r="AF1" s="99"/>
-      <c r="AG1" s="99"/>
-      <c r="AH1" s="99"/>
-      <c r="AI1" s="99"/>
-      <c r="AJ1" s="99"/>
-      <c r="AK1" s="99"/>
-      <c r="AL1" s="99"/>
-      <c r="AM1" s="99"/>
-      <c r="AN1" s="99"/>
-      <c r="AO1" s="99"/>
-      <c r="AP1" s="99"/>
-      <c r="AQ1" s="99"/>
-      <c r="AR1" s="99"/>
-      <c r="AS1" s="99"/>
-      <c r="AT1" s="99"/>
-      <c r="AU1" s="99"/>
-      <c r="AV1" s="99"/>
-      <c r="AW1" s="99"/>
-      <c r="AX1" s="99"/>
-      <c r="AY1" s="99"/>
-      <c r="AZ1" s="99"/>
-      <c r="BA1" s="99"/>
-      <c r="BB1" s="99"/>
-      <c r="BC1" s="99"/>
-      <c r="BD1" s="99"/>
-      <c r="BE1" s="100"/>
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="60"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="60"/>
+      <c r="J1" s="60"/>
+      <c r="K1" s="60"/>
+      <c r="L1" s="60"/>
+      <c r="M1" s="60"/>
+      <c r="N1" s="60"/>
+      <c r="O1" s="60"/>
+      <c r="P1" s="60"/>
+      <c r="Q1" s="60"/>
+      <c r="R1" s="60"/>
+      <c r="S1" s="60"/>
+      <c r="T1" s="60"/>
+      <c r="U1" s="60"/>
+      <c r="V1" s="60"/>
+      <c r="W1" s="60"/>
+      <c r="X1" s="60"/>
+      <c r="Y1" s="60"/>
+      <c r="Z1" s="60"/>
+      <c r="AA1" s="60"/>
+      <c r="AB1" s="60"/>
+      <c r="AC1" s="60"/>
+      <c r="AD1" s="60"/>
+      <c r="AE1" s="60"/>
+      <c r="AF1" s="60"/>
+      <c r="AG1" s="60"/>
+      <c r="AH1" s="60"/>
+      <c r="AI1" s="60"/>
+      <c r="AJ1" s="60"/>
+      <c r="AK1" s="60"/>
+      <c r="AL1" s="60"/>
+      <c r="AM1" s="60"/>
+      <c r="AN1" s="60"/>
+      <c r="AO1" s="60"/>
+      <c r="AP1" s="60"/>
+      <c r="AQ1" s="60"/>
+      <c r="AR1" s="60"/>
+      <c r="AS1" s="60"/>
+      <c r="AT1" s="60"/>
+      <c r="AU1" s="60"/>
+      <c r="AV1" s="60"/>
+      <c r="AW1" s="60"/>
+      <c r="AX1" s="60"/>
+      <c r="AY1" s="60"/>
+      <c r="AZ1" s="60"/>
+      <c r="BA1" s="60"/>
+      <c r="BB1" s="60"/>
+      <c r="BC1" s="60"/>
+      <c r="BD1" s="60"/>
+      <c r="BE1" s="61"/>
     </row>
     <row r="2" spans="1:57" s="26" customFormat="1" ht="12" customHeight="1" thickBot="1">
       <c r="A2" s="27"/>
@@ -5008,1972 +5007,2081 @@
       <c r="AR2" s="28"/>
     </row>
     <row r="3" spans="1:57" ht="15" customHeight="1" thickBot="1">
-      <c r="A3" s="73" t="s">
+      <c r="A3" s="100" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="74"/>
-      <c r="C3" s="74"/>
-      <c r="D3" s="74"/>
-      <c r="E3" s="74"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="101" t="s">
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="I3" s="74"/>
-      <c r="J3" s="74"/>
-      <c r="K3" s="74"/>
-      <c r="L3" s="74"/>
-      <c r="M3" s="74"/>
-      <c r="N3" s="75"/>
-      <c r="O3" s="101" t="s">
+      <c r="I3" s="63"/>
+      <c r="J3" s="63"/>
+      <c r="K3" s="63"/>
+      <c r="L3" s="63"/>
+      <c r="M3" s="63"/>
+      <c r="N3" s="64"/>
+      <c r="O3" s="62" t="s">
         <v>4</v>
       </c>
-      <c r="P3" s="102"/>
-      <c r="Q3" s="102"/>
-      <c r="R3" s="102"/>
-      <c r="S3" s="102"/>
-      <c r="T3" s="102"/>
-      <c r="U3" s="102"/>
-      <c r="V3" s="102"/>
-      <c r="W3" s="102"/>
-      <c r="X3" s="102"/>
-      <c r="Y3" s="102"/>
-      <c r="Z3" s="102"/>
-      <c r="AA3" s="102"/>
-      <c r="AB3" s="102"/>
-      <c r="AC3" s="102"/>
-      <c r="AD3" s="102"/>
-      <c r="AE3" s="102"/>
-      <c r="AF3" s="102"/>
-      <c r="AG3" s="102"/>
-      <c r="AH3" s="102"/>
-      <c r="AI3" s="102"/>
-      <c r="AJ3" s="102"/>
-      <c r="AK3" s="102"/>
-      <c r="AL3" s="102"/>
-      <c r="AM3" s="102"/>
-      <c r="AN3" s="102"/>
-      <c r="AO3" s="102"/>
-      <c r="AP3" s="103"/>
-      <c r="AQ3" s="104" t="s">
+      <c r="P3" s="65"/>
+      <c r="Q3" s="65"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="65"/>
+      <c r="T3" s="65"/>
+      <c r="U3" s="65"/>
+      <c r="V3" s="65"/>
+      <c r="W3" s="65"/>
+      <c r="X3" s="65"/>
+      <c r="Y3" s="65"/>
+      <c r="Z3" s="65"/>
+      <c r="AA3" s="65"/>
+      <c r="AB3" s="65"/>
+      <c r="AC3" s="65"/>
+      <c r="AD3" s="65"/>
+      <c r="AE3" s="65"/>
+      <c r="AF3" s="65"/>
+      <c r="AG3" s="65"/>
+      <c r="AH3" s="65"/>
+      <c r="AI3" s="65"/>
+      <c r="AJ3" s="65"/>
+      <c r="AK3" s="65"/>
+      <c r="AL3" s="65"/>
+      <c r="AM3" s="65"/>
+      <c r="AN3" s="65"/>
+      <c r="AO3" s="65"/>
+      <c r="AP3" s="66"/>
+      <c r="AQ3" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="AR3" s="105"/>
-      <c r="AS3" s="105"/>
-      <c r="AT3" s="105"/>
-      <c r="AU3" s="105"/>
-      <c r="AV3" s="105"/>
-      <c r="AW3" s="105"/>
-      <c r="AX3" s="105"/>
-      <c r="AY3" s="105"/>
-      <c r="AZ3" s="105"/>
-      <c r="BA3" s="105"/>
-      <c r="BB3" s="105"/>
-      <c r="BC3" s="105"/>
-      <c r="BD3" s="105"/>
-      <c r="BE3" s="106"/>
+      <c r="AR3" s="68"/>
+      <c r="AS3" s="68"/>
+      <c r="AT3" s="68"/>
+      <c r="AU3" s="68"/>
+      <c r="AV3" s="68"/>
+      <c r="AW3" s="68"/>
+      <c r="AX3" s="68"/>
+      <c r="AY3" s="68"/>
+      <c r="AZ3" s="68"/>
+      <c r="BA3" s="68"/>
+      <c r="BB3" s="68"/>
+      <c r="BC3" s="68"/>
+      <c r="BD3" s="68"/>
+      <c r="BE3" s="69"/>
     </row>
     <row r="4" spans="1:57" ht="15" customHeight="1">
-      <c r="A4" s="85">
+      <c r="A4" s="90">
         <v>1</v>
       </c>
-      <c r="B4" s="86"/>
-      <c r="C4" s="86"/>
-      <c r="D4" s="86"/>
-      <c r="E4" s="86"/>
-      <c r="F4" s="86"/>
-      <c r="G4" s="87"/>
-      <c r="H4" s="66"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="67"/>
-      <c r="K4" s="67"/>
-      <c r="L4" s="67"/>
-      <c r="M4" s="67"/>
-      <c r="N4" s="68"/>
-      <c r="O4" s="66" t="s">
+      <c r="B4" s="91"/>
+      <c r="C4" s="91"/>
+      <c r="D4" s="91"/>
+      <c r="E4" s="91"/>
+      <c r="F4" s="91"/>
+      <c r="G4" s="92"/>
+      <c r="H4" s="93"/>
+      <c r="I4" s="94"/>
+      <c r="J4" s="94"/>
+      <c r="K4" s="94"/>
+      <c r="L4" s="94"/>
+      <c r="M4" s="94"/>
+      <c r="N4" s="95"/>
+      <c r="O4" s="93" t="s">
         <v>6</v>
       </c>
-      <c r="P4" s="69"/>
-      <c r="Q4" s="69"/>
-      <c r="R4" s="69"/>
-      <c r="S4" s="69"/>
-      <c r="T4" s="69"/>
-      <c r="U4" s="69"/>
-      <c r="V4" s="69"/>
-      <c r="W4" s="69"/>
-      <c r="X4" s="69"/>
-      <c r="Y4" s="69"/>
-      <c r="Z4" s="69"/>
-      <c r="AA4" s="69"/>
-      <c r="AB4" s="69"/>
-      <c r="AC4" s="69"/>
-      <c r="AD4" s="69"/>
-      <c r="AE4" s="69"/>
-      <c r="AF4" s="69"/>
-      <c r="AG4" s="69"/>
-      <c r="AH4" s="69"/>
-      <c r="AI4" s="69"/>
-      <c r="AJ4" s="69"/>
-      <c r="AK4" s="69"/>
-      <c r="AL4" s="69"/>
-      <c r="AM4" s="69"/>
-      <c r="AN4" s="69"/>
-      <c r="AO4" s="69"/>
-      <c r="AP4" s="70"/>
-      <c r="AQ4" s="71"/>
-      <c r="AR4" s="69"/>
-      <c r="AS4" s="69"/>
-      <c r="AT4" s="69"/>
-      <c r="AU4" s="69"/>
-      <c r="AV4" s="69"/>
-      <c r="AW4" s="69"/>
-      <c r="AX4" s="69"/>
-      <c r="AY4" s="69"/>
-      <c r="AZ4" s="69"/>
-      <c r="BA4" s="69"/>
-      <c r="BB4" s="69"/>
-      <c r="BC4" s="69"/>
-      <c r="BD4" s="69"/>
-      <c r="BE4" s="72"/>
+      <c r="P4" s="96"/>
+      <c r="Q4" s="96"/>
+      <c r="R4" s="96"/>
+      <c r="S4" s="96"/>
+      <c r="T4" s="96"/>
+      <c r="U4" s="96"/>
+      <c r="V4" s="96"/>
+      <c r="W4" s="96"/>
+      <c r="X4" s="96"/>
+      <c r="Y4" s="96"/>
+      <c r="Z4" s="96"/>
+      <c r="AA4" s="96"/>
+      <c r="AB4" s="96"/>
+      <c r="AC4" s="96"/>
+      <c r="AD4" s="96"/>
+      <c r="AE4" s="96"/>
+      <c r="AF4" s="96"/>
+      <c r="AG4" s="96"/>
+      <c r="AH4" s="96"/>
+      <c r="AI4" s="96"/>
+      <c r="AJ4" s="96"/>
+      <c r="AK4" s="96"/>
+      <c r="AL4" s="96"/>
+      <c r="AM4" s="96"/>
+      <c r="AN4" s="96"/>
+      <c r="AO4" s="96"/>
+      <c r="AP4" s="97"/>
+      <c r="AQ4" s="98"/>
+      <c r="AR4" s="96"/>
+      <c r="AS4" s="96"/>
+      <c r="AT4" s="96"/>
+      <c r="AU4" s="96"/>
+      <c r="AV4" s="96"/>
+      <c r="AW4" s="96"/>
+      <c r="AX4" s="96"/>
+      <c r="AY4" s="96"/>
+      <c r="AZ4" s="96"/>
+      <c r="BA4" s="96"/>
+      <c r="BB4" s="96"/>
+      <c r="BC4" s="96"/>
+      <c r="BD4" s="96"/>
+      <c r="BE4" s="99"/>
     </row>
     <row r="5" spans="1:57" ht="15" customHeight="1">
-      <c r="A5" s="88">
+      <c r="A5" s="70">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B5" s="89"/>
-      <c r="C5" s="89"/>
-      <c r="D5" s="89"/>
-      <c r="E5" s="89"/>
-      <c r="F5" s="89"/>
-      <c r="G5" s="90"/>
-      <c r="H5" s="62"/>
-      <c r="I5" s="64"/>
-      <c r="J5" s="64"/>
-      <c r="K5" s="64"/>
-      <c r="L5" s="64"/>
-      <c r="M5" s="64"/>
-      <c r="N5" s="65"/>
-      <c r="O5" s="76" t="s">
+      <c r="B5" s="71"/>
+      <c r="C5" s="71"/>
+      <c r="D5" s="71"/>
+      <c r="E5" s="71"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="72"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
+      <c r="K5" s="79"/>
+      <c r="L5" s="79"/>
+      <c r="M5" s="79"/>
+      <c r="N5" s="80"/>
+      <c r="O5" s="101" t="s">
+        <v>181</v>
+      </c>
+      <c r="P5" s="102"/>
+      <c r="Q5" s="102"/>
+      <c r="R5" s="102"/>
+      <c r="S5" s="102"/>
+      <c r="T5" s="102"/>
+      <c r="U5" s="102"/>
+      <c r="V5" s="102"/>
+      <c r="W5" s="102"/>
+      <c r="X5" s="102"/>
+      <c r="Y5" s="102"/>
+      <c r="Z5" s="102"/>
+      <c r="AA5" s="102"/>
+      <c r="AB5" s="102"/>
+      <c r="AC5" s="102"/>
+      <c r="AD5" s="102"/>
+      <c r="AE5" s="102"/>
+      <c r="AF5" s="102"/>
+      <c r="AG5" s="102"/>
+      <c r="AH5" s="102"/>
+      <c r="AI5" s="102"/>
+      <c r="AJ5" s="102"/>
+      <c r="AK5" s="102"/>
+      <c r="AL5" s="102"/>
+      <c r="AM5" s="102"/>
+      <c r="AN5" s="102"/>
+      <c r="AO5" s="102"/>
+      <c r="AP5" s="103"/>
+      <c r="AQ5" s="104" t="s">
         <v>182</v>
       </c>
-      <c r="P5" s="77"/>
-      <c r="Q5" s="77"/>
-      <c r="R5" s="77"/>
-      <c r="S5" s="77"/>
-      <c r="T5" s="77"/>
-      <c r="U5" s="77"/>
-      <c r="V5" s="77"/>
-      <c r="W5" s="77"/>
-      <c r="X5" s="77"/>
-      <c r="Y5" s="77"/>
-      <c r="Z5" s="77"/>
-      <c r="AA5" s="77"/>
-      <c r="AB5" s="77"/>
-      <c r="AC5" s="77"/>
-      <c r="AD5" s="77"/>
-      <c r="AE5" s="77"/>
-      <c r="AF5" s="77"/>
-      <c r="AG5" s="77"/>
-      <c r="AH5" s="77"/>
-      <c r="AI5" s="77"/>
-      <c r="AJ5" s="77"/>
-      <c r="AK5" s="77"/>
-      <c r="AL5" s="77"/>
-      <c r="AM5" s="77"/>
-      <c r="AN5" s="77"/>
-      <c r="AO5" s="77"/>
-      <c r="AP5" s="78"/>
-      <c r="AQ5" s="79" t="s">
-        <v>183</v>
-      </c>
-      <c r="AR5" s="80"/>
-      <c r="AS5" s="80"/>
-      <c r="AT5" s="80"/>
-      <c r="AU5" s="80"/>
-      <c r="AV5" s="80"/>
-      <c r="AW5" s="80"/>
-      <c r="AX5" s="80"/>
-      <c r="AY5" s="80"/>
-      <c r="AZ5" s="80"/>
-      <c r="BA5" s="80"/>
-      <c r="BB5" s="80"/>
-      <c r="BC5" s="80"/>
-      <c r="BD5" s="80"/>
-      <c r="BE5" s="81"/>
+      <c r="AR5" s="105"/>
+      <c r="AS5" s="105"/>
+      <c r="AT5" s="105"/>
+      <c r="AU5" s="105"/>
+      <c r="AV5" s="105"/>
+      <c r="AW5" s="105"/>
+      <c r="AX5" s="105"/>
+      <c r="AY5" s="105"/>
+      <c r="AZ5" s="105"/>
+      <c r="BA5" s="105"/>
+      <c r="BB5" s="105"/>
+      <c r="BC5" s="105"/>
+      <c r="BD5" s="105"/>
+      <c r="BE5" s="106"/>
     </row>
     <row r="6" spans="1:57" ht="15" customHeight="1">
-      <c r="A6" s="88"/>
-      <c r="B6" s="89"/>
-      <c r="C6" s="89"/>
-      <c r="D6" s="89"/>
-      <c r="E6" s="89"/>
-      <c r="F6" s="89"/>
-      <c r="G6" s="90"/>
-      <c r="H6" s="62"/>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="64"/>
-      <c r="L6" s="64"/>
-      <c r="M6" s="64"/>
-      <c r="N6" s="65"/>
-      <c r="O6" s="62"/>
-      <c r="P6" s="60"/>
-      <c r="Q6" s="60"/>
-      <c r="R6" s="60"/>
-      <c r="S6" s="60"/>
-      <c r="T6" s="60"/>
-      <c r="U6" s="60"/>
-      <c r="V6" s="60"/>
-      <c r="W6" s="60"/>
-      <c r="X6" s="60"/>
-      <c r="Y6" s="60"/>
-      <c r="Z6" s="60"/>
-      <c r="AA6" s="60"/>
-      <c r="AB6" s="60"/>
-      <c r="AC6" s="60"/>
-      <c r="AD6" s="60"/>
-      <c r="AE6" s="60"/>
-      <c r="AF6" s="60"/>
-      <c r="AG6" s="60"/>
-      <c r="AH6" s="60"/>
-      <c r="AI6" s="60"/>
-      <c r="AJ6" s="60"/>
-      <c r="AK6" s="60"/>
-      <c r="AL6" s="60"/>
-      <c r="AM6" s="60"/>
-      <c r="AN6" s="60"/>
-      <c r="AO6" s="60"/>
-      <c r="AP6" s="63"/>
-      <c r="AQ6" s="59"/>
-      <c r="AR6" s="60"/>
-      <c r="AS6" s="60"/>
-      <c r="AT6" s="60"/>
-      <c r="AU6" s="60"/>
-      <c r="AV6" s="60"/>
-      <c r="AW6" s="60"/>
-      <c r="AX6" s="60"/>
-      <c r="AY6" s="60"/>
-      <c r="AZ6" s="60"/>
-      <c r="BA6" s="60"/>
-      <c r="BB6" s="60"/>
-      <c r="BC6" s="60"/>
-      <c r="BD6" s="60"/>
-      <c r="BE6" s="61"/>
+      <c r="A6" s="70"/>
+      <c r="B6" s="71"/>
+      <c r="C6" s="71"/>
+      <c r="D6" s="71"/>
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="72"/>
+      <c r="H6" s="78"/>
+      <c r="I6" s="79"/>
+      <c r="J6" s="79"/>
+      <c r="K6" s="79"/>
+      <c r="L6" s="79"/>
+      <c r="M6" s="79"/>
+      <c r="N6" s="80"/>
+      <c r="O6" s="78"/>
+      <c r="P6" s="81"/>
+      <c r="Q6" s="81"/>
+      <c r="R6" s="81"/>
+      <c r="S6" s="81"/>
+      <c r="T6" s="81"/>
+      <c r="U6" s="81"/>
+      <c r="V6" s="81"/>
+      <c r="W6" s="81"/>
+      <c r="X6" s="81"/>
+      <c r="Y6" s="81"/>
+      <c r="Z6" s="81"/>
+      <c r="AA6" s="81"/>
+      <c r="AB6" s="81"/>
+      <c r="AC6" s="81"/>
+      <c r="AD6" s="81"/>
+      <c r="AE6" s="81"/>
+      <c r="AF6" s="81"/>
+      <c r="AG6" s="81"/>
+      <c r="AH6" s="81"/>
+      <c r="AI6" s="81"/>
+      <c r="AJ6" s="81"/>
+      <c r="AK6" s="81"/>
+      <c r="AL6" s="81"/>
+      <c r="AM6" s="81"/>
+      <c r="AN6" s="81"/>
+      <c r="AO6" s="81"/>
+      <c r="AP6" s="82"/>
+      <c r="AQ6" s="86"/>
+      <c r="AR6" s="81"/>
+      <c r="AS6" s="81"/>
+      <c r="AT6" s="81"/>
+      <c r="AU6" s="81"/>
+      <c r="AV6" s="81"/>
+      <c r="AW6" s="81"/>
+      <c r="AX6" s="81"/>
+      <c r="AY6" s="81"/>
+      <c r="AZ6" s="81"/>
+      <c r="BA6" s="81"/>
+      <c r="BB6" s="81"/>
+      <c r="BC6" s="81"/>
+      <c r="BD6" s="81"/>
+      <c r="BE6" s="87"/>
     </row>
     <row r="7" spans="1:57" ht="15" customHeight="1">
-      <c r="A7" s="88"/>
-      <c r="B7" s="89"/>
-      <c r="C7" s="89"/>
-      <c r="D7" s="89"/>
-      <c r="E7" s="89"/>
-      <c r="F7" s="89"/>
-      <c r="G7" s="90"/>
-      <c r="H7" s="62"/>
-      <c r="I7" s="64"/>
-      <c r="J7" s="64"/>
-      <c r="K7" s="64"/>
-      <c r="L7" s="64"/>
-      <c r="M7" s="64"/>
-      <c r="N7" s="65"/>
-      <c r="O7" s="62"/>
-      <c r="P7" s="60"/>
-      <c r="Q7" s="60"/>
-      <c r="R7" s="60"/>
-      <c r="S7" s="60"/>
-      <c r="T7" s="60"/>
-      <c r="U7" s="60"/>
-      <c r="V7" s="60"/>
-      <c r="W7" s="60"/>
-      <c r="X7" s="60"/>
-      <c r="Y7" s="60"/>
-      <c r="Z7" s="60"/>
-      <c r="AA7" s="60"/>
-      <c r="AB7" s="60"/>
-      <c r="AC7" s="60"/>
-      <c r="AD7" s="60"/>
-      <c r="AE7" s="60"/>
-      <c r="AF7" s="60"/>
-      <c r="AG7" s="60"/>
-      <c r="AH7" s="60"/>
-      <c r="AI7" s="60"/>
-      <c r="AJ7" s="60"/>
-      <c r="AK7" s="60"/>
-      <c r="AL7" s="60"/>
-      <c r="AM7" s="60"/>
-      <c r="AN7" s="60"/>
-      <c r="AO7" s="60"/>
-      <c r="AP7" s="63"/>
-      <c r="AQ7" s="59"/>
-      <c r="AR7" s="60"/>
-      <c r="AS7" s="60"/>
-      <c r="AT7" s="60"/>
-      <c r="AU7" s="60"/>
-      <c r="AV7" s="60"/>
-      <c r="AW7" s="60"/>
-      <c r="AX7" s="60"/>
-      <c r="AY7" s="60"/>
-      <c r="AZ7" s="60"/>
-      <c r="BA7" s="60"/>
-      <c r="BB7" s="60"/>
-      <c r="BC7" s="60"/>
-      <c r="BD7" s="60"/>
-      <c r="BE7" s="61"/>
+      <c r="A7" s="70"/>
+      <c r="B7" s="71"/>
+      <c r="C7" s="71"/>
+      <c r="D7" s="71"/>
+      <c r="E7" s="71"/>
+      <c r="F7" s="71"/>
+      <c r="G7" s="72"/>
+      <c r="H7" s="78"/>
+      <c r="I7" s="79"/>
+      <c r="J7" s="79"/>
+      <c r="K7" s="79"/>
+      <c r="L7" s="79"/>
+      <c r="M7" s="79"/>
+      <c r="N7" s="80"/>
+      <c r="O7" s="78"/>
+      <c r="P7" s="81"/>
+      <c r="Q7" s="81"/>
+      <c r="R7" s="81"/>
+      <c r="S7" s="81"/>
+      <c r="T7" s="81"/>
+      <c r="U7" s="81"/>
+      <c r="V7" s="81"/>
+      <c r="W7" s="81"/>
+      <c r="X7" s="81"/>
+      <c r="Y7" s="81"/>
+      <c r="Z7" s="81"/>
+      <c r="AA7" s="81"/>
+      <c r="AB7" s="81"/>
+      <c r="AC7" s="81"/>
+      <c r="AD7" s="81"/>
+      <c r="AE7" s="81"/>
+      <c r="AF7" s="81"/>
+      <c r="AG7" s="81"/>
+      <c r="AH7" s="81"/>
+      <c r="AI7" s="81"/>
+      <c r="AJ7" s="81"/>
+      <c r="AK7" s="81"/>
+      <c r="AL7" s="81"/>
+      <c r="AM7" s="81"/>
+      <c r="AN7" s="81"/>
+      <c r="AO7" s="81"/>
+      <c r="AP7" s="82"/>
+      <c r="AQ7" s="86"/>
+      <c r="AR7" s="81"/>
+      <c r="AS7" s="81"/>
+      <c r="AT7" s="81"/>
+      <c r="AU7" s="81"/>
+      <c r="AV7" s="81"/>
+      <c r="AW7" s="81"/>
+      <c r="AX7" s="81"/>
+      <c r="AY7" s="81"/>
+      <c r="AZ7" s="81"/>
+      <c r="BA7" s="81"/>
+      <c r="BB7" s="81"/>
+      <c r="BC7" s="81"/>
+      <c r="BD7" s="81"/>
+      <c r="BE7" s="87"/>
     </row>
     <row r="8" spans="1:57" ht="15" customHeight="1">
-      <c r="A8" s="88"/>
-      <c r="B8" s="89"/>
-      <c r="C8" s="89"/>
-      <c r="D8" s="89"/>
-      <c r="E8" s="89"/>
-      <c r="F8" s="89"/>
-      <c r="G8" s="90"/>
-      <c r="H8" s="62"/>
-      <c r="I8" s="64"/>
-      <c r="J8" s="64"/>
-      <c r="K8" s="64"/>
-      <c r="L8" s="64"/>
-      <c r="M8" s="64"/>
-      <c r="N8" s="65"/>
-      <c r="O8" s="62"/>
-      <c r="P8" s="60"/>
-      <c r="Q8" s="60"/>
-      <c r="R8" s="60"/>
-      <c r="S8" s="60"/>
-      <c r="T8" s="60"/>
-      <c r="U8" s="60"/>
-      <c r="V8" s="60"/>
-      <c r="W8" s="60"/>
-      <c r="X8" s="60"/>
-      <c r="Y8" s="60"/>
-      <c r="Z8" s="60"/>
-      <c r="AA8" s="60"/>
-      <c r="AB8" s="60"/>
-      <c r="AC8" s="60"/>
-      <c r="AD8" s="60"/>
-      <c r="AE8" s="60"/>
-      <c r="AF8" s="60"/>
-      <c r="AG8" s="60"/>
-      <c r="AH8" s="60"/>
-      <c r="AI8" s="60"/>
-      <c r="AJ8" s="60"/>
-      <c r="AK8" s="60"/>
-      <c r="AL8" s="60"/>
-      <c r="AM8" s="60"/>
-      <c r="AN8" s="60"/>
-      <c r="AO8" s="60"/>
-      <c r="AP8" s="63"/>
-      <c r="AQ8" s="59"/>
-      <c r="AR8" s="60"/>
-      <c r="AS8" s="60"/>
-      <c r="AT8" s="60"/>
-      <c r="AU8" s="60"/>
-      <c r="AV8" s="60"/>
-      <c r="AW8" s="60"/>
-      <c r="AX8" s="60"/>
-      <c r="AY8" s="60"/>
-      <c r="AZ8" s="60"/>
-      <c r="BA8" s="60"/>
-      <c r="BB8" s="60"/>
-      <c r="BC8" s="60"/>
-      <c r="BD8" s="60"/>
-      <c r="BE8" s="61"/>
+      <c r="A8" s="70"/>
+      <c r="B8" s="71"/>
+      <c r="C8" s="71"/>
+      <c r="D8" s="71"/>
+      <c r="E8" s="71"/>
+      <c r="F8" s="71"/>
+      <c r="G8" s="72"/>
+      <c r="H8" s="78"/>
+      <c r="I8" s="79"/>
+      <c r="J8" s="79"/>
+      <c r="K8" s="79"/>
+      <c r="L8" s="79"/>
+      <c r="M8" s="79"/>
+      <c r="N8" s="80"/>
+      <c r="O8" s="78"/>
+      <c r="P8" s="81"/>
+      <c r="Q8" s="81"/>
+      <c r="R8" s="81"/>
+      <c r="S8" s="81"/>
+      <c r="T8" s="81"/>
+      <c r="U8" s="81"/>
+      <c r="V8" s="81"/>
+      <c r="W8" s="81"/>
+      <c r="X8" s="81"/>
+      <c r="Y8" s="81"/>
+      <c r="Z8" s="81"/>
+      <c r="AA8" s="81"/>
+      <c r="AB8" s="81"/>
+      <c r="AC8" s="81"/>
+      <c r="AD8" s="81"/>
+      <c r="AE8" s="81"/>
+      <c r="AF8" s="81"/>
+      <c r="AG8" s="81"/>
+      <c r="AH8" s="81"/>
+      <c r="AI8" s="81"/>
+      <c r="AJ8" s="81"/>
+      <c r="AK8" s="81"/>
+      <c r="AL8" s="81"/>
+      <c r="AM8" s="81"/>
+      <c r="AN8" s="81"/>
+      <c r="AO8" s="81"/>
+      <c r="AP8" s="82"/>
+      <c r="AQ8" s="86"/>
+      <c r="AR8" s="81"/>
+      <c r="AS8" s="81"/>
+      <c r="AT8" s="81"/>
+      <c r="AU8" s="81"/>
+      <c r="AV8" s="81"/>
+      <c r="AW8" s="81"/>
+      <c r="AX8" s="81"/>
+      <c r="AY8" s="81"/>
+      <c r="AZ8" s="81"/>
+      <c r="BA8" s="81"/>
+      <c r="BB8" s="81"/>
+      <c r="BC8" s="81"/>
+      <c r="BD8" s="81"/>
+      <c r="BE8" s="87"/>
     </row>
     <row r="9" spans="1:57" ht="15" customHeight="1">
-      <c r="A9" s="88"/>
-      <c r="B9" s="89"/>
-      <c r="C9" s="89"/>
-      <c r="D9" s="89"/>
-      <c r="E9" s="89"/>
-      <c r="F9" s="89"/>
-      <c r="G9" s="90"/>
-      <c r="H9" s="62"/>
-      <c r="I9" s="64"/>
-      <c r="J9" s="64"/>
-      <c r="K9" s="64"/>
-      <c r="L9" s="64"/>
-      <c r="M9" s="64"/>
-      <c r="N9" s="65"/>
-      <c r="O9" s="62"/>
-      <c r="P9" s="60"/>
-      <c r="Q9" s="60"/>
-      <c r="R9" s="60"/>
-      <c r="S9" s="60"/>
-      <c r="T9" s="60"/>
-      <c r="U9" s="60"/>
-      <c r="V9" s="60"/>
-      <c r="W9" s="60"/>
-      <c r="X9" s="60"/>
-      <c r="Y9" s="60"/>
-      <c r="Z9" s="60"/>
-      <c r="AA9" s="60"/>
-      <c r="AB9" s="60"/>
-      <c r="AC9" s="60"/>
-      <c r="AD9" s="60"/>
-      <c r="AE9" s="60"/>
-      <c r="AF9" s="60"/>
-      <c r="AG9" s="60"/>
-      <c r="AH9" s="60"/>
-      <c r="AI9" s="60"/>
-      <c r="AJ9" s="60"/>
-      <c r="AK9" s="60"/>
-      <c r="AL9" s="60"/>
-      <c r="AM9" s="60"/>
-      <c r="AN9" s="60"/>
-      <c r="AO9" s="60"/>
-      <c r="AP9" s="63"/>
-      <c r="AQ9" s="59"/>
-      <c r="AR9" s="60"/>
-      <c r="AS9" s="60"/>
-      <c r="AT9" s="60"/>
-      <c r="AU9" s="60"/>
-      <c r="AV9" s="60"/>
-      <c r="AW9" s="60"/>
-      <c r="AX9" s="60"/>
-      <c r="AY9" s="60"/>
-      <c r="AZ9" s="60"/>
-      <c r="BA9" s="60"/>
-      <c r="BB9" s="60"/>
-      <c r="BC9" s="60"/>
-      <c r="BD9" s="60"/>
-      <c r="BE9" s="61"/>
+      <c r="A9" s="70"/>
+      <c r="B9" s="71"/>
+      <c r="C9" s="71"/>
+      <c r="D9" s="71"/>
+      <c r="E9" s="71"/>
+      <c r="F9" s="71"/>
+      <c r="G9" s="72"/>
+      <c r="H9" s="78"/>
+      <c r="I9" s="79"/>
+      <c r="J9" s="79"/>
+      <c r="K9" s="79"/>
+      <c r="L9" s="79"/>
+      <c r="M9" s="79"/>
+      <c r="N9" s="80"/>
+      <c r="O9" s="78"/>
+      <c r="P9" s="81"/>
+      <c r="Q9" s="81"/>
+      <c r="R9" s="81"/>
+      <c r="S9" s="81"/>
+      <c r="T9" s="81"/>
+      <c r="U9" s="81"/>
+      <c r="V9" s="81"/>
+      <c r="W9" s="81"/>
+      <c r="X9" s="81"/>
+      <c r="Y9" s="81"/>
+      <c r="Z9" s="81"/>
+      <c r="AA9" s="81"/>
+      <c r="AB9" s="81"/>
+      <c r="AC9" s="81"/>
+      <c r="AD9" s="81"/>
+      <c r="AE9" s="81"/>
+      <c r="AF9" s="81"/>
+      <c r="AG9" s="81"/>
+      <c r="AH9" s="81"/>
+      <c r="AI9" s="81"/>
+      <c r="AJ9" s="81"/>
+      <c r="AK9" s="81"/>
+      <c r="AL9" s="81"/>
+      <c r="AM9" s="81"/>
+      <c r="AN9" s="81"/>
+      <c r="AO9" s="81"/>
+      <c r="AP9" s="82"/>
+      <c r="AQ9" s="86"/>
+      <c r="AR9" s="81"/>
+      <c r="AS9" s="81"/>
+      <c r="AT9" s="81"/>
+      <c r="AU9" s="81"/>
+      <c r="AV9" s="81"/>
+      <c r="AW9" s="81"/>
+      <c r="AX9" s="81"/>
+      <c r="AY9" s="81"/>
+      <c r="AZ9" s="81"/>
+      <c r="BA9" s="81"/>
+      <c r="BB9" s="81"/>
+      <c r="BC9" s="81"/>
+      <c r="BD9" s="81"/>
+      <c r="BE9" s="87"/>
     </row>
     <row r="10" spans="1:57" ht="15" customHeight="1">
-      <c r="A10" s="88"/>
-      <c r="B10" s="89"/>
-      <c r="C10" s="89"/>
-      <c r="D10" s="89"/>
-      <c r="E10" s="89"/>
-      <c r="F10" s="89"/>
-      <c r="G10" s="90"/>
-      <c r="H10" s="62"/>
-      <c r="I10" s="64"/>
-      <c r="J10" s="64"/>
-      <c r="K10" s="64"/>
-      <c r="L10" s="64"/>
-      <c r="M10" s="64"/>
-      <c r="N10" s="65"/>
-      <c r="O10" s="62"/>
-      <c r="P10" s="60"/>
-      <c r="Q10" s="60"/>
-      <c r="R10" s="60"/>
-      <c r="S10" s="60"/>
-      <c r="T10" s="60"/>
-      <c r="U10" s="60"/>
-      <c r="V10" s="60"/>
-      <c r="W10" s="60"/>
-      <c r="X10" s="60"/>
-      <c r="Y10" s="60"/>
-      <c r="Z10" s="60"/>
-      <c r="AA10" s="60"/>
-      <c r="AB10" s="60"/>
-      <c r="AC10" s="60"/>
-      <c r="AD10" s="60"/>
-      <c r="AE10" s="60"/>
-      <c r="AF10" s="60"/>
-      <c r="AG10" s="60"/>
-      <c r="AH10" s="60"/>
-      <c r="AI10" s="60"/>
-      <c r="AJ10" s="60"/>
-      <c r="AK10" s="60"/>
-      <c r="AL10" s="60"/>
-      <c r="AM10" s="60"/>
-      <c r="AN10" s="60"/>
-      <c r="AO10" s="60"/>
-      <c r="AP10" s="63"/>
-      <c r="AQ10" s="59"/>
-      <c r="AR10" s="60"/>
-      <c r="AS10" s="60"/>
-      <c r="AT10" s="60"/>
-      <c r="AU10" s="60"/>
-      <c r="AV10" s="60"/>
-      <c r="AW10" s="60"/>
-      <c r="AX10" s="60"/>
-      <c r="AY10" s="60"/>
-      <c r="AZ10" s="60"/>
-      <c r="BA10" s="60"/>
-      <c r="BB10" s="60"/>
-      <c r="BC10" s="60"/>
-      <c r="BD10" s="60"/>
-      <c r="BE10" s="61"/>
+      <c r="A10" s="70"/>
+      <c r="B10" s="71"/>
+      <c r="C10" s="71"/>
+      <c r="D10" s="71"/>
+      <c r="E10" s="71"/>
+      <c r="F10" s="71"/>
+      <c r="G10" s="72"/>
+      <c r="H10" s="78"/>
+      <c r="I10" s="79"/>
+      <c r="J10" s="79"/>
+      <c r="K10" s="79"/>
+      <c r="L10" s="79"/>
+      <c r="M10" s="79"/>
+      <c r="N10" s="80"/>
+      <c r="O10" s="78"/>
+      <c r="P10" s="81"/>
+      <c r="Q10" s="81"/>
+      <c r="R10" s="81"/>
+      <c r="S10" s="81"/>
+      <c r="T10" s="81"/>
+      <c r="U10" s="81"/>
+      <c r="V10" s="81"/>
+      <c r="W10" s="81"/>
+      <c r="X10" s="81"/>
+      <c r="Y10" s="81"/>
+      <c r="Z10" s="81"/>
+      <c r="AA10" s="81"/>
+      <c r="AB10" s="81"/>
+      <c r="AC10" s="81"/>
+      <c r="AD10" s="81"/>
+      <c r="AE10" s="81"/>
+      <c r="AF10" s="81"/>
+      <c r="AG10" s="81"/>
+      <c r="AH10" s="81"/>
+      <c r="AI10" s="81"/>
+      <c r="AJ10" s="81"/>
+      <c r="AK10" s="81"/>
+      <c r="AL10" s="81"/>
+      <c r="AM10" s="81"/>
+      <c r="AN10" s="81"/>
+      <c r="AO10" s="81"/>
+      <c r="AP10" s="82"/>
+      <c r="AQ10" s="86"/>
+      <c r="AR10" s="81"/>
+      <c r="AS10" s="81"/>
+      <c r="AT10" s="81"/>
+      <c r="AU10" s="81"/>
+      <c r="AV10" s="81"/>
+      <c r="AW10" s="81"/>
+      <c r="AX10" s="81"/>
+      <c r="AY10" s="81"/>
+      <c r="AZ10" s="81"/>
+      <c r="BA10" s="81"/>
+      <c r="BB10" s="81"/>
+      <c r="BC10" s="81"/>
+      <c r="BD10" s="81"/>
+      <c r="BE10" s="87"/>
     </row>
     <row r="11" spans="1:57" ht="15" customHeight="1">
-      <c r="A11" s="88"/>
-      <c r="B11" s="89"/>
-      <c r="C11" s="89"/>
-      <c r="D11" s="89"/>
-      <c r="E11" s="89"/>
-      <c r="F11" s="89"/>
-      <c r="G11" s="90"/>
-      <c r="H11" s="62"/>
-      <c r="I11" s="64"/>
-      <c r="J11" s="64"/>
-      <c r="K11" s="64"/>
-      <c r="L11" s="64"/>
-      <c r="M11" s="64"/>
-      <c r="N11" s="65"/>
-      <c r="O11" s="62"/>
-      <c r="P11" s="60"/>
-      <c r="Q11" s="60"/>
-      <c r="R11" s="60"/>
-      <c r="S11" s="60"/>
-      <c r="T11" s="60"/>
-      <c r="U11" s="60"/>
-      <c r="V11" s="60"/>
-      <c r="W11" s="60"/>
-      <c r="X11" s="60"/>
-      <c r="Y11" s="60"/>
-      <c r="Z11" s="60"/>
-      <c r="AA11" s="60"/>
-      <c r="AB11" s="60"/>
-      <c r="AC11" s="60"/>
-      <c r="AD11" s="60"/>
-      <c r="AE11" s="60"/>
-      <c r="AF11" s="60"/>
-      <c r="AG11" s="60"/>
-      <c r="AH11" s="60"/>
-      <c r="AI11" s="60"/>
-      <c r="AJ11" s="60"/>
-      <c r="AK11" s="60"/>
-      <c r="AL11" s="60"/>
-      <c r="AM11" s="60"/>
-      <c r="AN11" s="60"/>
-      <c r="AO11" s="60"/>
-      <c r="AP11" s="63"/>
-      <c r="AQ11" s="59"/>
-      <c r="AR11" s="60"/>
-      <c r="AS11" s="60"/>
-      <c r="AT11" s="60"/>
-      <c r="AU11" s="60"/>
-      <c r="AV11" s="60"/>
-      <c r="AW11" s="60"/>
-      <c r="AX11" s="60"/>
-      <c r="AY11" s="60"/>
-      <c r="AZ11" s="60"/>
-      <c r="BA11" s="60"/>
-      <c r="BB11" s="60"/>
-      <c r="BC11" s="60"/>
-      <c r="BD11" s="60"/>
-      <c r="BE11" s="61"/>
+      <c r="A11" s="70"/>
+      <c r="B11" s="71"/>
+      <c r="C11" s="71"/>
+      <c r="D11" s="71"/>
+      <c r="E11" s="71"/>
+      <c r="F11" s="71"/>
+      <c r="G11" s="72"/>
+      <c r="H11" s="78"/>
+      <c r="I11" s="79"/>
+      <c r="J11" s="79"/>
+      <c r="K11" s="79"/>
+      <c r="L11" s="79"/>
+      <c r="M11" s="79"/>
+      <c r="N11" s="80"/>
+      <c r="O11" s="78"/>
+      <c r="P11" s="81"/>
+      <c r="Q11" s="81"/>
+      <c r="R11" s="81"/>
+      <c r="S11" s="81"/>
+      <c r="T11" s="81"/>
+      <c r="U11" s="81"/>
+      <c r="V11" s="81"/>
+      <c r="W11" s="81"/>
+      <c r="X11" s="81"/>
+      <c r="Y11" s="81"/>
+      <c r="Z11" s="81"/>
+      <c r="AA11" s="81"/>
+      <c r="AB11" s="81"/>
+      <c r="AC11" s="81"/>
+      <c r="AD11" s="81"/>
+      <c r="AE11" s="81"/>
+      <c r="AF11" s="81"/>
+      <c r="AG11" s="81"/>
+      <c r="AH11" s="81"/>
+      <c r="AI11" s="81"/>
+      <c r="AJ11" s="81"/>
+      <c r="AK11" s="81"/>
+      <c r="AL11" s="81"/>
+      <c r="AM11" s="81"/>
+      <c r="AN11" s="81"/>
+      <c r="AO11" s="81"/>
+      <c r="AP11" s="82"/>
+      <c r="AQ11" s="86"/>
+      <c r="AR11" s="81"/>
+      <c r="AS11" s="81"/>
+      <c r="AT11" s="81"/>
+      <c r="AU11" s="81"/>
+      <c r="AV11" s="81"/>
+      <c r="AW11" s="81"/>
+      <c r="AX11" s="81"/>
+      <c r="AY11" s="81"/>
+      <c r="AZ11" s="81"/>
+      <c r="BA11" s="81"/>
+      <c r="BB11" s="81"/>
+      <c r="BC11" s="81"/>
+      <c r="BD11" s="81"/>
+      <c r="BE11" s="87"/>
     </row>
     <row r="12" spans="1:57" ht="15" customHeight="1">
-      <c r="A12" s="88"/>
-      <c r="B12" s="89"/>
-      <c r="C12" s="89"/>
-      <c r="D12" s="89"/>
-      <c r="E12" s="89"/>
-      <c r="F12" s="89"/>
-      <c r="G12" s="90"/>
-      <c r="H12" s="62"/>
-      <c r="I12" s="64"/>
-      <c r="J12" s="64"/>
-      <c r="K12" s="64"/>
-      <c r="L12" s="64"/>
-      <c r="M12" s="64"/>
-      <c r="N12" s="65"/>
-      <c r="O12" s="62"/>
-      <c r="P12" s="60"/>
-      <c r="Q12" s="60"/>
-      <c r="R12" s="60"/>
-      <c r="S12" s="60"/>
-      <c r="T12" s="60"/>
-      <c r="U12" s="60"/>
-      <c r="V12" s="60"/>
-      <c r="W12" s="60"/>
-      <c r="X12" s="60"/>
-      <c r="Y12" s="60"/>
-      <c r="Z12" s="60"/>
-      <c r="AA12" s="60"/>
-      <c r="AB12" s="60"/>
-      <c r="AC12" s="60"/>
-      <c r="AD12" s="60"/>
-      <c r="AE12" s="60"/>
-      <c r="AF12" s="60"/>
-      <c r="AG12" s="60"/>
-      <c r="AH12" s="60"/>
-      <c r="AI12" s="60"/>
-      <c r="AJ12" s="60"/>
-      <c r="AK12" s="60"/>
-      <c r="AL12" s="60"/>
-      <c r="AM12" s="60"/>
-      <c r="AN12" s="60"/>
-      <c r="AO12" s="60"/>
-      <c r="AP12" s="63"/>
-      <c r="AQ12" s="59"/>
-      <c r="AR12" s="60"/>
-      <c r="AS12" s="60"/>
-      <c r="AT12" s="60"/>
-      <c r="AU12" s="60"/>
-      <c r="AV12" s="60"/>
-      <c r="AW12" s="60"/>
-      <c r="AX12" s="60"/>
-      <c r="AY12" s="60"/>
-      <c r="AZ12" s="60"/>
-      <c r="BA12" s="60"/>
-      <c r="BB12" s="60"/>
-      <c r="BC12" s="60"/>
-      <c r="BD12" s="60"/>
-      <c r="BE12" s="61"/>
+      <c r="A12" s="70"/>
+      <c r="B12" s="71"/>
+      <c r="C12" s="71"/>
+      <c r="D12" s="71"/>
+      <c r="E12" s="71"/>
+      <c r="F12" s="71"/>
+      <c r="G12" s="72"/>
+      <c r="H12" s="78"/>
+      <c r="I12" s="79"/>
+      <c r="J12" s="79"/>
+      <c r="K12" s="79"/>
+      <c r="L12" s="79"/>
+      <c r="M12" s="79"/>
+      <c r="N12" s="80"/>
+      <c r="O12" s="78"/>
+      <c r="P12" s="81"/>
+      <c r="Q12" s="81"/>
+      <c r="R12" s="81"/>
+      <c r="S12" s="81"/>
+      <c r="T12" s="81"/>
+      <c r="U12" s="81"/>
+      <c r="V12" s="81"/>
+      <c r="W12" s="81"/>
+      <c r="X12" s="81"/>
+      <c r="Y12" s="81"/>
+      <c r="Z12" s="81"/>
+      <c r="AA12" s="81"/>
+      <c r="AB12" s="81"/>
+      <c r="AC12" s="81"/>
+      <c r="AD12" s="81"/>
+      <c r="AE12" s="81"/>
+      <c r="AF12" s="81"/>
+      <c r="AG12" s="81"/>
+      <c r="AH12" s="81"/>
+      <c r="AI12" s="81"/>
+      <c r="AJ12" s="81"/>
+      <c r="AK12" s="81"/>
+      <c r="AL12" s="81"/>
+      <c r="AM12" s="81"/>
+      <c r="AN12" s="81"/>
+      <c r="AO12" s="81"/>
+      <c r="AP12" s="82"/>
+      <c r="AQ12" s="86"/>
+      <c r="AR12" s="81"/>
+      <c r="AS12" s="81"/>
+      <c r="AT12" s="81"/>
+      <c r="AU12" s="81"/>
+      <c r="AV12" s="81"/>
+      <c r="AW12" s="81"/>
+      <c r="AX12" s="81"/>
+      <c r="AY12" s="81"/>
+      <c r="AZ12" s="81"/>
+      <c r="BA12" s="81"/>
+      <c r="BB12" s="81"/>
+      <c r="BC12" s="81"/>
+      <c r="BD12" s="81"/>
+      <c r="BE12" s="87"/>
     </row>
     <row r="13" spans="1:57" ht="15" customHeight="1">
-      <c r="A13" s="88"/>
-      <c r="B13" s="89"/>
-      <c r="C13" s="89"/>
-      <c r="D13" s="89"/>
-      <c r="E13" s="89"/>
-      <c r="F13" s="89"/>
-      <c r="G13" s="90"/>
-      <c r="H13" s="62"/>
-      <c r="I13" s="64"/>
-      <c r="J13" s="64"/>
-      <c r="K13" s="64"/>
-      <c r="L13" s="64"/>
-      <c r="M13" s="64"/>
-      <c r="N13" s="65"/>
-      <c r="O13" s="62"/>
-      <c r="P13" s="60"/>
-      <c r="Q13" s="60"/>
-      <c r="R13" s="60"/>
-      <c r="S13" s="60"/>
-      <c r="T13" s="60"/>
-      <c r="U13" s="60"/>
-      <c r="V13" s="60"/>
-      <c r="W13" s="60"/>
-      <c r="X13" s="60"/>
-      <c r="Y13" s="60"/>
-      <c r="Z13" s="60"/>
-      <c r="AA13" s="60"/>
-      <c r="AB13" s="60"/>
-      <c r="AC13" s="60"/>
-      <c r="AD13" s="60"/>
-      <c r="AE13" s="60"/>
-      <c r="AF13" s="60"/>
-      <c r="AG13" s="60"/>
-      <c r="AH13" s="60"/>
-      <c r="AI13" s="60"/>
-      <c r="AJ13" s="60"/>
-      <c r="AK13" s="60"/>
-      <c r="AL13" s="60"/>
-      <c r="AM13" s="60"/>
-      <c r="AN13" s="60"/>
-      <c r="AO13" s="60"/>
-      <c r="AP13" s="63"/>
-      <c r="AQ13" s="59"/>
-      <c r="AR13" s="60"/>
-      <c r="AS13" s="60"/>
-      <c r="AT13" s="60"/>
-      <c r="AU13" s="60"/>
-      <c r="AV13" s="60"/>
-      <c r="AW13" s="60"/>
-      <c r="AX13" s="60"/>
-      <c r="AY13" s="60"/>
-      <c r="AZ13" s="60"/>
-      <c r="BA13" s="60"/>
-      <c r="BB13" s="60"/>
-      <c r="BC13" s="60"/>
-      <c r="BD13" s="60"/>
-      <c r="BE13" s="61"/>
+      <c r="A13" s="70"/>
+      <c r="B13" s="71"/>
+      <c r="C13" s="71"/>
+      <c r="D13" s="71"/>
+      <c r="E13" s="71"/>
+      <c r="F13" s="71"/>
+      <c r="G13" s="72"/>
+      <c r="H13" s="78"/>
+      <c r="I13" s="79"/>
+      <c r="J13" s="79"/>
+      <c r="K13" s="79"/>
+      <c r="L13" s="79"/>
+      <c r="M13" s="79"/>
+      <c r="N13" s="80"/>
+      <c r="O13" s="78"/>
+      <c r="P13" s="81"/>
+      <c r="Q13" s="81"/>
+      <c r="R13" s="81"/>
+      <c r="S13" s="81"/>
+      <c r="T13" s="81"/>
+      <c r="U13" s="81"/>
+      <c r="V13" s="81"/>
+      <c r="W13" s="81"/>
+      <c r="X13" s="81"/>
+      <c r="Y13" s="81"/>
+      <c r="Z13" s="81"/>
+      <c r="AA13" s="81"/>
+      <c r="AB13" s="81"/>
+      <c r="AC13" s="81"/>
+      <c r="AD13" s="81"/>
+      <c r="AE13" s="81"/>
+      <c r="AF13" s="81"/>
+      <c r="AG13" s="81"/>
+      <c r="AH13" s="81"/>
+      <c r="AI13" s="81"/>
+      <c r="AJ13" s="81"/>
+      <c r="AK13" s="81"/>
+      <c r="AL13" s="81"/>
+      <c r="AM13" s="81"/>
+      <c r="AN13" s="81"/>
+      <c r="AO13" s="81"/>
+      <c r="AP13" s="82"/>
+      <c r="AQ13" s="86"/>
+      <c r="AR13" s="81"/>
+      <c r="AS13" s="81"/>
+      <c r="AT13" s="81"/>
+      <c r="AU13" s="81"/>
+      <c r="AV13" s="81"/>
+      <c r="AW13" s="81"/>
+      <c r="AX13" s="81"/>
+      <c r="AY13" s="81"/>
+      <c r="AZ13" s="81"/>
+      <c r="BA13" s="81"/>
+      <c r="BB13" s="81"/>
+      <c r="BC13" s="81"/>
+      <c r="BD13" s="81"/>
+      <c r="BE13" s="87"/>
     </row>
     <row r="14" spans="1:57" ht="15" customHeight="1">
-      <c r="A14" s="88"/>
-      <c r="B14" s="89"/>
-      <c r="C14" s="89"/>
-      <c r="D14" s="89"/>
-      <c r="E14" s="89"/>
-      <c r="F14" s="89"/>
-      <c r="G14" s="90"/>
-      <c r="H14" s="62"/>
-      <c r="I14" s="64"/>
-      <c r="J14" s="64"/>
-      <c r="K14" s="64"/>
-      <c r="L14" s="64"/>
-      <c r="M14" s="64"/>
-      <c r="N14" s="65"/>
-      <c r="O14" s="62"/>
-      <c r="P14" s="60"/>
-      <c r="Q14" s="60"/>
-      <c r="R14" s="60"/>
-      <c r="S14" s="60"/>
-      <c r="T14" s="60"/>
-      <c r="U14" s="60"/>
-      <c r="V14" s="60"/>
-      <c r="W14" s="60"/>
-      <c r="X14" s="60"/>
-      <c r="Y14" s="60"/>
-      <c r="Z14" s="60"/>
-      <c r="AA14" s="60"/>
-      <c r="AB14" s="60"/>
-      <c r="AC14" s="60"/>
-      <c r="AD14" s="60"/>
-      <c r="AE14" s="60"/>
-      <c r="AF14" s="60"/>
-      <c r="AG14" s="60"/>
-      <c r="AH14" s="60"/>
-      <c r="AI14" s="60"/>
-      <c r="AJ14" s="60"/>
-      <c r="AK14" s="60"/>
-      <c r="AL14" s="60"/>
-      <c r="AM14" s="60"/>
-      <c r="AN14" s="60"/>
-      <c r="AO14" s="60"/>
-      <c r="AP14" s="63"/>
-      <c r="AQ14" s="59"/>
-      <c r="AR14" s="60"/>
-      <c r="AS14" s="60"/>
-      <c r="AT14" s="60"/>
-      <c r="AU14" s="60"/>
-      <c r="AV14" s="60"/>
-      <c r="AW14" s="60"/>
-      <c r="AX14" s="60"/>
-      <c r="AY14" s="60"/>
-      <c r="AZ14" s="60"/>
-      <c r="BA14" s="60"/>
-      <c r="BB14" s="60"/>
-      <c r="BC14" s="60"/>
-      <c r="BD14" s="60"/>
-      <c r="BE14" s="61"/>
+      <c r="A14" s="70"/>
+      <c r="B14" s="71"/>
+      <c r="C14" s="71"/>
+      <c r="D14" s="71"/>
+      <c r="E14" s="71"/>
+      <c r="F14" s="71"/>
+      <c r="G14" s="72"/>
+      <c r="H14" s="78"/>
+      <c r="I14" s="79"/>
+      <c r="J14" s="79"/>
+      <c r="K14" s="79"/>
+      <c r="L14" s="79"/>
+      <c r="M14" s="79"/>
+      <c r="N14" s="80"/>
+      <c r="O14" s="78"/>
+      <c r="P14" s="81"/>
+      <c r="Q14" s="81"/>
+      <c r="R14" s="81"/>
+      <c r="S14" s="81"/>
+      <c r="T14" s="81"/>
+      <c r="U14" s="81"/>
+      <c r="V14" s="81"/>
+      <c r="W14" s="81"/>
+      <c r="X14" s="81"/>
+      <c r="Y14" s="81"/>
+      <c r="Z14" s="81"/>
+      <c r="AA14" s="81"/>
+      <c r="AB14" s="81"/>
+      <c r="AC14" s="81"/>
+      <c r="AD14" s="81"/>
+      <c r="AE14" s="81"/>
+      <c r="AF14" s="81"/>
+      <c r="AG14" s="81"/>
+      <c r="AH14" s="81"/>
+      <c r="AI14" s="81"/>
+      <c r="AJ14" s="81"/>
+      <c r="AK14" s="81"/>
+      <c r="AL14" s="81"/>
+      <c r="AM14" s="81"/>
+      <c r="AN14" s="81"/>
+      <c r="AO14" s="81"/>
+      <c r="AP14" s="82"/>
+      <c r="AQ14" s="86"/>
+      <c r="AR14" s="81"/>
+      <c r="AS14" s="81"/>
+      <c r="AT14" s="81"/>
+      <c r="AU14" s="81"/>
+      <c r="AV14" s="81"/>
+      <c r="AW14" s="81"/>
+      <c r="AX14" s="81"/>
+      <c r="AY14" s="81"/>
+      <c r="AZ14" s="81"/>
+      <c r="BA14" s="81"/>
+      <c r="BB14" s="81"/>
+      <c r="BC14" s="81"/>
+      <c r="BD14" s="81"/>
+      <c r="BE14" s="87"/>
     </row>
     <row r="15" spans="1:57" ht="15" customHeight="1">
-      <c r="A15" s="88"/>
-      <c r="B15" s="89"/>
-      <c r="C15" s="89"/>
-      <c r="D15" s="89"/>
-      <c r="E15" s="89"/>
-      <c r="F15" s="89"/>
-      <c r="G15" s="90"/>
-      <c r="H15" s="62"/>
-      <c r="I15" s="64"/>
-      <c r="J15" s="64"/>
-      <c r="K15" s="64"/>
-      <c r="L15" s="64"/>
-      <c r="M15" s="64"/>
-      <c r="N15" s="65"/>
-      <c r="O15" s="62"/>
-      <c r="P15" s="60"/>
-      <c r="Q15" s="60"/>
-      <c r="R15" s="60"/>
-      <c r="S15" s="60"/>
-      <c r="T15" s="60"/>
-      <c r="U15" s="60"/>
-      <c r="V15" s="60"/>
-      <c r="W15" s="60"/>
-      <c r="X15" s="60"/>
-      <c r="Y15" s="60"/>
-      <c r="Z15" s="60"/>
-      <c r="AA15" s="60"/>
-      <c r="AB15" s="60"/>
-      <c r="AC15" s="60"/>
-      <c r="AD15" s="60"/>
-      <c r="AE15" s="60"/>
-      <c r="AF15" s="60"/>
-      <c r="AG15" s="60"/>
-      <c r="AH15" s="60"/>
-      <c r="AI15" s="60"/>
-      <c r="AJ15" s="60"/>
-      <c r="AK15" s="60"/>
-      <c r="AL15" s="60"/>
-      <c r="AM15" s="60"/>
-      <c r="AN15" s="60"/>
-      <c r="AO15" s="60"/>
-      <c r="AP15" s="63"/>
-      <c r="AQ15" s="59"/>
-      <c r="AR15" s="60"/>
-      <c r="AS15" s="60"/>
-      <c r="AT15" s="60"/>
-      <c r="AU15" s="60"/>
-      <c r="AV15" s="60"/>
-      <c r="AW15" s="60"/>
-      <c r="AX15" s="60"/>
-      <c r="AY15" s="60"/>
-      <c r="AZ15" s="60"/>
-      <c r="BA15" s="60"/>
-      <c r="BB15" s="60"/>
-      <c r="BC15" s="60"/>
-      <c r="BD15" s="60"/>
-      <c r="BE15" s="61"/>
+      <c r="A15" s="70"/>
+      <c r="B15" s="71"/>
+      <c r="C15" s="71"/>
+      <c r="D15" s="71"/>
+      <c r="E15" s="71"/>
+      <c r="F15" s="71"/>
+      <c r="G15" s="72"/>
+      <c r="H15" s="78"/>
+      <c r="I15" s="79"/>
+      <c r="J15" s="79"/>
+      <c r="K15" s="79"/>
+      <c r="L15" s="79"/>
+      <c r="M15" s="79"/>
+      <c r="N15" s="80"/>
+      <c r="O15" s="78"/>
+      <c r="P15" s="81"/>
+      <c r="Q15" s="81"/>
+      <c r="R15" s="81"/>
+      <c r="S15" s="81"/>
+      <c r="T15" s="81"/>
+      <c r="U15" s="81"/>
+      <c r="V15" s="81"/>
+      <c r="W15" s="81"/>
+      <c r="X15" s="81"/>
+      <c r="Y15" s="81"/>
+      <c r="Z15" s="81"/>
+      <c r="AA15" s="81"/>
+      <c r="AB15" s="81"/>
+      <c r="AC15" s="81"/>
+      <c r="AD15" s="81"/>
+      <c r="AE15" s="81"/>
+      <c r="AF15" s="81"/>
+      <c r="AG15" s="81"/>
+      <c r="AH15" s="81"/>
+      <c r="AI15" s="81"/>
+      <c r="AJ15" s="81"/>
+      <c r="AK15" s="81"/>
+      <c r="AL15" s="81"/>
+      <c r="AM15" s="81"/>
+      <c r="AN15" s="81"/>
+      <c r="AO15" s="81"/>
+      <c r="AP15" s="82"/>
+      <c r="AQ15" s="86"/>
+      <c r="AR15" s="81"/>
+      <c r="AS15" s="81"/>
+      <c r="AT15" s="81"/>
+      <c r="AU15" s="81"/>
+      <c r="AV15" s="81"/>
+      <c r="AW15" s="81"/>
+      <c r="AX15" s="81"/>
+      <c r="AY15" s="81"/>
+      <c r="AZ15" s="81"/>
+      <c r="BA15" s="81"/>
+      <c r="BB15" s="81"/>
+      <c r="BC15" s="81"/>
+      <c r="BD15" s="81"/>
+      <c r="BE15" s="87"/>
     </row>
     <row r="16" spans="1:57" ht="15" customHeight="1">
-      <c r="A16" s="88"/>
-      <c r="B16" s="89"/>
-      <c r="C16" s="89"/>
-      <c r="D16" s="89"/>
-      <c r="E16" s="89"/>
-      <c r="F16" s="89"/>
-      <c r="G16" s="90"/>
-      <c r="H16" s="62"/>
-      <c r="I16" s="64"/>
-      <c r="J16" s="64"/>
-      <c r="K16" s="64"/>
-      <c r="L16" s="64"/>
-      <c r="M16" s="64"/>
-      <c r="N16" s="65"/>
-      <c r="O16" s="62"/>
-      <c r="P16" s="60"/>
-      <c r="Q16" s="60"/>
-      <c r="R16" s="60"/>
-      <c r="S16" s="60"/>
-      <c r="T16" s="60"/>
-      <c r="U16" s="60"/>
-      <c r="V16" s="60"/>
-      <c r="W16" s="60"/>
-      <c r="X16" s="60"/>
-      <c r="Y16" s="60"/>
-      <c r="Z16" s="60"/>
-      <c r="AA16" s="60"/>
-      <c r="AB16" s="60"/>
-      <c r="AC16" s="60"/>
-      <c r="AD16" s="60"/>
-      <c r="AE16" s="60"/>
-      <c r="AF16" s="60"/>
-      <c r="AG16" s="60"/>
-      <c r="AH16" s="60"/>
-      <c r="AI16" s="60"/>
-      <c r="AJ16" s="60"/>
-      <c r="AK16" s="60"/>
-      <c r="AL16" s="60"/>
-      <c r="AM16" s="60"/>
-      <c r="AN16" s="60"/>
-      <c r="AO16" s="60"/>
-      <c r="AP16" s="63"/>
-      <c r="AQ16" s="59"/>
-      <c r="AR16" s="60"/>
-      <c r="AS16" s="60"/>
-      <c r="AT16" s="60"/>
-      <c r="AU16" s="60"/>
-      <c r="AV16" s="60"/>
-      <c r="AW16" s="60"/>
-      <c r="AX16" s="60"/>
-      <c r="AY16" s="60"/>
-      <c r="AZ16" s="60"/>
-      <c r="BA16" s="60"/>
-      <c r="BB16" s="60"/>
-      <c r="BC16" s="60"/>
-      <c r="BD16" s="60"/>
-      <c r="BE16" s="61"/>
+      <c r="A16" s="70"/>
+      <c r="B16" s="71"/>
+      <c r="C16" s="71"/>
+      <c r="D16" s="71"/>
+      <c r="E16" s="71"/>
+      <c r="F16" s="71"/>
+      <c r="G16" s="72"/>
+      <c r="H16" s="78"/>
+      <c r="I16" s="79"/>
+      <c r="J16" s="79"/>
+      <c r="K16" s="79"/>
+      <c r="L16" s="79"/>
+      <c r="M16" s="79"/>
+      <c r="N16" s="80"/>
+      <c r="O16" s="78"/>
+      <c r="P16" s="81"/>
+      <c r="Q16" s="81"/>
+      <c r="R16" s="81"/>
+      <c r="S16" s="81"/>
+      <c r="T16" s="81"/>
+      <c r="U16" s="81"/>
+      <c r="V16" s="81"/>
+      <c r="W16" s="81"/>
+      <c r="X16" s="81"/>
+      <c r="Y16" s="81"/>
+      <c r="Z16" s="81"/>
+      <c r="AA16" s="81"/>
+      <c r="AB16" s="81"/>
+      <c r="AC16" s="81"/>
+      <c r="AD16" s="81"/>
+      <c r="AE16" s="81"/>
+      <c r="AF16" s="81"/>
+      <c r="AG16" s="81"/>
+      <c r="AH16" s="81"/>
+      <c r="AI16" s="81"/>
+      <c r="AJ16" s="81"/>
+      <c r="AK16" s="81"/>
+      <c r="AL16" s="81"/>
+      <c r="AM16" s="81"/>
+      <c r="AN16" s="81"/>
+      <c r="AO16" s="81"/>
+      <c r="AP16" s="82"/>
+      <c r="AQ16" s="86"/>
+      <c r="AR16" s="81"/>
+      <c r="AS16" s="81"/>
+      <c r="AT16" s="81"/>
+      <c r="AU16" s="81"/>
+      <c r="AV16" s="81"/>
+      <c r="AW16" s="81"/>
+      <c r="AX16" s="81"/>
+      <c r="AY16" s="81"/>
+      <c r="AZ16" s="81"/>
+      <c r="BA16" s="81"/>
+      <c r="BB16" s="81"/>
+      <c r="BC16" s="81"/>
+      <c r="BD16" s="81"/>
+      <c r="BE16" s="87"/>
     </row>
     <row r="17" spans="1:57" ht="15" customHeight="1">
-      <c r="A17" s="88"/>
-      <c r="B17" s="89"/>
-      <c r="C17" s="89"/>
-      <c r="D17" s="89"/>
-      <c r="E17" s="89"/>
-      <c r="F17" s="89"/>
-      <c r="G17" s="90"/>
-      <c r="H17" s="62"/>
-      <c r="I17" s="64"/>
-      <c r="J17" s="64"/>
-      <c r="K17" s="64"/>
-      <c r="L17" s="64"/>
-      <c r="M17" s="64"/>
-      <c r="N17" s="65"/>
-      <c r="O17" s="62"/>
-      <c r="P17" s="60"/>
-      <c r="Q17" s="60"/>
-      <c r="R17" s="60"/>
-      <c r="S17" s="60"/>
-      <c r="T17" s="60"/>
-      <c r="U17" s="60"/>
-      <c r="V17" s="60"/>
-      <c r="W17" s="60"/>
-      <c r="X17" s="60"/>
-      <c r="Y17" s="60"/>
-      <c r="Z17" s="60"/>
-      <c r="AA17" s="60"/>
-      <c r="AB17" s="60"/>
-      <c r="AC17" s="60"/>
-      <c r="AD17" s="60"/>
-      <c r="AE17" s="60"/>
-      <c r="AF17" s="60"/>
-      <c r="AG17" s="60"/>
-      <c r="AH17" s="60"/>
-      <c r="AI17" s="60"/>
-      <c r="AJ17" s="60"/>
-      <c r="AK17" s="60"/>
-      <c r="AL17" s="60"/>
-      <c r="AM17" s="60"/>
-      <c r="AN17" s="60"/>
-      <c r="AO17" s="60"/>
-      <c r="AP17" s="63"/>
-      <c r="AQ17" s="59"/>
-      <c r="AR17" s="60"/>
-      <c r="AS17" s="60"/>
-      <c r="AT17" s="60"/>
-      <c r="AU17" s="60"/>
-      <c r="AV17" s="60"/>
-      <c r="AW17" s="60"/>
-      <c r="AX17" s="60"/>
-      <c r="AY17" s="60"/>
-      <c r="AZ17" s="60"/>
-      <c r="BA17" s="60"/>
-      <c r="BB17" s="60"/>
-      <c r="BC17" s="60"/>
-      <c r="BD17" s="60"/>
-      <c r="BE17" s="61"/>
+      <c r="A17" s="70"/>
+      <c r="B17" s="71"/>
+      <c r="C17" s="71"/>
+      <c r="D17" s="71"/>
+      <c r="E17" s="71"/>
+      <c r="F17" s="71"/>
+      <c r="G17" s="72"/>
+      <c r="H17" s="78"/>
+      <c r="I17" s="79"/>
+      <c r="J17" s="79"/>
+      <c r="K17" s="79"/>
+      <c r="L17" s="79"/>
+      <c r="M17" s="79"/>
+      <c r="N17" s="80"/>
+      <c r="O17" s="78"/>
+      <c r="P17" s="81"/>
+      <c r="Q17" s="81"/>
+      <c r="R17" s="81"/>
+      <c r="S17" s="81"/>
+      <c r="T17" s="81"/>
+      <c r="U17" s="81"/>
+      <c r="V17" s="81"/>
+      <c r="W17" s="81"/>
+      <c r="X17" s="81"/>
+      <c r="Y17" s="81"/>
+      <c r="Z17" s="81"/>
+      <c r="AA17" s="81"/>
+      <c r="AB17" s="81"/>
+      <c r="AC17" s="81"/>
+      <c r="AD17" s="81"/>
+      <c r="AE17" s="81"/>
+      <c r="AF17" s="81"/>
+      <c r="AG17" s="81"/>
+      <c r="AH17" s="81"/>
+      <c r="AI17" s="81"/>
+      <c r="AJ17" s="81"/>
+      <c r="AK17" s="81"/>
+      <c r="AL17" s="81"/>
+      <c r="AM17" s="81"/>
+      <c r="AN17" s="81"/>
+      <c r="AO17" s="81"/>
+      <c r="AP17" s="82"/>
+      <c r="AQ17" s="86"/>
+      <c r="AR17" s="81"/>
+      <c r="AS17" s="81"/>
+      <c r="AT17" s="81"/>
+      <c r="AU17" s="81"/>
+      <c r="AV17" s="81"/>
+      <c r="AW17" s="81"/>
+      <c r="AX17" s="81"/>
+      <c r="AY17" s="81"/>
+      <c r="AZ17" s="81"/>
+      <c r="BA17" s="81"/>
+      <c r="BB17" s="81"/>
+      <c r="BC17" s="81"/>
+      <c r="BD17" s="81"/>
+      <c r="BE17" s="87"/>
     </row>
     <row r="18" spans="1:57" ht="15" customHeight="1">
-      <c r="A18" s="88"/>
-      <c r="B18" s="89"/>
-      <c r="C18" s="89"/>
-      <c r="D18" s="89"/>
-      <c r="E18" s="89"/>
-      <c r="F18" s="89"/>
-      <c r="G18" s="90"/>
-      <c r="H18" s="62"/>
-      <c r="I18" s="64"/>
-      <c r="J18" s="64"/>
-      <c r="K18" s="64"/>
-      <c r="L18" s="64"/>
-      <c r="M18" s="64"/>
-      <c r="N18" s="65"/>
-      <c r="O18" s="62"/>
-      <c r="P18" s="60"/>
-      <c r="Q18" s="60"/>
-      <c r="R18" s="60"/>
-      <c r="S18" s="60"/>
-      <c r="T18" s="60"/>
-      <c r="U18" s="60"/>
-      <c r="V18" s="60"/>
-      <c r="W18" s="60"/>
-      <c r="X18" s="60"/>
-      <c r="Y18" s="60"/>
-      <c r="Z18" s="60"/>
-      <c r="AA18" s="60"/>
-      <c r="AB18" s="60"/>
-      <c r="AC18" s="60"/>
-      <c r="AD18" s="60"/>
-      <c r="AE18" s="60"/>
-      <c r="AF18" s="60"/>
-      <c r="AG18" s="60"/>
-      <c r="AH18" s="60"/>
-      <c r="AI18" s="60"/>
-      <c r="AJ18" s="60"/>
-      <c r="AK18" s="60"/>
-      <c r="AL18" s="60"/>
-      <c r="AM18" s="60"/>
-      <c r="AN18" s="60"/>
-      <c r="AO18" s="60"/>
-      <c r="AP18" s="63"/>
-      <c r="AQ18" s="59"/>
-      <c r="AR18" s="60"/>
-      <c r="AS18" s="60"/>
-      <c r="AT18" s="60"/>
-      <c r="AU18" s="60"/>
-      <c r="AV18" s="60"/>
-      <c r="AW18" s="60"/>
-      <c r="AX18" s="60"/>
-      <c r="AY18" s="60"/>
-      <c r="AZ18" s="60"/>
-      <c r="BA18" s="60"/>
-      <c r="BB18" s="60"/>
-      <c r="BC18" s="60"/>
-      <c r="BD18" s="60"/>
-      <c r="BE18" s="61"/>
+      <c r="A18" s="70"/>
+      <c r="B18" s="71"/>
+      <c r="C18" s="71"/>
+      <c r="D18" s="71"/>
+      <c r="E18" s="71"/>
+      <c r="F18" s="71"/>
+      <c r="G18" s="72"/>
+      <c r="H18" s="78"/>
+      <c r="I18" s="79"/>
+      <c r="J18" s="79"/>
+      <c r="K18" s="79"/>
+      <c r="L18" s="79"/>
+      <c r="M18" s="79"/>
+      <c r="N18" s="80"/>
+      <c r="O18" s="78"/>
+      <c r="P18" s="81"/>
+      <c r="Q18" s="81"/>
+      <c r="R18" s="81"/>
+      <c r="S18" s="81"/>
+      <c r="T18" s="81"/>
+      <c r="U18" s="81"/>
+      <c r="V18" s="81"/>
+      <c r="W18" s="81"/>
+      <c r="X18" s="81"/>
+      <c r="Y18" s="81"/>
+      <c r="Z18" s="81"/>
+      <c r="AA18" s="81"/>
+      <c r="AB18" s="81"/>
+      <c r="AC18" s="81"/>
+      <c r="AD18" s="81"/>
+      <c r="AE18" s="81"/>
+      <c r="AF18" s="81"/>
+      <c r="AG18" s="81"/>
+      <c r="AH18" s="81"/>
+      <c r="AI18" s="81"/>
+      <c r="AJ18" s="81"/>
+      <c r="AK18" s="81"/>
+      <c r="AL18" s="81"/>
+      <c r="AM18" s="81"/>
+      <c r="AN18" s="81"/>
+      <c r="AO18" s="81"/>
+      <c r="AP18" s="82"/>
+      <c r="AQ18" s="86"/>
+      <c r="AR18" s="81"/>
+      <c r="AS18" s="81"/>
+      <c r="AT18" s="81"/>
+      <c r="AU18" s="81"/>
+      <c r="AV18" s="81"/>
+      <c r="AW18" s="81"/>
+      <c r="AX18" s="81"/>
+      <c r="AY18" s="81"/>
+      <c r="AZ18" s="81"/>
+      <c r="BA18" s="81"/>
+      <c r="BB18" s="81"/>
+      <c r="BC18" s="81"/>
+      <c r="BD18" s="81"/>
+      <c r="BE18" s="87"/>
     </row>
     <row r="19" spans="1:57" ht="15" customHeight="1">
-      <c r="A19" s="88"/>
-      <c r="B19" s="89"/>
-      <c r="C19" s="89"/>
-      <c r="D19" s="89"/>
-      <c r="E19" s="89"/>
-      <c r="F19" s="89"/>
-      <c r="G19" s="90"/>
-      <c r="H19" s="62"/>
-      <c r="I19" s="64"/>
-      <c r="J19" s="64"/>
-      <c r="K19" s="64"/>
-      <c r="L19" s="64"/>
-      <c r="M19" s="64"/>
-      <c r="N19" s="65"/>
-      <c r="O19" s="62"/>
-      <c r="P19" s="60"/>
-      <c r="Q19" s="60"/>
-      <c r="R19" s="60"/>
-      <c r="S19" s="60"/>
-      <c r="T19" s="60"/>
-      <c r="U19" s="60"/>
-      <c r="V19" s="60"/>
-      <c r="W19" s="60"/>
-      <c r="X19" s="60"/>
-      <c r="Y19" s="60"/>
-      <c r="Z19" s="60"/>
-      <c r="AA19" s="60"/>
-      <c r="AB19" s="60"/>
-      <c r="AC19" s="60"/>
-      <c r="AD19" s="60"/>
-      <c r="AE19" s="60"/>
-      <c r="AF19" s="60"/>
-      <c r="AG19" s="60"/>
-      <c r="AH19" s="60"/>
-      <c r="AI19" s="60"/>
-      <c r="AJ19" s="60"/>
-      <c r="AK19" s="60"/>
-      <c r="AL19" s="60"/>
-      <c r="AM19" s="60"/>
-      <c r="AN19" s="60"/>
-      <c r="AO19" s="60"/>
-      <c r="AP19" s="63"/>
-      <c r="AQ19" s="59"/>
-      <c r="AR19" s="60"/>
-      <c r="AS19" s="60"/>
-      <c r="AT19" s="60"/>
-      <c r="AU19" s="60"/>
-      <c r="AV19" s="60"/>
-      <c r="AW19" s="60"/>
-      <c r="AX19" s="60"/>
-      <c r="AY19" s="60"/>
-      <c r="AZ19" s="60"/>
-      <c r="BA19" s="60"/>
-      <c r="BB19" s="60"/>
-      <c r="BC19" s="60"/>
-      <c r="BD19" s="60"/>
-      <c r="BE19" s="61"/>
+      <c r="A19" s="70"/>
+      <c r="B19" s="71"/>
+      <c r="C19" s="71"/>
+      <c r="D19" s="71"/>
+      <c r="E19" s="71"/>
+      <c r="F19" s="71"/>
+      <c r="G19" s="72"/>
+      <c r="H19" s="78"/>
+      <c r="I19" s="79"/>
+      <c r="J19" s="79"/>
+      <c r="K19" s="79"/>
+      <c r="L19" s="79"/>
+      <c r="M19" s="79"/>
+      <c r="N19" s="80"/>
+      <c r="O19" s="78"/>
+      <c r="P19" s="81"/>
+      <c r="Q19" s="81"/>
+      <c r="R19" s="81"/>
+      <c r="S19" s="81"/>
+      <c r="T19" s="81"/>
+      <c r="U19" s="81"/>
+      <c r="V19" s="81"/>
+      <c r="W19" s="81"/>
+      <c r="X19" s="81"/>
+      <c r="Y19" s="81"/>
+      <c r="Z19" s="81"/>
+      <c r="AA19" s="81"/>
+      <c r="AB19" s="81"/>
+      <c r="AC19" s="81"/>
+      <c r="AD19" s="81"/>
+      <c r="AE19" s="81"/>
+      <c r="AF19" s="81"/>
+      <c r="AG19" s="81"/>
+      <c r="AH19" s="81"/>
+      <c r="AI19" s="81"/>
+      <c r="AJ19" s="81"/>
+      <c r="AK19" s="81"/>
+      <c r="AL19" s="81"/>
+      <c r="AM19" s="81"/>
+      <c r="AN19" s="81"/>
+      <c r="AO19" s="81"/>
+      <c r="AP19" s="82"/>
+      <c r="AQ19" s="86"/>
+      <c r="AR19" s="81"/>
+      <c r="AS19" s="81"/>
+      <c r="AT19" s="81"/>
+      <c r="AU19" s="81"/>
+      <c r="AV19" s="81"/>
+      <c r="AW19" s="81"/>
+      <c r="AX19" s="81"/>
+      <c r="AY19" s="81"/>
+      <c r="AZ19" s="81"/>
+      <c r="BA19" s="81"/>
+      <c r="BB19" s="81"/>
+      <c r="BC19" s="81"/>
+      <c r="BD19" s="81"/>
+      <c r="BE19" s="87"/>
     </row>
     <row r="20" spans="1:57" ht="15" customHeight="1">
-      <c r="A20" s="88"/>
-      <c r="B20" s="89"/>
-      <c r="C20" s="89"/>
-      <c r="D20" s="89"/>
-      <c r="E20" s="89"/>
-      <c r="F20" s="89"/>
-      <c r="G20" s="90"/>
-      <c r="H20" s="62"/>
-      <c r="I20" s="64"/>
-      <c r="J20" s="64"/>
-      <c r="K20" s="64"/>
-      <c r="L20" s="64"/>
-      <c r="M20" s="64"/>
-      <c r="N20" s="65"/>
-      <c r="O20" s="62"/>
-      <c r="P20" s="60"/>
-      <c r="Q20" s="60"/>
-      <c r="R20" s="60"/>
-      <c r="S20" s="60"/>
-      <c r="T20" s="60"/>
-      <c r="U20" s="60"/>
-      <c r="V20" s="60"/>
-      <c r="W20" s="60"/>
-      <c r="X20" s="60"/>
-      <c r="Y20" s="60"/>
-      <c r="Z20" s="60"/>
-      <c r="AA20" s="60"/>
-      <c r="AB20" s="60"/>
-      <c r="AC20" s="60"/>
-      <c r="AD20" s="60"/>
-      <c r="AE20" s="60"/>
-      <c r="AF20" s="60"/>
-      <c r="AG20" s="60"/>
-      <c r="AH20" s="60"/>
-      <c r="AI20" s="60"/>
-      <c r="AJ20" s="60"/>
-      <c r="AK20" s="60"/>
-      <c r="AL20" s="60"/>
-      <c r="AM20" s="60"/>
-      <c r="AN20" s="60"/>
-      <c r="AO20" s="60"/>
-      <c r="AP20" s="63"/>
-      <c r="AQ20" s="59"/>
-      <c r="AR20" s="60"/>
-      <c r="AS20" s="60"/>
-      <c r="AT20" s="60"/>
-      <c r="AU20" s="60"/>
-      <c r="AV20" s="60"/>
-      <c r="AW20" s="60"/>
-      <c r="AX20" s="60"/>
-      <c r="AY20" s="60"/>
-      <c r="AZ20" s="60"/>
-      <c r="BA20" s="60"/>
-      <c r="BB20" s="60"/>
-      <c r="BC20" s="60"/>
-      <c r="BD20" s="60"/>
-      <c r="BE20" s="61"/>
+      <c r="A20" s="70"/>
+      <c r="B20" s="71"/>
+      <c r="C20" s="71"/>
+      <c r="D20" s="71"/>
+      <c r="E20" s="71"/>
+      <c r="F20" s="71"/>
+      <c r="G20" s="72"/>
+      <c r="H20" s="78"/>
+      <c r="I20" s="79"/>
+      <c r="J20" s="79"/>
+      <c r="K20" s="79"/>
+      <c r="L20" s="79"/>
+      <c r="M20" s="79"/>
+      <c r="N20" s="80"/>
+      <c r="O20" s="78"/>
+      <c r="P20" s="81"/>
+      <c r="Q20" s="81"/>
+      <c r="R20" s="81"/>
+      <c r="S20" s="81"/>
+      <c r="T20" s="81"/>
+      <c r="U20" s="81"/>
+      <c r="V20" s="81"/>
+      <c r="W20" s="81"/>
+      <c r="X20" s="81"/>
+      <c r="Y20" s="81"/>
+      <c r="Z20" s="81"/>
+      <c r="AA20" s="81"/>
+      <c r="AB20" s="81"/>
+      <c r="AC20" s="81"/>
+      <c r="AD20" s="81"/>
+      <c r="AE20" s="81"/>
+      <c r="AF20" s="81"/>
+      <c r="AG20" s="81"/>
+      <c r="AH20" s="81"/>
+      <c r="AI20" s="81"/>
+      <c r="AJ20" s="81"/>
+      <c r="AK20" s="81"/>
+      <c r="AL20" s="81"/>
+      <c r="AM20" s="81"/>
+      <c r="AN20" s="81"/>
+      <c r="AO20" s="81"/>
+      <c r="AP20" s="82"/>
+      <c r="AQ20" s="86"/>
+      <c r="AR20" s="81"/>
+      <c r="AS20" s="81"/>
+      <c r="AT20" s="81"/>
+      <c r="AU20" s="81"/>
+      <c r="AV20" s="81"/>
+      <c r="AW20" s="81"/>
+      <c r="AX20" s="81"/>
+      <c r="AY20" s="81"/>
+      <c r="AZ20" s="81"/>
+      <c r="BA20" s="81"/>
+      <c r="BB20" s="81"/>
+      <c r="BC20" s="81"/>
+      <c r="BD20" s="81"/>
+      <c r="BE20" s="87"/>
     </row>
     <row r="21" spans="1:57" ht="15" customHeight="1">
-      <c r="A21" s="88"/>
-      <c r="B21" s="89"/>
-      <c r="C21" s="89"/>
-      <c r="D21" s="89"/>
-      <c r="E21" s="89"/>
-      <c r="F21" s="89"/>
-      <c r="G21" s="90"/>
-      <c r="H21" s="62"/>
-      <c r="I21" s="64"/>
-      <c r="J21" s="64"/>
-      <c r="K21" s="64"/>
-      <c r="L21" s="64"/>
-      <c r="M21" s="64"/>
-      <c r="N21" s="65"/>
-      <c r="O21" s="62"/>
-      <c r="P21" s="60"/>
-      <c r="Q21" s="60"/>
-      <c r="R21" s="60"/>
-      <c r="S21" s="60"/>
-      <c r="T21" s="60"/>
-      <c r="U21" s="60"/>
-      <c r="V21" s="60"/>
-      <c r="W21" s="60"/>
-      <c r="X21" s="60"/>
-      <c r="Y21" s="60"/>
-      <c r="Z21" s="60"/>
-      <c r="AA21" s="60"/>
-      <c r="AB21" s="60"/>
-      <c r="AC21" s="60"/>
-      <c r="AD21" s="60"/>
-      <c r="AE21" s="60"/>
-      <c r="AF21" s="60"/>
-      <c r="AG21" s="60"/>
-      <c r="AH21" s="60"/>
-      <c r="AI21" s="60"/>
-      <c r="AJ21" s="60"/>
-      <c r="AK21" s="60"/>
-      <c r="AL21" s="60"/>
-      <c r="AM21" s="60"/>
-      <c r="AN21" s="60"/>
-      <c r="AO21" s="60"/>
-      <c r="AP21" s="63"/>
-      <c r="AQ21" s="59"/>
-      <c r="AR21" s="60"/>
-      <c r="AS21" s="60"/>
-      <c r="AT21" s="60"/>
-      <c r="AU21" s="60"/>
-      <c r="AV21" s="60"/>
-      <c r="AW21" s="60"/>
-      <c r="AX21" s="60"/>
-      <c r="AY21" s="60"/>
-      <c r="AZ21" s="60"/>
-      <c r="BA21" s="60"/>
-      <c r="BB21" s="60"/>
-      <c r="BC21" s="60"/>
-      <c r="BD21" s="60"/>
-      <c r="BE21" s="61"/>
+      <c r="A21" s="70"/>
+      <c r="B21" s="71"/>
+      <c r="C21" s="71"/>
+      <c r="D21" s="71"/>
+      <c r="E21" s="71"/>
+      <c r="F21" s="71"/>
+      <c r="G21" s="72"/>
+      <c r="H21" s="78"/>
+      <c r="I21" s="79"/>
+      <c r="J21" s="79"/>
+      <c r="K21" s="79"/>
+      <c r="L21" s="79"/>
+      <c r="M21" s="79"/>
+      <c r="N21" s="80"/>
+      <c r="O21" s="78"/>
+      <c r="P21" s="81"/>
+      <c r="Q21" s="81"/>
+      <c r="R21" s="81"/>
+      <c r="S21" s="81"/>
+      <c r="T21" s="81"/>
+      <c r="U21" s="81"/>
+      <c r="V21" s="81"/>
+      <c r="W21" s="81"/>
+      <c r="X21" s="81"/>
+      <c r="Y21" s="81"/>
+      <c r="Z21" s="81"/>
+      <c r="AA21" s="81"/>
+      <c r="AB21" s="81"/>
+      <c r="AC21" s="81"/>
+      <c r="AD21" s="81"/>
+      <c r="AE21" s="81"/>
+      <c r="AF21" s="81"/>
+      <c r="AG21" s="81"/>
+      <c r="AH21" s="81"/>
+      <c r="AI21" s="81"/>
+      <c r="AJ21" s="81"/>
+      <c r="AK21" s="81"/>
+      <c r="AL21" s="81"/>
+      <c r="AM21" s="81"/>
+      <c r="AN21" s="81"/>
+      <c r="AO21" s="81"/>
+      <c r="AP21" s="82"/>
+      <c r="AQ21" s="86"/>
+      <c r="AR21" s="81"/>
+      <c r="AS21" s="81"/>
+      <c r="AT21" s="81"/>
+      <c r="AU21" s="81"/>
+      <c r="AV21" s="81"/>
+      <c r="AW21" s="81"/>
+      <c r="AX21" s="81"/>
+      <c r="AY21" s="81"/>
+      <c r="AZ21" s="81"/>
+      <c r="BA21" s="81"/>
+      <c r="BB21" s="81"/>
+      <c r="BC21" s="81"/>
+      <c r="BD21" s="81"/>
+      <c r="BE21" s="87"/>
     </row>
     <row r="22" spans="1:57" ht="15" customHeight="1">
-      <c r="A22" s="88"/>
-      <c r="B22" s="89"/>
-      <c r="C22" s="89"/>
-      <c r="D22" s="89"/>
-      <c r="E22" s="89"/>
-      <c r="F22" s="89"/>
-      <c r="G22" s="90"/>
-      <c r="H22" s="62"/>
-      <c r="I22" s="64"/>
-      <c r="J22" s="64"/>
-      <c r="K22" s="64"/>
-      <c r="L22" s="64"/>
-      <c r="M22" s="64"/>
-      <c r="N22" s="65"/>
-      <c r="O22" s="62"/>
-      <c r="P22" s="60"/>
-      <c r="Q22" s="60"/>
-      <c r="R22" s="60"/>
-      <c r="S22" s="60"/>
-      <c r="T22" s="60"/>
-      <c r="U22" s="60"/>
-      <c r="V22" s="60"/>
-      <c r="W22" s="60"/>
-      <c r="X22" s="60"/>
-      <c r="Y22" s="60"/>
-      <c r="Z22" s="60"/>
-      <c r="AA22" s="60"/>
-      <c r="AB22" s="60"/>
-      <c r="AC22" s="60"/>
-      <c r="AD22" s="60"/>
-      <c r="AE22" s="60"/>
-      <c r="AF22" s="60"/>
-      <c r="AG22" s="60"/>
-      <c r="AH22" s="60"/>
-      <c r="AI22" s="60"/>
-      <c r="AJ22" s="60"/>
-      <c r="AK22" s="60"/>
-      <c r="AL22" s="60"/>
-      <c r="AM22" s="60"/>
-      <c r="AN22" s="60"/>
-      <c r="AO22" s="60"/>
-      <c r="AP22" s="63"/>
-      <c r="AQ22" s="59"/>
-      <c r="AR22" s="60"/>
-      <c r="AS22" s="60"/>
-      <c r="AT22" s="60"/>
-      <c r="AU22" s="60"/>
-      <c r="AV22" s="60"/>
-      <c r="AW22" s="60"/>
-      <c r="AX22" s="60"/>
-      <c r="AY22" s="60"/>
-      <c r="AZ22" s="60"/>
-      <c r="BA22" s="60"/>
-      <c r="BB22" s="60"/>
-      <c r="BC22" s="60"/>
-      <c r="BD22" s="60"/>
-      <c r="BE22" s="61"/>
+      <c r="A22" s="70"/>
+      <c r="B22" s="71"/>
+      <c r="C22" s="71"/>
+      <c r="D22" s="71"/>
+      <c r="E22" s="71"/>
+      <c r="F22" s="71"/>
+      <c r="G22" s="72"/>
+      <c r="H22" s="78"/>
+      <c r="I22" s="79"/>
+      <c r="J22" s="79"/>
+      <c r="K22" s="79"/>
+      <c r="L22" s="79"/>
+      <c r="M22" s="79"/>
+      <c r="N22" s="80"/>
+      <c r="O22" s="78"/>
+      <c r="P22" s="81"/>
+      <c r="Q22" s="81"/>
+      <c r="R22" s="81"/>
+      <c r="S22" s="81"/>
+      <c r="T22" s="81"/>
+      <c r="U22" s="81"/>
+      <c r="V22" s="81"/>
+      <c r="W22" s="81"/>
+      <c r="X22" s="81"/>
+      <c r="Y22" s="81"/>
+      <c r="Z22" s="81"/>
+      <c r="AA22" s="81"/>
+      <c r="AB22" s="81"/>
+      <c r="AC22" s="81"/>
+      <c r="AD22" s="81"/>
+      <c r="AE22" s="81"/>
+      <c r="AF22" s="81"/>
+      <c r="AG22" s="81"/>
+      <c r="AH22" s="81"/>
+      <c r="AI22" s="81"/>
+      <c r="AJ22" s="81"/>
+      <c r="AK22" s="81"/>
+      <c r="AL22" s="81"/>
+      <c r="AM22" s="81"/>
+      <c r="AN22" s="81"/>
+      <c r="AO22" s="81"/>
+      <c r="AP22" s="82"/>
+      <c r="AQ22" s="86"/>
+      <c r="AR22" s="81"/>
+      <c r="AS22" s="81"/>
+      <c r="AT22" s="81"/>
+      <c r="AU22" s="81"/>
+      <c r="AV22" s="81"/>
+      <c r="AW22" s="81"/>
+      <c r="AX22" s="81"/>
+      <c r="AY22" s="81"/>
+      <c r="AZ22" s="81"/>
+      <c r="BA22" s="81"/>
+      <c r="BB22" s="81"/>
+      <c r="BC22" s="81"/>
+      <c r="BD22" s="81"/>
+      <c r="BE22" s="87"/>
     </row>
     <row r="23" spans="1:57" ht="15" customHeight="1">
-      <c r="A23" s="88"/>
-      <c r="B23" s="89"/>
-      <c r="C23" s="89"/>
-      <c r="D23" s="89"/>
-      <c r="E23" s="89"/>
-      <c r="F23" s="89"/>
-      <c r="G23" s="90"/>
-      <c r="H23" s="62"/>
-      <c r="I23" s="64"/>
-      <c r="J23" s="64"/>
-      <c r="K23" s="64"/>
-      <c r="L23" s="64"/>
-      <c r="M23" s="64"/>
-      <c r="N23" s="65"/>
-      <c r="O23" s="62"/>
-      <c r="P23" s="60"/>
-      <c r="Q23" s="60"/>
-      <c r="R23" s="60"/>
-      <c r="S23" s="60"/>
-      <c r="T23" s="60"/>
-      <c r="U23" s="60"/>
-      <c r="V23" s="60"/>
-      <c r="W23" s="60"/>
-      <c r="X23" s="60"/>
-      <c r="Y23" s="60"/>
-      <c r="Z23" s="60"/>
-      <c r="AA23" s="60"/>
-      <c r="AB23" s="60"/>
-      <c r="AC23" s="60"/>
-      <c r="AD23" s="60"/>
-      <c r="AE23" s="60"/>
-      <c r="AF23" s="60"/>
-      <c r="AG23" s="60"/>
-      <c r="AH23" s="60"/>
-      <c r="AI23" s="60"/>
-      <c r="AJ23" s="60"/>
-      <c r="AK23" s="60"/>
-      <c r="AL23" s="60"/>
-      <c r="AM23" s="60"/>
-      <c r="AN23" s="60"/>
-      <c r="AO23" s="60"/>
-      <c r="AP23" s="63"/>
-      <c r="AQ23" s="59"/>
-      <c r="AR23" s="60"/>
-      <c r="AS23" s="60"/>
-      <c r="AT23" s="60"/>
-      <c r="AU23" s="60"/>
-      <c r="AV23" s="60"/>
-      <c r="AW23" s="60"/>
-      <c r="AX23" s="60"/>
-      <c r="AY23" s="60"/>
-      <c r="AZ23" s="60"/>
-      <c r="BA23" s="60"/>
-      <c r="BB23" s="60"/>
-      <c r="BC23" s="60"/>
-      <c r="BD23" s="60"/>
-      <c r="BE23" s="61"/>
+      <c r="A23" s="70"/>
+      <c r="B23" s="71"/>
+      <c r="C23" s="71"/>
+      <c r="D23" s="71"/>
+      <c r="E23" s="71"/>
+      <c r="F23" s="71"/>
+      <c r="G23" s="72"/>
+      <c r="H23" s="78"/>
+      <c r="I23" s="79"/>
+      <c r="J23" s="79"/>
+      <c r="K23" s="79"/>
+      <c r="L23" s="79"/>
+      <c r="M23" s="79"/>
+      <c r="N23" s="80"/>
+      <c r="O23" s="78"/>
+      <c r="P23" s="81"/>
+      <c r="Q23" s="81"/>
+      <c r="R23" s="81"/>
+      <c r="S23" s="81"/>
+      <c r="T23" s="81"/>
+      <c r="U23" s="81"/>
+      <c r="V23" s="81"/>
+      <c r="W23" s="81"/>
+      <c r="X23" s="81"/>
+      <c r="Y23" s="81"/>
+      <c r="Z23" s="81"/>
+      <c r="AA23" s="81"/>
+      <c r="AB23" s="81"/>
+      <c r="AC23" s="81"/>
+      <c r="AD23" s="81"/>
+      <c r="AE23" s="81"/>
+      <c r="AF23" s="81"/>
+      <c r="AG23" s="81"/>
+      <c r="AH23" s="81"/>
+      <c r="AI23" s="81"/>
+      <c r="AJ23" s="81"/>
+      <c r="AK23" s="81"/>
+      <c r="AL23" s="81"/>
+      <c r="AM23" s="81"/>
+      <c r="AN23" s="81"/>
+      <c r="AO23" s="81"/>
+      <c r="AP23" s="82"/>
+      <c r="AQ23" s="86"/>
+      <c r="AR23" s="81"/>
+      <c r="AS23" s="81"/>
+      <c r="AT23" s="81"/>
+      <c r="AU23" s="81"/>
+      <c r="AV23" s="81"/>
+      <c r="AW23" s="81"/>
+      <c r="AX23" s="81"/>
+      <c r="AY23" s="81"/>
+      <c r="AZ23" s="81"/>
+      <c r="BA23" s="81"/>
+      <c r="BB23" s="81"/>
+      <c r="BC23" s="81"/>
+      <c r="BD23" s="81"/>
+      <c r="BE23" s="87"/>
     </row>
     <row r="24" spans="1:57" ht="15" customHeight="1">
-      <c r="A24" s="88"/>
-      <c r="B24" s="89"/>
-      <c r="C24" s="89"/>
-      <c r="D24" s="89"/>
-      <c r="E24" s="89"/>
-      <c r="F24" s="89"/>
-      <c r="G24" s="90"/>
-      <c r="H24" s="62"/>
-      <c r="I24" s="64"/>
-      <c r="J24" s="64"/>
-      <c r="K24" s="64"/>
-      <c r="L24" s="64"/>
-      <c r="M24" s="64"/>
-      <c r="N24" s="65"/>
-      <c r="O24" s="62"/>
-      <c r="P24" s="60"/>
-      <c r="Q24" s="60"/>
-      <c r="R24" s="60"/>
-      <c r="S24" s="60"/>
-      <c r="T24" s="60"/>
-      <c r="U24" s="60"/>
-      <c r="V24" s="60"/>
-      <c r="W24" s="60"/>
-      <c r="X24" s="60"/>
-      <c r="Y24" s="60"/>
-      <c r="Z24" s="60"/>
-      <c r="AA24" s="60"/>
-      <c r="AB24" s="60"/>
-      <c r="AC24" s="60"/>
-      <c r="AD24" s="60"/>
-      <c r="AE24" s="60"/>
-      <c r="AF24" s="60"/>
-      <c r="AG24" s="60"/>
-      <c r="AH24" s="60"/>
-      <c r="AI24" s="60"/>
-      <c r="AJ24" s="60"/>
-      <c r="AK24" s="60"/>
-      <c r="AL24" s="60"/>
-      <c r="AM24" s="60"/>
-      <c r="AN24" s="60"/>
-      <c r="AO24" s="60"/>
-      <c r="AP24" s="63"/>
-      <c r="AQ24" s="59"/>
-      <c r="AR24" s="60"/>
-      <c r="AS24" s="60"/>
-      <c r="AT24" s="60"/>
-      <c r="AU24" s="60"/>
-      <c r="AV24" s="60"/>
-      <c r="AW24" s="60"/>
-      <c r="AX24" s="60"/>
-      <c r="AY24" s="60"/>
-      <c r="AZ24" s="60"/>
-      <c r="BA24" s="60"/>
-      <c r="BB24" s="60"/>
-      <c r="BC24" s="60"/>
-      <c r="BD24" s="60"/>
-      <c r="BE24" s="61"/>
+      <c r="A24" s="70"/>
+      <c r="B24" s="71"/>
+      <c r="C24" s="71"/>
+      <c r="D24" s="71"/>
+      <c r="E24" s="71"/>
+      <c r="F24" s="71"/>
+      <c r="G24" s="72"/>
+      <c r="H24" s="78"/>
+      <c r="I24" s="79"/>
+      <c r="J24" s="79"/>
+      <c r="K24" s="79"/>
+      <c r="L24" s="79"/>
+      <c r="M24" s="79"/>
+      <c r="N24" s="80"/>
+      <c r="O24" s="78"/>
+      <c r="P24" s="81"/>
+      <c r="Q24" s="81"/>
+      <c r="R24" s="81"/>
+      <c r="S24" s="81"/>
+      <c r="T24" s="81"/>
+      <c r="U24" s="81"/>
+      <c r="V24" s="81"/>
+      <c r="W24" s="81"/>
+      <c r="X24" s="81"/>
+      <c r="Y24" s="81"/>
+      <c r="Z24" s="81"/>
+      <c r="AA24" s="81"/>
+      <c r="AB24" s="81"/>
+      <c r="AC24" s="81"/>
+      <c r="AD24" s="81"/>
+      <c r="AE24" s="81"/>
+      <c r="AF24" s="81"/>
+      <c r="AG24" s="81"/>
+      <c r="AH24" s="81"/>
+      <c r="AI24" s="81"/>
+      <c r="AJ24" s="81"/>
+      <c r="AK24" s="81"/>
+      <c r="AL24" s="81"/>
+      <c r="AM24" s="81"/>
+      <c r="AN24" s="81"/>
+      <c r="AO24" s="81"/>
+      <c r="AP24" s="82"/>
+      <c r="AQ24" s="86"/>
+      <c r="AR24" s="81"/>
+      <c r="AS24" s="81"/>
+      <c r="AT24" s="81"/>
+      <c r="AU24" s="81"/>
+      <c r="AV24" s="81"/>
+      <c r="AW24" s="81"/>
+      <c r="AX24" s="81"/>
+      <c r="AY24" s="81"/>
+      <c r="AZ24" s="81"/>
+      <c r="BA24" s="81"/>
+      <c r="BB24" s="81"/>
+      <c r="BC24" s="81"/>
+      <c r="BD24" s="81"/>
+      <c r="BE24" s="87"/>
     </row>
     <row r="25" spans="1:57" ht="15" customHeight="1">
-      <c r="A25" s="88"/>
-      <c r="B25" s="89"/>
-      <c r="C25" s="89"/>
-      <c r="D25" s="89"/>
-      <c r="E25" s="89"/>
-      <c r="F25" s="89"/>
-      <c r="G25" s="90"/>
-      <c r="H25" s="62"/>
-      <c r="I25" s="64"/>
-      <c r="J25" s="64"/>
-      <c r="K25" s="64"/>
-      <c r="L25" s="64"/>
-      <c r="M25" s="64"/>
-      <c r="N25" s="65"/>
-      <c r="O25" s="62"/>
-      <c r="P25" s="60"/>
-      <c r="Q25" s="60"/>
-      <c r="R25" s="60"/>
-      <c r="S25" s="60"/>
-      <c r="T25" s="60"/>
-      <c r="U25" s="60"/>
-      <c r="V25" s="60"/>
-      <c r="W25" s="60"/>
-      <c r="X25" s="60"/>
-      <c r="Y25" s="60"/>
-      <c r="Z25" s="60"/>
-      <c r="AA25" s="60"/>
-      <c r="AB25" s="60"/>
-      <c r="AC25" s="60"/>
-      <c r="AD25" s="60"/>
-      <c r="AE25" s="60"/>
-      <c r="AF25" s="60"/>
-      <c r="AG25" s="60"/>
-      <c r="AH25" s="60"/>
-      <c r="AI25" s="60"/>
-      <c r="AJ25" s="60"/>
-      <c r="AK25" s="60"/>
-      <c r="AL25" s="60"/>
-      <c r="AM25" s="60"/>
-      <c r="AN25" s="60"/>
-      <c r="AO25" s="60"/>
-      <c r="AP25" s="63"/>
-      <c r="AQ25" s="59"/>
-      <c r="AR25" s="60"/>
-      <c r="AS25" s="60"/>
-      <c r="AT25" s="60"/>
-      <c r="AU25" s="60"/>
-      <c r="AV25" s="60"/>
-      <c r="AW25" s="60"/>
-      <c r="AX25" s="60"/>
-      <c r="AY25" s="60"/>
-      <c r="AZ25" s="60"/>
-      <c r="BA25" s="60"/>
-      <c r="BB25" s="60"/>
-      <c r="BC25" s="60"/>
-      <c r="BD25" s="60"/>
-      <c r="BE25" s="61"/>
+      <c r="A25" s="70"/>
+      <c r="B25" s="71"/>
+      <c r="C25" s="71"/>
+      <c r="D25" s="71"/>
+      <c r="E25" s="71"/>
+      <c r="F25" s="71"/>
+      <c r="G25" s="72"/>
+      <c r="H25" s="78"/>
+      <c r="I25" s="79"/>
+      <c r="J25" s="79"/>
+      <c r="K25" s="79"/>
+      <c r="L25" s="79"/>
+      <c r="M25" s="79"/>
+      <c r="N25" s="80"/>
+      <c r="O25" s="78"/>
+      <c r="P25" s="81"/>
+      <c r="Q25" s="81"/>
+      <c r="R25" s="81"/>
+      <c r="S25" s="81"/>
+      <c r="T25" s="81"/>
+      <c r="U25" s="81"/>
+      <c r="V25" s="81"/>
+      <c r="W25" s="81"/>
+      <c r="X25" s="81"/>
+      <c r="Y25" s="81"/>
+      <c r="Z25" s="81"/>
+      <c r="AA25" s="81"/>
+      <c r="AB25" s="81"/>
+      <c r="AC25" s="81"/>
+      <c r="AD25" s="81"/>
+      <c r="AE25" s="81"/>
+      <c r="AF25" s="81"/>
+      <c r="AG25" s="81"/>
+      <c r="AH25" s="81"/>
+      <c r="AI25" s="81"/>
+      <c r="AJ25" s="81"/>
+      <c r="AK25" s="81"/>
+      <c r="AL25" s="81"/>
+      <c r="AM25" s="81"/>
+      <c r="AN25" s="81"/>
+      <c r="AO25" s="81"/>
+      <c r="AP25" s="82"/>
+      <c r="AQ25" s="86"/>
+      <c r="AR25" s="81"/>
+      <c r="AS25" s="81"/>
+      <c r="AT25" s="81"/>
+      <c r="AU25" s="81"/>
+      <c r="AV25" s="81"/>
+      <c r="AW25" s="81"/>
+      <c r="AX25" s="81"/>
+      <c r="AY25" s="81"/>
+      <c r="AZ25" s="81"/>
+      <c r="BA25" s="81"/>
+      <c r="BB25" s="81"/>
+      <c r="BC25" s="81"/>
+      <c r="BD25" s="81"/>
+      <c r="BE25" s="87"/>
     </row>
     <row r="26" spans="1:57" ht="15" customHeight="1">
-      <c r="A26" s="88"/>
-      <c r="B26" s="89"/>
-      <c r="C26" s="89"/>
-      <c r="D26" s="89"/>
-      <c r="E26" s="89"/>
-      <c r="F26" s="89"/>
-      <c r="G26" s="90"/>
-      <c r="H26" s="62"/>
-      <c r="I26" s="64"/>
-      <c r="J26" s="64"/>
-      <c r="K26" s="64"/>
-      <c r="L26" s="64"/>
-      <c r="M26" s="64"/>
-      <c r="N26" s="65"/>
-      <c r="O26" s="62"/>
-      <c r="P26" s="60"/>
-      <c r="Q26" s="60"/>
-      <c r="R26" s="60"/>
-      <c r="S26" s="60"/>
-      <c r="T26" s="60"/>
-      <c r="U26" s="60"/>
-      <c r="V26" s="60"/>
-      <c r="W26" s="60"/>
-      <c r="X26" s="60"/>
-      <c r="Y26" s="60"/>
-      <c r="Z26" s="60"/>
-      <c r="AA26" s="60"/>
-      <c r="AB26" s="60"/>
-      <c r="AC26" s="60"/>
-      <c r="AD26" s="60"/>
-      <c r="AE26" s="60"/>
-      <c r="AF26" s="60"/>
-      <c r="AG26" s="60"/>
-      <c r="AH26" s="60"/>
-      <c r="AI26" s="60"/>
-      <c r="AJ26" s="60"/>
-      <c r="AK26" s="60"/>
-      <c r="AL26" s="60"/>
-      <c r="AM26" s="60"/>
-      <c r="AN26" s="60"/>
-      <c r="AO26" s="60"/>
-      <c r="AP26" s="63"/>
-      <c r="AQ26" s="59"/>
-      <c r="AR26" s="60"/>
-      <c r="AS26" s="60"/>
-      <c r="AT26" s="60"/>
-      <c r="AU26" s="60"/>
-      <c r="AV26" s="60"/>
-      <c r="AW26" s="60"/>
-      <c r="AX26" s="60"/>
-      <c r="AY26" s="60"/>
-      <c r="AZ26" s="60"/>
-      <c r="BA26" s="60"/>
-      <c r="BB26" s="60"/>
-      <c r="BC26" s="60"/>
-      <c r="BD26" s="60"/>
-      <c r="BE26" s="61"/>
+      <c r="A26" s="70"/>
+      <c r="B26" s="71"/>
+      <c r="C26" s="71"/>
+      <c r="D26" s="71"/>
+      <c r="E26" s="71"/>
+      <c r="F26" s="71"/>
+      <c r="G26" s="72"/>
+      <c r="H26" s="78"/>
+      <c r="I26" s="79"/>
+      <c r="J26" s="79"/>
+      <c r="K26" s="79"/>
+      <c r="L26" s="79"/>
+      <c r="M26" s="79"/>
+      <c r="N26" s="80"/>
+      <c r="O26" s="78"/>
+      <c r="P26" s="81"/>
+      <c r="Q26" s="81"/>
+      <c r="R26" s="81"/>
+      <c r="S26" s="81"/>
+      <c r="T26" s="81"/>
+      <c r="U26" s="81"/>
+      <c r="V26" s="81"/>
+      <c r="W26" s="81"/>
+      <c r="X26" s="81"/>
+      <c r="Y26" s="81"/>
+      <c r="Z26" s="81"/>
+      <c r="AA26" s="81"/>
+      <c r="AB26" s="81"/>
+      <c r="AC26" s="81"/>
+      <c r="AD26" s="81"/>
+      <c r="AE26" s="81"/>
+      <c r="AF26" s="81"/>
+      <c r="AG26" s="81"/>
+      <c r="AH26" s="81"/>
+      <c r="AI26" s="81"/>
+      <c r="AJ26" s="81"/>
+      <c r="AK26" s="81"/>
+      <c r="AL26" s="81"/>
+      <c r="AM26" s="81"/>
+      <c r="AN26" s="81"/>
+      <c r="AO26" s="81"/>
+      <c r="AP26" s="82"/>
+      <c r="AQ26" s="86"/>
+      <c r="AR26" s="81"/>
+      <c r="AS26" s="81"/>
+      <c r="AT26" s="81"/>
+      <c r="AU26" s="81"/>
+      <c r="AV26" s="81"/>
+      <c r="AW26" s="81"/>
+      <c r="AX26" s="81"/>
+      <c r="AY26" s="81"/>
+      <c r="AZ26" s="81"/>
+      <c r="BA26" s="81"/>
+      <c r="BB26" s="81"/>
+      <c r="BC26" s="81"/>
+      <c r="BD26" s="81"/>
+      <c r="BE26" s="87"/>
     </row>
     <row r="27" spans="1:57" ht="15" customHeight="1">
-      <c r="A27" s="88"/>
-      <c r="B27" s="89"/>
-      <c r="C27" s="89"/>
-      <c r="D27" s="89"/>
-      <c r="E27" s="89"/>
-      <c r="F27" s="89"/>
-      <c r="G27" s="90"/>
-      <c r="H27" s="62"/>
-      <c r="I27" s="64"/>
-      <c r="J27" s="64"/>
-      <c r="K27" s="64"/>
-      <c r="L27" s="64"/>
-      <c r="M27" s="64"/>
-      <c r="N27" s="65"/>
-      <c r="O27" s="62"/>
-      <c r="P27" s="60"/>
-      <c r="Q27" s="60"/>
-      <c r="R27" s="60"/>
-      <c r="S27" s="60"/>
-      <c r="T27" s="60"/>
-      <c r="U27" s="60"/>
-      <c r="V27" s="60"/>
-      <c r="W27" s="60"/>
-      <c r="X27" s="60"/>
-      <c r="Y27" s="60"/>
-      <c r="Z27" s="60"/>
-      <c r="AA27" s="60"/>
-      <c r="AB27" s="60"/>
-      <c r="AC27" s="60"/>
-      <c r="AD27" s="60"/>
-      <c r="AE27" s="60"/>
-      <c r="AF27" s="60"/>
-      <c r="AG27" s="60"/>
-      <c r="AH27" s="60"/>
-      <c r="AI27" s="60"/>
-      <c r="AJ27" s="60"/>
-      <c r="AK27" s="60"/>
-      <c r="AL27" s="60"/>
-      <c r="AM27" s="60"/>
-      <c r="AN27" s="60"/>
-      <c r="AO27" s="60"/>
-      <c r="AP27" s="63"/>
-      <c r="AQ27" s="59"/>
-      <c r="AR27" s="60"/>
-      <c r="AS27" s="60"/>
-      <c r="AT27" s="60"/>
-      <c r="AU27" s="60"/>
-      <c r="AV27" s="60"/>
-      <c r="AW27" s="60"/>
-      <c r="AX27" s="60"/>
-      <c r="AY27" s="60"/>
-      <c r="AZ27" s="60"/>
-      <c r="BA27" s="60"/>
-      <c r="BB27" s="60"/>
-      <c r="BC27" s="60"/>
-      <c r="BD27" s="60"/>
-      <c r="BE27" s="61"/>
+      <c r="A27" s="70"/>
+      <c r="B27" s="71"/>
+      <c r="C27" s="71"/>
+      <c r="D27" s="71"/>
+      <c r="E27" s="71"/>
+      <c r="F27" s="71"/>
+      <c r="G27" s="72"/>
+      <c r="H27" s="78"/>
+      <c r="I27" s="79"/>
+      <c r="J27" s="79"/>
+      <c r="K27" s="79"/>
+      <c r="L27" s="79"/>
+      <c r="M27" s="79"/>
+      <c r="N27" s="80"/>
+      <c r="O27" s="78"/>
+      <c r="P27" s="81"/>
+      <c r="Q27" s="81"/>
+      <c r="R27" s="81"/>
+      <c r="S27" s="81"/>
+      <c r="T27" s="81"/>
+      <c r="U27" s="81"/>
+      <c r="V27" s="81"/>
+      <c r="W27" s="81"/>
+      <c r="X27" s="81"/>
+      <c r="Y27" s="81"/>
+      <c r="Z27" s="81"/>
+      <c r="AA27" s="81"/>
+      <c r="AB27" s="81"/>
+      <c r="AC27" s="81"/>
+      <c r="AD27" s="81"/>
+      <c r="AE27" s="81"/>
+      <c r="AF27" s="81"/>
+      <c r="AG27" s="81"/>
+      <c r="AH27" s="81"/>
+      <c r="AI27" s="81"/>
+      <c r="AJ27" s="81"/>
+      <c r="AK27" s="81"/>
+      <c r="AL27" s="81"/>
+      <c r="AM27" s="81"/>
+      <c r="AN27" s="81"/>
+      <c r="AO27" s="81"/>
+      <c r="AP27" s="82"/>
+      <c r="AQ27" s="86"/>
+      <c r="AR27" s="81"/>
+      <c r="AS27" s="81"/>
+      <c r="AT27" s="81"/>
+      <c r="AU27" s="81"/>
+      <c r="AV27" s="81"/>
+      <c r="AW27" s="81"/>
+      <c r="AX27" s="81"/>
+      <c r="AY27" s="81"/>
+      <c r="AZ27" s="81"/>
+      <c r="BA27" s="81"/>
+      <c r="BB27" s="81"/>
+      <c r="BC27" s="81"/>
+      <c r="BD27" s="81"/>
+      <c r="BE27" s="87"/>
     </row>
     <row r="28" spans="1:57" ht="15" customHeight="1">
-      <c r="A28" s="88"/>
-      <c r="B28" s="89"/>
-      <c r="C28" s="89"/>
-      <c r="D28" s="89"/>
-      <c r="E28" s="89"/>
-      <c r="F28" s="89"/>
-      <c r="G28" s="90"/>
-      <c r="H28" s="62"/>
-      <c r="I28" s="64"/>
-      <c r="J28" s="64"/>
-      <c r="K28" s="64"/>
-      <c r="L28" s="64"/>
-      <c r="M28" s="64"/>
-      <c r="N28" s="65"/>
-      <c r="O28" s="62"/>
-      <c r="P28" s="60"/>
-      <c r="Q28" s="60"/>
-      <c r="R28" s="60"/>
-      <c r="S28" s="60"/>
-      <c r="T28" s="60"/>
-      <c r="U28" s="60"/>
-      <c r="V28" s="60"/>
-      <c r="W28" s="60"/>
-      <c r="X28" s="60"/>
-      <c r="Y28" s="60"/>
-      <c r="Z28" s="60"/>
-      <c r="AA28" s="60"/>
-      <c r="AB28" s="60"/>
-      <c r="AC28" s="60"/>
-      <c r="AD28" s="60"/>
-      <c r="AE28" s="60"/>
-      <c r="AF28" s="60"/>
-      <c r="AG28" s="60"/>
-      <c r="AH28" s="60"/>
-      <c r="AI28" s="60"/>
-      <c r="AJ28" s="60"/>
-      <c r="AK28" s="60"/>
-      <c r="AL28" s="60"/>
-      <c r="AM28" s="60"/>
-      <c r="AN28" s="60"/>
-      <c r="AO28" s="60"/>
-      <c r="AP28" s="63"/>
-      <c r="AQ28" s="59"/>
-      <c r="AR28" s="60"/>
-      <c r="AS28" s="60"/>
-      <c r="AT28" s="60"/>
-      <c r="AU28" s="60"/>
-      <c r="AV28" s="60"/>
-      <c r="AW28" s="60"/>
-      <c r="AX28" s="60"/>
-      <c r="AY28" s="60"/>
-      <c r="AZ28" s="60"/>
-      <c r="BA28" s="60"/>
-      <c r="BB28" s="60"/>
-      <c r="BC28" s="60"/>
-      <c r="BD28" s="60"/>
-      <c r="BE28" s="61"/>
+      <c r="A28" s="70"/>
+      <c r="B28" s="71"/>
+      <c r="C28" s="71"/>
+      <c r="D28" s="71"/>
+      <c r="E28" s="71"/>
+      <c r="F28" s="71"/>
+      <c r="G28" s="72"/>
+      <c r="H28" s="78"/>
+      <c r="I28" s="79"/>
+      <c r="J28" s="79"/>
+      <c r="K28" s="79"/>
+      <c r="L28" s="79"/>
+      <c r="M28" s="79"/>
+      <c r="N28" s="80"/>
+      <c r="O28" s="78"/>
+      <c r="P28" s="81"/>
+      <c r="Q28" s="81"/>
+      <c r="R28" s="81"/>
+      <c r="S28" s="81"/>
+      <c r="T28" s="81"/>
+      <c r="U28" s="81"/>
+      <c r="V28" s="81"/>
+      <c r="W28" s="81"/>
+      <c r="X28" s="81"/>
+      <c r="Y28" s="81"/>
+      <c r="Z28" s="81"/>
+      <c r="AA28" s="81"/>
+      <c r="AB28" s="81"/>
+      <c r="AC28" s="81"/>
+      <c r="AD28" s="81"/>
+      <c r="AE28" s="81"/>
+      <c r="AF28" s="81"/>
+      <c r="AG28" s="81"/>
+      <c r="AH28" s="81"/>
+      <c r="AI28" s="81"/>
+      <c r="AJ28" s="81"/>
+      <c r="AK28" s="81"/>
+      <c r="AL28" s="81"/>
+      <c r="AM28" s="81"/>
+      <c r="AN28" s="81"/>
+      <c r="AO28" s="81"/>
+      <c r="AP28" s="82"/>
+      <c r="AQ28" s="86"/>
+      <c r="AR28" s="81"/>
+      <c r="AS28" s="81"/>
+      <c r="AT28" s="81"/>
+      <c r="AU28" s="81"/>
+      <c r="AV28" s="81"/>
+      <c r="AW28" s="81"/>
+      <c r="AX28" s="81"/>
+      <c r="AY28" s="81"/>
+      <c r="AZ28" s="81"/>
+      <c r="BA28" s="81"/>
+      <c r="BB28" s="81"/>
+      <c r="BC28" s="81"/>
+      <c r="BD28" s="81"/>
+      <c r="BE28" s="87"/>
     </row>
     <row r="29" spans="1:57" ht="15" customHeight="1">
-      <c r="A29" s="88"/>
-      <c r="B29" s="89"/>
-      <c r="C29" s="89"/>
-      <c r="D29" s="89"/>
-      <c r="E29" s="89"/>
-      <c r="F29" s="89"/>
-      <c r="G29" s="90"/>
-      <c r="H29" s="62"/>
-      <c r="I29" s="64"/>
-      <c r="J29" s="64"/>
-      <c r="K29" s="64"/>
-      <c r="L29" s="64"/>
-      <c r="M29" s="64"/>
-      <c r="N29" s="65"/>
-      <c r="O29" s="62"/>
-      <c r="P29" s="60"/>
-      <c r="Q29" s="60"/>
-      <c r="R29" s="60"/>
-      <c r="S29" s="60"/>
-      <c r="T29" s="60"/>
-      <c r="U29" s="60"/>
-      <c r="V29" s="60"/>
-      <c r="W29" s="60"/>
-      <c r="X29" s="60"/>
-      <c r="Y29" s="60"/>
-      <c r="Z29" s="60"/>
-      <c r="AA29" s="60"/>
-      <c r="AB29" s="60"/>
-      <c r="AC29" s="60"/>
-      <c r="AD29" s="60"/>
-      <c r="AE29" s="60"/>
-      <c r="AF29" s="60"/>
-      <c r="AG29" s="60"/>
-      <c r="AH29" s="60"/>
-      <c r="AI29" s="60"/>
-      <c r="AJ29" s="60"/>
-      <c r="AK29" s="60"/>
-      <c r="AL29" s="60"/>
-      <c r="AM29" s="60"/>
-      <c r="AN29" s="60"/>
-      <c r="AO29" s="60"/>
-      <c r="AP29" s="63"/>
-      <c r="AQ29" s="59"/>
-      <c r="AR29" s="60"/>
-      <c r="AS29" s="60"/>
-      <c r="AT29" s="60"/>
-      <c r="AU29" s="60"/>
-      <c r="AV29" s="60"/>
-      <c r="AW29" s="60"/>
-      <c r="AX29" s="60"/>
-      <c r="AY29" s="60"/>
-      <c r="AZ29" s="60"/>
-      <c r="BA29" s="60"/>
-      <c r="BB29" s="60"/>
-      <c r="BC29" s="60"/>
-      <c r="BD29" s="60"/>
-      <c r="BE29" s="61"/>
+      <c r="A29" s="70"/>
+      <c r="B29" s="71"/>
+      <c r="C29" s="71"/>
+      <c r="D29" s="71"/>
+      <c r="E29" s="71"/>
+      <c r="F29" s="71"/>
+      <c r="G29" s="72"/>
+      <c r="H29" s="78"/>
+      <c r="I29" s="79"/>
+      <c r="J29" s="79"/>
+      <c r="K29" s="79"/>
+      <c r="L29" s="79"/>
+      <c r="M29" s="79"/>
+      <c r="N29" s="80"/>
+      <c r="O29" s="78"/>
+      <c r="P29" s="81"/>
+      <c r="Q29" s="81"/>
+      <c r="R29" s="81"/>
+      <c r="S29" s="81"/>
+      <c r="T29" s="81"/>
+      <c r="U29" s="81"/>
+      <c r="V29" s="81"/>
+      <c r="W29" s="81"/>
+      <c r="X29" s="81"/>
+      <c r="Y29" s="81"/>
+      <c r="Z29" s="81"/>
+      <c r="AA29" s="81"/>
+      <c r="AB29" s="81"/>
+      <c r="AC29" s="81"/>
+      <c r="AD29" s="81"/>
+      <c r="AE29" s="81"/>
+      <c r="AF29" s="81"/>
+      <c r="AG29" s="81"/>
+      <c r="AH29" s="81"/>
+      <c r="AI29" s="81"/>
+      <c r="AJ29" s="81"/>
+      <c r="AK29" s="81"/>
+      <c r="AL29" s="81"/>
+      <c r="AM29" s="81"/>
+      <c r="AN29" s="81"/>
+      <c r="AO29" s="81"/>
+      <c r="AP29" s="82"/>
+      <c r="AQ29" s="86"/>
+      <c r="AR29" s="81"/>
+      <c r="AS29" s="81"/>
+      <c r="AT29" s="81"/>
+      <c r="AU29" s="81"/>
+      <c r="AV29" s="81"/>
+      <c r="AW29" s="81"/>
+      <c r="AX29" s="81"/>
+      <c r="AY29" s="81"/>
+      <c r="AZ29" s="81"/>
+      <c r="BA29" s="81"/>
+      <c r="BB29" s="81"/>
+      <c r="BC29" s="81"/>
+      <c r="BD29" s="81"/>
+      <c r="BE29" s="87"/>
     </row>
     <row r="30" spans="1:57" ht="15" customHeight="1">
-      <c r="A30" s="88"/>
-      <c r="B30" s="89"/>
-      <c r="C30" s="89"/>
-      <c r="D30" s="89"/>
-      <c r="E30" s="89"/>
-      <c r="F30" s="89"/>
-      <c r="G30" s="90"/>
-      <c r="H30" s="62"/>
-      <c r="I30" s="64"/>
-      <c r="J30" s="64"/>
-      <c r="K30" s="64"/>
-      <c r="L30" s="64"/>
-      <c r="M30" s="64"/>
-      <c r="N30" s="65"/>
-      <c r="O30" s="62"/>
-      <c r="P30" s="60"/>
-      <c r="Q30" s="60"/>
-      <c r="R30" s="60"/>
-      <c r="S30" s="60"/>
-      <c r="T30" s="60"/>
-      <c r="U30" s="60"/>
-      <c r="V30" s="60"/>
-      <c r="W30" s="60"/>
-      <c r="X30" s="60"/>
-      <c r="Y30" s="60"/>
-      <c r="Z30" s="60"/>
-      <c r="AA30" s="60"/>
-      <c r="AB30" s="60"/>
-      <c r="AC30" s="60"/>
-      <c r="AD30" s="60"/>
-      <c r="AE30" s="60"/>
-      <c r="AF30" s="60"/>
-      <c r="AG30" s="60"/>
-      <c r="AH30" s="60"/>
-      <c r="AI30" s="60"/>
-      <c r="AJ30" s="60"/>
-      <c r="AK30" s="60"/>
-      <c r="AL30" s="60"/>
-      <c r="AM30" s="60"/>
-      <c r="AN30" s="60"/>
-      <c r="AO30" s="60"/>
-      <c r="AP30" s="63"/>
-      <c r="AQ30" s="59"/>
-      <c r="AR30" s="60"/>
-      <c r="AS30" s="60"/>
-      <c r="AT30" s="60"/>
-      <c r="AU30" s="60"/>
-      <c r="AV30" s="60"/>
-      <c r="AW30" s="60"/>
-      <c r="AX30" s="60"/>
-      <c r="AY30" s="60"/>
-      <c r="AZ30" s="60"/>
-      <c r="BA30" s="60"/>
-      <c r="BB30" s="60"/>
-      <c r="BC30" s="60"/>
-      <c r="BD30" s="60"/>
-      <c r="BE30" s="61"/>
+      <c r="A30" s="70"/>
+      <c r="B30" s="71"/>
+      <c r="C30" s="71"/>
+      <c r="D30" s="71"/>
+      <c r="E30" s="71"/>
+      <c r="F30" s="71"/>
+      <c r="G30" s="72"/>
+      <c r="H30" s="78"/>
+      <c r="I30" s="79"/>
+      <c r="J30" s="79"/>
+      <c r="K30" s="79"/>
+      <c r="L30" s="79"/>
+      <c r="M30" s="79"/>
+      <c r="N30" s="80"/>
+      <c r="O30" s="78"/>
+      <c r="P30" s="81"/>
+      <c r="Q30" s="81"/>
+      <c r="R30" s="81"/>
+      <c r="S30" s="81"/>
+      <c r="T30" s="81"/>
+      <c r="U30" s="81"/>
+      <c r="V30" s="81"/>
+      <c r="W30" s="81"/>
+      <c r="X30" s="81"/>
+      <c r="Y30" s="81"/>
+      <c r="Z30" s="81"/>
+      <c r="AA30" s="81"/>
+      <c r="AB30" s="81"/>
+      <c r="AC30" s="81"/>
+      <c r="AD30" s="81"/>
+      <c r="AE30" s="81"/>
+      <c r="AF30" s="81"/>
+      <c r="AG30" s="81"/>
+      <c r="AH30" s="81"/>
+      <c r="AI30" s="81"/>
+      <c r="AJ30" s="81"/>
+      <c r="AK30" s="81"/>
+      <c r="AL30" s="81"/>
+      <c r="AM30" s="81"/>
+      <c r="AN30" s="81"/>
+      <c r="AO30" s="81"/>
+      <c r="AP30" s="82"/>
+      <c r="AQ30" s="86"/>
+      <c r="AR30" s="81"/>
+      <c r="AS30" s="81"/>
+      <c r="AT30" s="81"/>
+      <c r="AU30" s="81"/>
+      <c r="AV30" s="81"/>
+      <c r="AW30" s="81"/>
+      <c r="AX30" s="81"/>
+      <c r="AY30" s="81"/>
+      <c r="AZ30" s="81"/>
+      <c r="BA30" s="81"/>
+      <c r="BB30" s="81"/>
+      <c r="BC30" s="81"/>
+      <c r="BD30" s="81"/>
+      <c r="BE30" s="87"/>
     </row>
     <row r="31" spans="1:57" ht="15" customHeight="1">
-      <c r="A31" s="88"/>
-      <c r="B31" s="89"/>
-      <c r="C31" s="89"/>
-      <c r="D31" s="89"/>
-      <c r="E31" s="89"/>
-      <c r="F31" s="89"/>
-      <c r="G31" s="90"/>
-      <c r="H31" s="62"/>
-      <c r="I31" s="64"/>
-      <c r="J31" s="64"/>
-      <c r="K31" s="64"/>
-      <c r="L31" s="64"/>
-      <c r="M31" s="64"/>
-      <c r="N31" s="65"/>
-      <c r="O31" s="62"/>
-      <c r="P31" s="60"/>
-      <c r="Q31" s="60"/>
-      <c r="R31" s="60"/>
-      <c r="S31" s="60"/>
-      <c r="T31" s="60"/>
-      <c r="U31" s="60"/>
-      <c r="V31" s="60"/>
-      <c r="W31" s="60"/>
-      <c r="X31" s="60"/>
-      <c r="Y31" s="60"/>
-      <c r="Z31" s="60"/>
-      <c r="AA31" s="60"/>
-      <c r="AB31" s="60"/>
-      <c r="AC31" s="60"/>
-      <c r="AD31" s="60"/>
-      <c r="AE31" s="60"/>
-      <c r="AF31" s="60"/>
-      <c r="AG31" s="60"/>
-      <c r="AH31" s="60"/>
-      <c r="AI31" s="60"/>
-      <c r="AJ31" s="60"/>
-      <c r="AK31" s="60"/>
-      <c r="AL31" s="60"/>
-      <c r="AM31" s="60"/>
-      <c r="AN31" s="60"/>
-      <c r="AO31" s="60"/>
-      <c r="AP31" s="63"/>
-      <c r="AQ31" s="59"/>
-      <c r="AR31" s="60"/>
-      <c r="AS31" s="60"/>
-      <c r="AT31" s="60"/>
-      <c r="AU31" s="60"/>
-      <c r="AV31" s="60"/>
-      <c r="AW31" s="60"/>
-      <c r="AX31" s="60"/>
-      <c r="AY31" s="60"/>
-      <c r="AZ31" s="60"/>
-      <c r="BA31" s="60"/>
-      <c r="BB31" s="60"/>
-      <c r="BC31" s="60"/>
-      <c r="BD31" s="60"/>
-      <c r="BE31" s="61"/>
+      <c r="A31" s="70"/>
+      <c r="B31" s="71"/>
+      <c r="C31" s="71"/>
+      <c r="D31" s="71"/>
+      <c r="E31" s="71"/>
+      <c r="F31" s="71"/>
+      <c r="G31" s="72"/>
+      <c r="H31" s="78"/>
+      <c r="I31" s="79"/>
+      <c r="J31" s="79"/>
+      <c r="K31" s="79"/>
+      <c r="L31" s="79"/>
+      <c r="M31" s="79"/>
+      <c r="N31" s="80"/>
+      <c r="O31" s="78"/>
+      <c r="P31" s="81"/>
+      <c r="Q31" s="81"/>
+      <c r="R31" s="81"/>
+      <c r="S31" s="81"/>
+      <c r="T31" s="81"/>
+      <c r="U31" s="81"/>
+      <c r="V31" s="81"/>
+      <c r="W31" s="81"/>
+      <c r="X31" s="81"/>
+      <c r="Y31" s="81"/>
+      <c r="Z31" s="81"/>
+      <c r="AA31" s="81"/>
+      <c r="AB31" s="81"/>
+      <c r="AC31" s="81"/>
+      <c r="AD31" s="81"/>
+      <c r="AE31" s="81"/>
+      <c r="AF31" s="81"/>
+      <c r="AG31" s="81"/>
+      <c r="AH31" s="81"/>
+      <c r="AI31" s="81"/>
+      <c r="AJ31" s="81"/>
+      <c r="AK31" s="81"/>
+      <c r="AL31" s="81"/>
+      <c r="AM31" s="81"/>
+      <c r="AN31" s="81"/>
+      <c r="AO31" s="81"/>
+      <c r="AP31" s="82"/>
+      <c r="AQ31" s="86"/>
+      <c r="AR31" s="81"/>
+      <c r="AS31" s="81"/>
+      <c r="AT31" s="81"/>
+      <c r="AU31" s="81"/>
+      <c r="AV31" s="81"/>
+      <c r="AW31" s="81"/>
+      <c r="AX31" s="81"/>
+      <c r="AY31" s="81"/>
+      <c r="AZ31" s="81"/>
+      <c r="BA31" s="81"/>
+      <c r="BB31" s="81"/>
+      <c r="BC31" s="81"/>
+      <c r="BD31" s="81"/>
+      <c r="BE31" s="87"/>
     </row>
     <row r="32" spans="1:57" ht="15" customHeight="1">
-      <c r="A32" s="88"/>
-      <c r="B32" s="89"/>
-      <c r="C32" s="89"/>
-      <c r="D32" s="89"/>
-      <c r="E32" s="89"/>
-      <c r="F32" s="89"/>
-      <c r="G32" s="90"/>
-      <c r="H32" s="62"/>
-      <c r="I32" s="64"/>
-      <c r="J32" s="64"/>
-      <c r="K32" s="64"/>
-      <c r="L32" s="64"/>
-      <c r="M32" s="64"/>
-      <c r="N32" s="65"/>
-      <c r="O32" s="62"/>
-      <c r="P32" s="60"/>
-      <c r="Q32" s="60"/>
-      <c r="R32" s="60"/>
-      <c r="S32" s="60"/>
-      <c r="T32" s="60"/>
-      <c r="U32" s="60"/>
-      <c r="V32" s="60"/>
-      <c r="W32" s="60"/>
-      <c r="X32" s="60"/>
-      <c r="Y32" s="60"/>
-      <c r="Z32" s="60"/>
-      <c r="AA32" s="60"/>
-      <c r="AB32" s="60"/>
-      <c r="AC32" s="60"/>
-      <c r="AD32" s="60"/>
-      <c r="AE32" s="60"/>
-      <c r="AF32" s="60"/>
-      <c r="AG32" s="60"/>
-      <c r="AH32" s="60"/>
-      <c r="AI32" s="60"/>
-      <c r="AJ32" s="60"/>
-      <c r="AK32" s="60"/>
-      <c r="AL32" s="60"/>
-      <c r="AM32" s="60"/>
-      <c r="AN32" s="60"/>
-      <c r="AO32" s="60"/>
-      <c r="AP32" s="63"/>
-      <c r="AQ32" s="59"/>
-      <c r="AR32" s="60"/>
-      <c r="AS32" s="60"/>
-      <c r="AT32" s="60"/>
-      <c r="AU32" s="60"/>
-      <c r="AV32" s="60"/>
-      <c r="AW32" s="60"/>
-      <c r="AX32" s="60"/>
-      <c r="AY32" s="60"/>
-      <c r="AZ32" s="60"/>
-      <c r="BA32" s="60"/>
-      <c r="BB32" s="60"/>
-      <c r="BC32" s="60"/>
-      <c r="BD32" s="60"/>
-      <c r="BE32" s="61"/>
+      <c r="A32" s="70"/>
+      <c r="B32" s="71"/>
+      <c r="C32" s="71"/>
+      <c r="D32" s="71"/>
+      <c r="E32" s="71"/>
+      <c r="F32" s="71"/>
+      <c r="G32" s="72"/>
+      <c r="H32" s="78"/>
+      <c r="I32" s="79"/>
+      <c r="J32" s="79"/>
+      <c r="K32" s="79"/>
+      <c r="L32" s="79"/>
+      <c r="M32" s="79"/>
+      <c r="N32" s="80"/>
+      <c r="O32" s="78"/>
+      <c r="P32" s="81"/>
+      <c r="Q32" s="81"/>
+      <c r="R32" s="81"/>
+      <c r="S32" s="81"/>
+      <c r="T32" s="81"/>
+      <c r="U32" s="81"/>
+      <c r="V32" s="81"/>
+      <c r="W32" s="81"/>
+      <c r="X32" s="81"/>
+      <c r="Y32" s="81"/>
+      <c r="Z32" s="81"/>
+      <c r="AA32" s="81"/>
+      <c r="AB32" s="81"/>
+      <c r="AC32" s="81"/>
+      <c r="AD32" s="81"/>
+      <c r="AE32" s="81"/>
+      <c r="AF32" s="81"/>
+      <c r="AG32" s="81"/>
+      <c r="AH32" s="81"/>
+      <c r="AI32" s="81"/>
+      <c r="AJ32" s="81"/>
+      <c r="AK32" s="81"/>
+      <c r="AL32" s="81"/>
+      <c r="AM32" s="81"/>
+      <c r="AN32" s="81"/>
+      <c r="AO32" s="81"/>
+      <c r="AP32" s="82"/>
+      <c r="AQ32" s="86"/>
+      <c r="AR32" s="81"/>
+      <c r="AS32" s="81"/>
+      <c r="AT32" s="81"/>
+      <c r="AU32" s="81"/>
+      <c r="AV32" s="81"/>
+      <c r="AW32" s="81"/>
+      <c r="AX32" s="81"/>
+      <c r="AY32" s="81"/>
+      <c r="AZ32" s="81"/>
+      <c r="BA32" s="81"/>
+      <c r="BB32" s="81"/>
+      <c r="BC32" s="81"/>
+      <c r="BD32" s="81"/>
+      <c r="BE32" s="87"/>
     </row>
     <row r="33" spans="1:57" ht="15" customHeight="1">
-      <c r="A33" s="88"/>
-      <c r="B33" s="89"/>
-      <c r="C33" s="89"/>
-      <c r="D33" s="89"/>
-      <c r="E33" s="89"/>
-      <c r="F33" s="89"/>
-      <c r="G33" s="90"/>
-      <c r="H33" s="62"/>
-      <c r="I33" s="64"/>
-      <c r="J33" s="64"/>
-      <c r="K33" s="64"/>
-      <c r="L33" s="64"/>
-      <c r="M33" s="64"/>
-      <c r="N33" s="65"/>
-      <c r="O33" s="62"/>
-      <c r="P33" s="60"/>
-      <c r="Q33" s="60"/>
-      <c r="R33" s="60"/>
-      <c r="S33" s="60"/>
-      <c r="T33" s="60"/>
-      <c r="U33" s="60"/>
-      <c r="V33" s="60"/>
-      <c r="W33" s="60"/>
-      <c r="X33" s="60"/>
-      <c r="Y33" s="60"/>
-      <c r="Z33" s="60"/>
-      <c r="AA33" s="60"/>
-      <c r="AB33" s="60"/>
-      <c r="AC33" s="60"/>
-      <c r="AD33" s="60"/>
-      <c r="AE33" s="60"/>
-      <c r="AF33" s="60"/>
-      <c r="AG33" s="60"/>
-      <c r="AH33" s="60"/>
-      <c r="AI33" s="60"/>
-      <c r="AJ33" s="60"/>
-      <c r="AK33" s="60"/>
-      <c r="AL33" s="60"/>
-      <c r="AM33" s="60"/>
-      <c r="AN33" s="60"/>
-      <c r="AO33" s="60"/>
-      <c r="AP33" s="63"/>
-      <c r="AQ33" s="59"/>
-      <c r="AR33" s="60"/>
-      <c r="AS33" s="60"/>
-      <c r="AT33" s="60"/>
-      <c r="AU33" s="60"/>
-      <c r="AV33" s="60"/>
-      <c r="AW33" s="60"/>
-      <c r="AX33" s="60"/>
-      <c r="AY33" s="60"/>
-      <c r="AZ33" s="60"/>
-      <c r="BA33" s="60"/>
-      <c r="BB33" s="60"/>
-      <c r="BC33" s="60"/>
-      <c r="BD33" s="60"/>
-      <c r="BE33" s="61"/>
+      <c r="A33" s="70"/>
+      <c r="B33" s="71"/>
+      <c r="C33" s="71"/>
+      <c r="D33" s="71"/>
+      <c r="E33" s="71"/>
+      <c r="F33" s="71"/>
+      <c r="G33" s="72"/>
+      <c r="H33" s="78"/>
+      <c r="I33" s="79"/>
+      <c r="J33" s="79"/>
+      <c r="K33" s="79"/>
+      <c r="L33" s="79"/>
+      <c r="M33" s="79"/>
+      <c r="N33" s="80"/>
+      <c r="O33" s="78"/>
+      <c r="P33" s="81"/>
+      <c r="Q33" s="81"/>
+      <c r="R33" s="81"/>
+      <c r="S33" s="81"/>
+      <c r="T33" s="81"/>
+      <c r="U33" s="81"/>
+      <c r="V33" s="81"/>
+      <c r="W33" s="81"/>
+      <c r="X33" s="81"/>
+      <c r="Y33" s="81"/>
+      <c r="Z33" s="81"/>
+      <c r="AA33" s="81"/>
+      <c r="AB33" s="81"/>
+      <c r="AC33" s="81"/>
+      <c r="AD33" s="81"/>
+      <c r="AE33" s="81"/>
+      <c r="AF33" s="81"/>
+      <c r="AG33" s="81"/>
+      <c r="AH33" s="81"/>
+      <c r="AI33" s="81"/>
+      <c r="AJ33" s="81"/>
+      <c r="AK33" s="81"/>
+      <c r="AL33" s="81"/>
+      <c r="AM33" s="81"/>
+      <c r="AN33" s="81"/>
+      <c r="AO33" s="81"/>
+      <c r="AP33" s="82"/>
+      <c r="AQ33" s="86"/>
+      <c r="AR33" s="81"/>
+      <c r="AS33" s="81"/>
+      <c r="AT33" s="81"/>
+      <c r="AU33" s="81"/>
+      <c r="AV33" s="81"/>
+      <c r="AW33" s="81"/>
+      <c r="AX33" s="81"/>
+      <c r="AY33" s="81"/>
+      <c r="AZ33" s="81"/>
+      <c r="BA33" s="81"/>
+      <c r="BB33" s="81"/>
+      <c r="BC33" s="81"/>
+      <c r="BD33" s="81"/>
+      <c r="BE33" s="87"/>
     </row>
     <row r="34" spans="1:57" ht="15" customHeight="1">
-      <c r="A34" s="88"/>
-      <c r="B34" s="89"/>
-      <c r="C34" s="89"/>
-      <c r="D34" s="89"/>
-      <c r="E34" s="89"/>
-      <c r="F34" s="89"/>
-      <c r="G34" s="90"/>
-      <c r="H34" s="62"/>
-      <c r="I34" s="64"/>
-      <c r="J34" s="64"/>
-      <c r="K34" s="64"/>
-      <c r="L34" s="64"/>
-      <c r="M34" s="64"/>
-      <c r="N34" s="65"/>
-      <c r="O34" s="62"/>
-      <c r="P34" s="60"/>
-      <c r="Q34" s="60"/>
-      <c r="R34" s="60"/>
-      <c r="S34" s="60"/>
-      <c r="T34" s="60"/>
-      <c r="U34" s="60"/>
-      <c r="V34" s="60"/>
-      <c r="W34" s="60"/>
-      <c r="X34" s="60"/>
-      <c r="Y34" s="60"/>
-      <c r="Z34" s="60"/>
-      <c r="AA34" s="60"/>
-      <c r="AB34" s="60"/>
-      <c r="AC34" s="60"/>
-      <c r="AD34" s="60"/>
-      <c r="AE34" s="60"/>
-      <c r="AF34" s="60"/>
-      <c r="AG34" s="60"/>
-      <c r="AH34" s="60"/>
-      <c r="AI34" s="60"/>
-      <c r="AJ34" s="60"/>
-      <c r="AK34" s="60"/>
-      <c r="AL34" s="60"/>
-      <c r="AM34" s="60"/>
-      <c r="AN34" s="60"/>
-      <c r="AO34" s="60"/>
-      <c r="AP34" s="63"/>
-      <c r="AQ34" s="59"/>
-      <c r="AR34" s="60"/>
-      <c r="AS34" s="60"/>
-      <c r="AT34" s="60"/>
-      <c r="AU34" s="60"/>
-      <c r="AV34" s="60"/>
-      <c r="AW34" s="60"/>
-      <c r="AX34" s="60"/>
-      <c r="AY34" s="60"/>
-      <c r="AZ34" s="60"/>
-      <c r="BA34" s="60"/>
-      <c r="BB34" s="60"/>
-      <c r="BC34" s="60"/>
-      <c r="BD34" s="60"/>
-      <c r="BE34" s="61"/>
+      <c r="A34" s="70"/>
+      <c r="B34" s="71"/>
+      <c r="C34" s="71"/>
+      <c r="D34" s="71"/>
+      <c r="E34" s="71"/>
+      <c r="F34" s="71"/>
+      <c r="G34" s="72"/>
+      <c r="H34" s="78"/>
+      <c r="I34" s="79"/>
+      <c r="J34" s="79"/>
+      <c r="K34" s="79"/>
+      <c r="L34" s="79"/>
+      <c r="M34" s="79"/>
+      <c r="N34" s="80"/>
+      <c r="O34" s="78"/>
+      <c r="P34" s="81"/>
+      <c r="Q34" s="81"/>
+      <c r="R34" s="81"/>
+      <c r="S34" s="81"/>
+      <c r="T34" s="81"/>
+      <c r="U34" s="81"/>
+      <c r="V34" s="81"/>
+      <c r="W34" s="81"/>
+      <c r="X34" s="81"/>
+      <c r="Y34" s="81"/>
+      <c r="Z34" s="81"/>
+      <c r="AA34" s="81"/>
+      <c r="AB34" s="81"/>
+      <c r="AC34" s="81"/>
+      <c r="AD34" s="81"/>
+      <c r="AE34" s="81"/>
+      <c r="AF34" s="81"/>
+      <c r="AG34" s="81"/>
+      <c r="AH34" s="81"/>
+      <c r="AI34" s="81"/>
+      <c r="AJ34" s="81"/>
+      <c r="AK34" s="81"/>
+      <c r="AL34" s="81"/>
+      <c r="AM34" s="81"/>
+      <c r="AN34" s="81"/>
+      <c r="AO34" s="81"/>
+      <c r="AP34" s="82"/>
+      <c r="AQ34" s="86"/>
+      <c r="AR34" s="81"/>
+      <c r="AS34" s="81"/>
+      <c r="AT34" s="81"/>
+      <c r="AU34" s="81"/>
+      <c r="AV34" s="81"/>
+      <c r="AW34" s="81"/>
+      <c r="AX34" s="81"/>
+      <c r="AY34" s="81"/>
+      <c r="AZ34" s="81"/>
+      <c r="BA34" s="81"/>
+      <c r="BB34" s="81"/>
+      <c r="BC34" s="81"/>
+      <c r="BD34" s="81"/>
+      <c r="BE34" s="87"/>
     </row>
     <row r="35" spans="1:57" ht="15" customHeight="1" thickBot="1">
-      <c r="A35" s="95"/>
-      <c r="B35" s="96"/>
-      <c r="C35" s="96"/>
-      <c r="D35" s="96"/>
-      <c r="E35" s="96"/>
-      <c r="F35" s="96"/>
-      <c r="G35" s="97"/>
-      <c r="H35" s="91"/>
-      <c r="I35" s="92"/>
-      <c r="J35" s="92"/>
-      <c r="K35" s="92"/>
-      <c r="L35" s="92"/>
-      <c r="M35" s="92"/>
-      <c r="N35" s="93"/>
-      <c r="O35" s="91"/>
-      <c r="P35" s="83"/>
-      <c r="Q35" s="83"/>
-      <c r="R35" s="83"/>
-      <c r="S35" s="83"/>
-      <c r="T35" s="83"/>
-      <c r="U35" s="83"/>
-      <c r="V35" s="83"/>
-      <c r="W35" s="83"/>
-      <c r="X35" s="83"/>
-      <c r="Y35" s="83"/>
-      <c r="Z35" s="83"/>
-      <c r="AA35" s="83"/>
-      <c r="AB35" s="83"/>
-      <c r="AC35" s="83"/>
-      <c r="AD35" s="83"/>
-      <c r="AE35" s="83"/>
-      <c r="AF35" s="83"/>
-      <c r="AG35" s="83"/>
-      <c r="AH35" s="83"/>
-      <c r="AI35" s="83"/>
-      <c r="AJ35" s="83"/>
-      <c r="AK35" s="83"/>
-      <c r="AL35" s="83"/>
-      <c r="AM35" s="83"/>
-      <c r="AN35" s="83"/>
-      <c r="AO35" s="83"/>
-      <c r="AP35" s="94"/>
-      <c r="AQ35" s="82"/>
-      <c r="AR35" s="83"/>
-      <c r="AS35" s="83"/>
-      <c r="AT35" s="83"/>
-      <c r="AU35" s="83"/>
-      <c r="AV35" s="83"/>
-      <c r="AW35" s="83"/>
-      <c r="AX35" s="83"/>
-      <c r="AY35" s="83"/>
-      <c r="AZ35" s="83"/>
-      <c r="BA35" s="83"/>
-      <c r="BB35" s="83"/>
-      <c r="BC35" s="83"/>
-      <c r="BD35" s="83"/>
-      <c r="BE35" s="84"/>
+      <c r="A35" s="83"/>
+      <c r="B35" s="84"/>
+      <c r="C35" s="84"/>
+      <c r="D35" s="84"/>
+      <c r="E35" s="84"/>
+      <c r="F35" s="84"/>
+      <c r="G35" s="85"/>
+      <c r="H35" s="73"/>
+      <c r="I35" s="74"/>
+      <c r="J35" s="74"/>
+      <c r="K35" s="74"/>
+      <c r="L35" s="74"/>
+      <c r="M35" s="74"/>
+      <c r="N35" s="75"/>
+      <c r="O35" s="73"/>
+      <c r="P35" s="76"/>
+      <c r="Q35" s="76"/>
+      <c r="R35" s="76"/>
+      <c r="S35" s="76"/>
+      <c r="T35" s="76"/>
+      <c r="U35" s="76"/>
+      <c r="V35" s="76"/>
+      <c r="W35" s="76"/>
+      <c r="X35" s="76"/>
+      <c r="Y35" s="76"/>
+      <c r="Z35" s="76"/>
+      <c r="AA35" s="76"/>
+      <c r="AB35" s="76"/>
+      <c r="AC35" s="76"/>
+      <c r="AD35" s="76"/>
+      <c r="AE35" s="76"/>
+      <c r="AF35" s="76"/>
+      <c r="AG35" s="76"/>
+      <c r="AH35" s="76"/>
+      <c r="AI35" s="76"/>
+      <c r="AJ35" s="76"/>
+      <c r="AK35" s="76"/>
+      <c r="AL35" s="76"/>
+      <c r="AM35" s="76"/>
+      <c r="AN35" s="76"/>
+      <c r="AO35" s="76"/>
+      <c r="AP35" s="77"/>
+      <c r="AQ35" s="88"/>
+      <c r="AR35" s="76"/>
+      <c r="AS35" s="76"/>
+      <c r="AT35" s="76"/>
+      <c r="AU35" s="76"/>
+      <c r="AV35" s="76"/>
+      <c r="AW35" s="76"/>
+      <c r="AX35" s="76"/>
+      <c r="AY35" s="76"/>
+      <c r="AZ35" s="76"/>
+      <c r="BA35" s="76"/>
+      <c r="BB35" s="76"/>
+      <c r="BC35" s="76"/>
+      <c r="BD35" s="76"/>
+      <c r="BE35" s="89"/>
     </row>
   </sheetData>
   <mergeCells count="133">
+    <mergeCell ref="AQ28:BE28"/>
+    <mergeCell ref="O29:AP29"/>
+    <mergeCell ref="AQ29:BE29"/>
+    <mergeCell ref="H25:N25"/>
+    <mergeCell ref="O25:AP25"/>
+    <mergeCell ref="AQ25:BE25"/>
+    <mergeCell ref="H27:N27"/>
+    <mergeCell ref="O27:AP27"/>
+    <mergeCell ref="O26:AP26"/>
+    <mergeCell ref="AQ26:BE26"/>
+    <mergeCell ref="AQ27:BE27"/>
+    <mergeCell ref="H29:N29"/>
+    <mergeCell ref="H28:N28"/>
+    <mergeCell ref="AQ13:BE13"/>
+    <mergeCell ref="H14:N14"/>
+    <mergeCell ref="O14:AP14"/>
+    <mergeCell ref="AQ14:BE14"/>
+    <mergeCell ref="H21:N21"/>
+    <mergeCell ref="O21:AP21"/>
+    <mergeCell ref="AQ21:BE21"/>
+    <mergeCell ref="H22:N22"/>
+    <mergeCell ref="O22:AP22"/>
+    <mergeCell ref="AQ22:BE22"/>
+    <mergeCell ref="AQ18:BE18"/>
+    <mergeCell ref="AQ16:BE16"/>
+    <mergeCell ref="H4:N4"/>
+    <mergeCell ref="O4:AP4"/>
+    <mergeCell ref="AQ4:BE4"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="H12:N12"/>
+    <mergeCell ref="O12:AP12"/>
+    <mergeCell ref="AQ12:BE12"/>
+    <mergeCell ref="H11:N11"/>
+    <mergeCell ref="H7:N7"/>
+    <mergeCell ref="O11:AP11"/>
+    <mergeCell ref="AQ10:BE10"/>
+    <mergeCell ref="AQ8:BE8"/>
+    <mergeCell ref="H5:N5"/>
+    <mergeCell ref="O5:AP5"/>
+    <mergeCell ref="AQ5:BE5"/>
+    <mergeCell ref="H6:N6"/>
+    <mergeCell ref="O6:AP6"/>
+    <mergeCell ref="AQ6:BE6"/>
+    <mergeCell ref="AQ11:BE11"/>
+    <mergeCell ref="H9:N9"/>
+    <mergeCell ref="O9:AP9"/>
+    <mergeCell ref="AQ9:BE9"/>
+    <mergeCell ref="O7:AP7"/>
+    <mergeCell ref="AQ7:BE7"/>
+    <mergeCell ref="H8:N8"/>
+    <mergeCell ref="O8:AP8"/>
+    <mergeCell ref="H10:N10"/>
+    <mergeCell ref="O10:AP10"/>
+    <mergeCell ref="AQ30:BE30"/>
+    <mergeCell ref="H26:N26"/>
+    <mergeCell ref="O15:AP15"/>
+    <mergeCell ref="AQ15:BE15"/>
+    <mergeCell ref="H16:N16"/>
+    <mergeCell ref="O16:AP16"/>
+    <mergeCell ref="O23:AP23"/>
+    <mergeCell ref="AQ23:BE23"/>
+    <mergeCell ref="H20:N20"/>
+    <mergeCell ref="O20:AP20"/>
+    <mergeCell ref="AQ20:BE20"/>
+    <mergeCell ref="H19:N19"/>
+    <mergeCell ref="H15:N15"/>
+    <mergeCell ref="O19:AP19"/>
+    <mergeCell ref="AQ19:BE19"/>
+    <mergeCell ref="H17:N17"/>
+    <mergeCell ref="O17:AP17"/>
+    <mergeCell ref="AQ17:BE17"/>
+    <mergeCell ref="H18:N18"/>
+    <mergeCell ref="O18:AP18"/>
+    <mergeCell ref="AQ34:BE34"/>
+    <mergeCell ref="H33:N33"/>
+    <mergeCell ref="H34:N34"/>
+    <mergeCell ref="O34:AP34"/>
+    <mergeCell ref="AQ35:BE35"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="H32:N32"/>
+    <mergeCell ref="O32:AP32"/>
+    <mergeCell ref="AQ32:BE32"/>
+    <mergeCell ref="H31:N31"/>
+    <mergeCell ref="O33:AP33"/>
+    <mergeCell ref="AQ33:BE33"/>
+    <mergeCell ref="H24:N24"/>
+    <mergeCell ref="O24:AP24"/>
+    <mergeCell ref="AQ24:BE24"/>
+    <mergeCell ref="H23:N23"/>
+    <mergeCell ref="O31:AP31"/>
+    <mergeCell ref="AQ31:BE31"/>
+    <mergeCell ref="H30:N30"/>
+    <mergeCell ref="O30:AP30"/>
+    <mergeCell ref="H35:N35"/>
+    <mergeCell ref="O35:AP35"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="H13:N13"/>
+    <mergeCell ref="O13:AP13"/>
+    <mergeCell ref="O28:AP28"/>
+    <mergeCell ref="A35:G35"/>
     <mergeCell ref="A1:BE1"/>
     <mergeCell ref="H3:N3"/>
     <mergeCell ref="O3:AP3"/>
@@ -6998,115 +7106,6 @@
     <mergeCell ref="A22:G22"/>
     <mergeCell ref="A9:G9"/>
     <mergeCell ref="A10:G10"/>
-    <mergeCell ref="H35:N35"/>
-    <mergeCell ref="O35:AP35"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="H13:N13"/>
-    <mergeCell ref="O13:AP13"/>
-    <mergeCell ref="O28:AP28"/>
-    <mergeCell ref="A35:G35"/>
-    <mergeCell ref="AQ34:BE34"/>
-    <mergeCell ref="H33:N33"/>
-    <mergeCell ref="H34:N34"/>
-    <mergeCell ref="O34:AP34"/>
-    <mergeCell ref="AQ35:BE35"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="H32:N32"/>
-    <mergeCell ref="O32:AP32"/>
-    <mergeCell ref="AQ32:BE32"/>
-    <mergeCell ref="H31:N31"/>
-    <mergeCell ref="O33:AP33"/>
-    <mergeCell ref="AQ33:BE33"/>
-    <mergeCell ref="H24:N24"/>
-    <mergeCell ref="O24:AP24"/>
-    <mergeCell ref="AQ24:BE24"/>
-    <mergeCell ref="H23:N23"/>
-    <mergeCell ref="O31:AP31"/>
-    <mergeCell ref="AQ31:BE31"/>
-    <mergeCell ref="H30:N30"/>
-    <mergeCell ref="O30:AP30"/>
-    <mergeCell ref="H8:N8"/>
-    <mergeCell ref="O8:AP8"/>
-    <mergeCell ref="H10:N10"/>
-    <mergeCell ref="O10:AP10"/>
-    <mergeCell ref="AQ30:BE30"/>
-    <mergeCell ref="H26:N26"/>
-    <mergeCell ref="O15:AP15"/>
-    <mergeCell ref="AQ15:BE15"/>
-    <mergeCell ref="H16:N16"/>
-    <mergeCell ref="O16:AP16"/>
-    <mergeCell ref="O23:AP23"/>
-    <mergeCell ref="AQ23:BE23"/>
-    <mergeCell ref="H20:N20"/>
-    <mergeCell ref="O20:AP20"/>
-    <mergeCell ref="AQ20:BE20"/>
-    <mergeCell ref="H19:N19"/>
-    <mergeCell ref="H15:N15"/>
-    <mergeCell ref="O19:AP19"/>
-    <mergeCell ref="AQ19:BE19"/>
-    <mergeCell ref="H17:N17"/>
-    <mergeCell ref="O17:AP17"/>
-    <mergeCell ref="AQ17:BE17"/>
-    <mergeCell ref="H18:N18"/>
-    <mergeCell ref="O18:AP18"/>
-    <mergeCell ref="H4:N4"/>
-    <mergeCell ref="O4:AP4"/>
-    <mergeCell ref="AQ4:BE4"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="H12:N12"/>
-    <mergeCell ref="O12:AP12"/>
-    <mergeCell ref="AQ12:BE12"/>
-    <mergeCell ref="H11:N11"/>
-    <mergeCell ref="H7:N7"/>
-    <mergeCell ref="O11:AP11"/>
-    <mergeCell ref="AQ10:BE10"/>
-    <mergeCell ref="AQ8:BE8"/>
-    <mergeCell ref="H5:N5"/>
-    <mergeCell ref="O5:AP5"/>
-    <mergeCell ref="AQ5:BE5"/>
-    <mergeCell ref="H6:N6"/>
-    <mergeCell ref="O6:AP6"/>
-    <mergeCell ref="AQ6:BE6"/>
-    <mergeCell ref="AQ11:BE11"/>
-    <mergeCell ref="H9:N9"/>
-    <mergeCell ref="O9:AP9"/>
-    <mergeCell ref="AQ9:BE9"/>
-    <mergeCell ref="O7:AP7"/>
-    <mergeCell ref="AQ7:BE7"/>
-    <mergeCell ref="AQ13:BE13"/>
-    <mergeCell ref="H14:N14"/>
-    <mergeCell ref="O14:AP14"/>
-    <mergeCell ref="AQ14:BE14"/>
-    <mergeCell ref="H21:N21"/>
-    <mergeCell ref="O21:AP21"/>
-    <mergeCell ref="AQ21:BE21"/>
-    <mergeCell ref="H22:N22"/>
-    <mergeCell ref="O22:AP22"/>
-    <mergeCell ref="AQ22:BE22"/>
-    <mergeCell ref="AQ18:BE18"/>
-    <mergeCell ref="AQ16:BE16"/>
-    <mergeCell ref="AQ28:BE28"/>
-    <mergeCell ref="O29:AP29"/>
-    <mergeCell ref="AQ29:BE29"/>
-    <mergeCell ref="H25:N25"/>
-    <mergeCell ref="O25:AP25"/>
-    <mergeCell ref="AQ25:BE25"/>
-    <mergeCell ref="H27:N27"/>
-    <mergeCell ref="O27:AP27"/>
-    <mergeCell ref="O26:AP26"/>
-    <mergeCell ref="AQ26:BE26"/>
-    <mergeCell ref="AQ27:BE27"/>
-    <mergeCell ref="H29:N29"/>
-    <mergeCell ref="H28:N28"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>

--- a/development/MS/spec/MSBB/Panel/MSBBPA0030_SloDlv_H.xlsx
+++ b/development/MS/spec/MSBB/Panel/MSBBPA0030_SloDlv_H.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\mcframeDEV\development\MS\spec\MSBB\Panel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E46DFD2-4993-4FFE-84D7-B28A762EA8BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{641194BF-E977-43FA-B602-DD46744D8F2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="821" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2820" yWindow="3840" windowWidth="21600" windowHeight="12645" tabRatio="821" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MSBBPA0030" sheetId="1" r:id="rId1"/>
@@ -451,10 +451,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>bp_is_srch_typ</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>ModuleID :</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -508,10 +504,6 @@
   </si>
   <si>
     <t>ScreenType :</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>MAC_BP_IS_SRCH_TYP.DLV</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -906,6 +898,12 @@
   </si>
   <si>
     <t>MS.MSUAP0030.SloDlv</t>
+  </si>
+  <si>
+    <t>MAC_BP_IS_SRCH_TYP.DLV;cst_cd</t>
+  </si>
+  <si>
+    <t>bp_is_srch_typ;bp_cd</t>
   </si>
 </sst>
 </file>
@@ -2359,6 +2357,123 @@
     <xf numFmtId="0" fontId="30" fillId="18" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="18" xfId="138" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="2" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="35" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="18" xfId="138" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="19" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="2" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="19" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="40" xfId="138" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="38" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="39" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="38" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="39" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="40" xfId="138" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="41" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="19" borderId="42" xfId="138" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="31" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="18" xfId="138" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="2" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="19" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="18" xfId="138" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="2" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="35" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="34" xfId="138" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="26" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="36" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="37" xfId="138" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="38" xfId="136" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="39" xfId="136" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="33" xfId="138" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="2" xfId="136" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="19" xfId="136" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="34" xfId="138" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="26" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="27" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="27" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="25" xfId="138" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="26" xfId="136" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="27" xfId="136" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="31" fillId="19" borderId="28" xfId="137" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2371,12 +2486,6 @@
     <xf numFmtId="0" fontId="33" fillId="19" borderId="30" xfId="138" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="31" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="33" fillId="19" borderId="1" xfId="138" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2391,117 +2500,6 @@
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="32" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="33" xfId="138" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="2" xfId="136" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="19" xfId="136" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="34" xfId="138" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="26" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="27" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="26" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="27" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="18" xfId="138" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="2" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="19" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="2" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="19" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="25" xfId="138" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="26" xfId="136" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="27" xfId="136" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="18" xfId="138" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="35" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="34" xfId="138" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="36" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="37" xfId="138" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="38" xfId="136" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="39" xfId="136" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="40" xfId="138" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="38" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="39" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="38" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="39" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="40" xfId="138" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="41" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="19" borderId="42" xfId="138" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="18" xfId="138" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="2" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="19" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="18" xfId="138" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="2" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="35" xfId="136" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="143">
@@ -3110,24 +3108,24 @@
       <c r="B2" s="37"/>
       <c r="C2" s="37"/>
       <c r="D2" s="38" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F2" s="32" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="G2" s="51" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H2" s="53"/>
       <c r="I2" s="56" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="J2" s="57"/>
       <c r="K2" s="54" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L2" s="54"/>
       <c r="M2" s="54"/>
@@ -3135,13 +3133,13 @@
       <c r="O2" s="51"/>
       <c r="P2" s="39"/>
       <c r="Q2" s="32" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="R2" s="20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S2" s="32" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="T2" s="40"/>
       <c r="U2" s="41"/>
@@ -3171,21 +3169,21 @@
       <c r="B3" s="43"/>
       <c r="C3" s="43"/>
       <c r="E3" s="20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F3" s="32" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G3" s="51" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H3" s="53"/>
       <c r="I3" s="56" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="J3" s="57"/>
       <c r="K3" s="54" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L3" s="54"/>
       <c r="M3" s="54"/>
@@ -3194,10 +3192,10 @@
       <c r="P3" s="39"/>
       <c r="Q3" s="32"/>
       <c r="R3" s="20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="S3" s="32" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="T3" s="32"/>
       <c r="AM3" s="23"/>
@@ -3210,19 +3208,19 @@
       <c r="C4" s="43"/>
       <c r="D4" s="23"/>
       <c r="E4" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F4" s="32"/>
       <c r="G4" s="51" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H4" s="53"/>
       <c r="I4" s="56" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="J4" s="57"/>
       <c r="K4" s="54" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L4" s="54"/>
       <c r="M4" s="54"/>
@@ -3230,7 +3228,7 @@
       <c r="O4" s="51"/>
       <c r="P4" s="39"/>
       <c r="Q4" s="32" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="R4" s="20"/>
       <c r="S4" s="20"/>
@@ -3249,7 +3247,7 @@
       </c>
       <c r="F5" s="32"/>
       <c r="G5" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H5" s="53"/>
       <c r="I5" s="58" t="s">
@@ -3393,52 +3391,52 @@
       <c r="B8" s="32"/>
       <c r="C8" s="32"/>
       <c r="D8" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="F8" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="G8" s="17" t="s">
         <v>139</v>
-      </c>
-      <c r="E8" s="20" t="s">
-        <v>115</v>
-      </c>
-      <c r="F8" s="20" t="s">
-        <v>140</v>
-      </c>
-      <c r="G8" s="17" t="s">
-        <v>141</v>
       </c>
       <c r="H8" s="20"/>
       <c r="I8" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="J8" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="K8" s="20" t="s">
         <v>142</v>
       </c>
-      <c r="J8" s="20" t="s">
+      <c r="L8" s="20" t="s">
         <v>143</v>
       </c>
-      <c r="K8" s="20" t="s">
+      <c r="M8" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="N8" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="O8" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="P8" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q8" s="51" t="s">
         <v>144</v>
-      </c>
-      <c r="L8" s="20" t="s">
-        <v>145</v>
-      </c>
-      <c r="M8" s="20" t="s">
-        <v>116</v>
-      </c>
-      <c r="N8" s="20" t="s">
-        <v>117</v>
-      </c>
-      <c r="O8" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="P8" s="20" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q8" s="51" t="s">
-        <v>146</v>
       </c>
       <c r="R8" s="52"/>
       <c r="S8" s="53"/>
       <c r="T8" s="40" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="U8" s="32" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="V8" s="32" t="s">
         <v>75</v>
@@ -3447,38 +3445,38 @@
         <v>74</v>
       </c>
       <c r="X8" s="32" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="Y8" s="5"/>
       <c r="Z8" s="32" t="s">
         <v>8</v>
       </c>
       <c r="AA8" s="32" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="AB8" s="32" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="AC8" s="6"/>
       <c r="AD8" s="20" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="AE8" s="32"/>
       <c r="AF8" s="20" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="AG8" s="32"/>
       <c r="AH8" s="20" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="AI8" s="32"/>
       <c r="AJ8" s="20" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="AK8" s="32"/>
       <c r="AL8" s="7"/>
       <c r="AM8" s="20" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="9" spans="1:39" s="1" customFormat="1" ht="60" customHeight="1">
@@ -3488,52 +3486,52 @@
       <c r="B9" s="32"/>
       <c r="C9" s="32"/>
       <c r="D9" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="F9" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="G9" s="48" t="s">
         <v>149</v>
       </c>
-      <c r="F9" s="48" t="s">
+      <c r="H9" s="48" t="s">
         <v>150</v>
       </c>
-      <c r="G9" s="48" t="s">
+      <c r="I9" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="H9" s="48" t="s">
+      <c r="J9" s="48" t="s">
+        <v>122</v>
+      </c>
+      <c r="K9" s="48" t="s">
         <v>152</v>
       </c>
-      <c r="I9" s="20" t="s">
+      <c r="L9" s="20" t="s">
         <v>153</v>
       </c>
-      <c r="J9" s="48" t="s">
+      <c r="M9" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="N9" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="O9" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="P9" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q9" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="R9" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="S9" s="20" t="s">
         <v>124</v>
-      </c>
-      <c r="K9" s="48" t="s">
-        <v>154</v>
-      </c>
-      <c r="L9" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="M9" s="20" t="s">
-        <v>156</v>
-      </c>
-      <c r="N9" s="20" t="s">
-        <v>157</v>
-      </c>
-      <c r="O9" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="P9" s="20" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q9" s="20" t="s">
-        <v>125</v>
-      </c>
-      <c r="R9" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="S9" s="20" t="s">
-        <v>126</v>
       </c>
       <c r="T9" s="49"/>
       <c r="U9" s="4"/>
@@ -3546,30 +3544,30 @@
       <c r="AB9" s="8"/>
       <c r="AC9" s="9"/>
       <c r="AD9" s="20" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="AE9" s="32" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="AF9" s="20" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="AG9" s="32" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="AH9" s="20" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="AI9" s="32"/>
       <c r="AJ9" s="20" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="AK9" s="32"/>
       <c r="AL9" s="39" t="s">
+        <v>156</v>
+      </c>
+      <c r="AM9" s="20" t="s">
         <v>158</v>
-      </c>
-      <c r="AM9" s="20" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="10" spans="1:39" s="1" customFormat="1" ht="54">
@@ -3603,28 +3601,28 @@
       <c r="AB10" s="4"/>
       <c r="AC10" s="31"/>
       <c r="AD10" s="20" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="AE10" s="20" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AF10" s="20" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="AG10" s="20" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AH10" s="20" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="AI10" s="20" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AJ10" s="20" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="AK10" s="20" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AL10" s="14"/>
       <c r="AM10" s="10"/>
@@ -3638,7 +3636,7 @@
       </c>
       <c r="C11" s="15"/>
       <c r="D11" s="15" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E11" s="16"/>
       <c r="F11" s="15"/>
@@ -3690,7 +3688,7 @@
         <v>54</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F12" s="32" t="s">
         <v>52</v>
@@ -3704,7 +3702,7 @@
       </c>
       <c r="J12" s="32"/>
       <c r="K12" s="32" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="L12" s="32"/>
       <c r="M12" s="32"/>
@@ -3712,7 +3710,7 @@
       <c r="O12" s="32"/>
       <c r="P12" s="32"/>
       <c r="Q12" s="32" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="R12" s="32"/>
       <c r="S12" s="32" t="s">
@@ -3721,10 +3719,10 @@
       <c r="T12" s="32"/>
       <c r="U12" s="32"/>
       <c r="V12" s="32" t="s">
-        <v>92</v>
+        <v>189</v>
       </c>
       <c r="W12" s="32" t="s">
-        <v>77</v>
+        <v>190</v>
       </c>
       <c r="X12" s="32"/>
       <c r="Z12" s="32" t="s">
@@ -3756,7 +3754,7 @@
         <v>55</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F13" s="32" t="s">
         <v>53</v>
@@ -3812,7 +3810,7 @@
         <v>38</v>
       </c>
       <c r="E14" s="19" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F14" s="32" t="s">
         <v>25</v>
@@ -3870,7 +3868,7 @@
         <v>39</v>
       </c>
       <c r="E15" s="19" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F15" s="32" t="s">
         <v>28</v>
@@ -3928,7 +3926,7 @@
         <v>56</v>
       </c>
       <c r="E16" s="19" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F16" s="32" t="s">
         <v>59</v>
@@ -3940,11 +3938,11 @@
       <c r="I16" s="32"/>
       <c r="J16" s="32"/>
       <c r="K16" s="32" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="L16" s="32"/>
       <c r="M16" s="32" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="N16" s="32"/>
       <c r="O16" s="32"/>
@@ -3983,10 +3981,10 @@
       <c r="B17" s="32"/>
       <c r="C17" s="32"/>
       <c r="D17" s="32" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F17" s="32" t="s">
         <v>70</v>
@@ -3996,11 +3994,11 @@
       </c>
       <c r="H17" s="32"/>
       <c r="I17" s="32" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="J17" s="32"/>
       <c r="K17" s="32" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="L17" s="32"/>
       <c r="M17" s="32"/>
@@ -4008,22 +4006,22 @@
       <c r="O17" s="32"/>
       <c r="P17" s="32"/>
       <c r="Q17" s="32" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="R17" s="32"/>
       <c r="S17" s="32" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="T17" s="32"/>
       <c r="U17" s="32"/>
       <c r="V17" s="50" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="W17" s="32" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="X17" s="32" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Z17" s="32" t="s">
         <v>11</v>
@@ -4054,7 +4052,7 @@
         <v>72</v>
       </c>
       <c r="E18" s="19" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F18" s="32" t="s">
         <v>73</v>
@@ -4062,7 +4060,7 @@
       <c r="G18" s="32"/>
       <c r="H18" s="32"/>
       <c r="I18" s="32" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J18" s="32"/>
       <c r="K18" s="32" t="s">
@@ -4081,7 +4079,7 @@
       <c r="V18" s="32"/>
       <c r="W18" s="32"/>
       <c r="X18" s="32" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Z18" s="32" t="s">
         <v>51</v>
@@ -4112,7 +4110,7 @@
         <v>45</v>
       </c>
       <c r="E19" s="19" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F19" s="32" t="s">
         <v>60</v>
@@ -4122,7 +4120,7 @@
       </c>
       <c r="H19" s="32"/>
       <c r="I19" s="32" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="J19" s="32"/>
       <c r="K19" s="32" t="s">
@@ -4170,7 +4168,7 @@
         <v>46</v>
       </c>
       <c r="E20" s="19" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F20" s="32" t="s">
         <v>61</v>
@@ -4178,7 +4176,7 @@
       <c r="G20" s="32"/>
       <c r="H20" s="32"/>
       <c r="I20" s="32" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="J20" s="32"/>
       <c r="K20" s="32" t="s">
@@ -4226,7 +4224,7 @@
         <v>40</v>
       </c>
       <c r="E21" s="19" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F21" s="32" t="s">
         <v>63</v>
@@ -4236,7 +4234,7 @@
       </c>
       <c r="H21" s="32"/>
       <c r="I21" s="32" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="J21" s="32"/>
       <c r="K21" s="32" t="s">
@@ -4284,7 +4282,7 @@
         <v>41</v>
       </c>
       <c r="E22" s="19" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F22" s="32" t="s">
         <v>64</v>
@@ -4294,7 +4292,7 @@
       </c>
       <c r="H22" s="32"/>
       <c r="I22" s="32" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="J22" s="32"/>
       <c r="K22" s="32" t="s">
@@ -4313,7 +4311,7 @@
       <c r="V22" s="32"/>
       <c r="W22" s="32"/>
       <c r="X22" s="32" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="Z22" s="32" t="s">
         <v>11</v>
@@ -4344,7 +4342,7 @@
         <v>42</v>
       </c>
       <c r="E23" s="19" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F23" s="32" t="s">
         <v>65</v>
@@ -4354,7 +4352,7 @@
       </c>
       <c r="H23" s="32"/>
       <c r="I23" s="32" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="J23" s="32"/>
       <c r="K23" s="32" t="s">
@@ -4373,7 +4371,7 @@
       <c r="V23" s="32"/>
       <c r="W23" s="32"/>
       <c r="X23" s="32" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="Z23" s="32" t="s">
         <v>11</v>
@@ -4404,7 +4402,7 @@
         <v>43</v>
       </c>
       <c r="E24" s="19" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F24" s="32" t="s">
         <v>66</v>
@@ -4414,7 +4412,7 @@
       </c>
       <c r="H24" s="32"/>
       <c r="I24" s="32" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="J24" s="32"/>
       <c r="K24" s="32" t="s">
@@ -4433,7 +4431,7 @@
       <c r="V24" s="32"/>
       <c r="W24" s="32"/>
       <c r="X24" s="32" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="Z24" s="32" t="s">
         <v>11</v>
@@ -4464,7 +4462,7 @@
         <v>44</v>
       </c>
       <c r="E25" s="19" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F25" s="32" t="s">
         <v>67</v>
@@ -4474,7 +4472,7 @@
       </c>
       <c r="H25" s="32"/>
       <c r="I25" s="32" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="J25" s="32"/>
       <c r="K25" s="32" t="s">
@@ -4493,7 +4491,7 @@
       <c r="V25" s="32"/>
       <c r="W25" s="32"/>
       <c r="X25" s="32" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="Z25" s="32" t="s">
         <v>11</v>
@@ -4524,7 +4522,7 @@
         <v>47</v>
       </c>
       <c r="E26" s="19" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F26" s="32" t="s">
         <v>68</v>
@@ -4534,7 +4532,7 @@
       </c>
       <c r="H26" s="32"/>
       <c r="I26" s="32" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="J26" s="32"/>
       <c r="K26" s="32" t="s">
@@ -4582,7 +4580,7 @@
         <v>48</v>
       </c>
       <c r="E27" s="19" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F27" s="32" t="s">
         <v>69</v>
@@ -4592,7 +4590,7 @@
       </c>
       <c r="H27" s="32"/>
       <c r="I27" s="32" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="J27" s="32"/>
       <c r="K27" s="32" t="s">
@@ -4640,7 +4638,7 @@
         <v>49</v>
       </c>
       <c r="E28" s="19" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F28" s="32" t="s">
         <v>35</v>
@@ -4650,7 +4648,7 @@
       </c>
       <c r="H28" s="32"/>
       <c r="I28" s="32" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="J28" s="32"/>
       <c r="K28" s="32" t="s">
@@ -4698,7 +4696,7 @@
         <v>50</v>
       </c>
       <c r="E29" s="19" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F29" s="32" t="s">
         <v>36</v>
@@ -4708,7 +4706,7 @@
       </c>
       <c r="H29" s="32"/>
       <c r="I29" s="32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J29" s="32"/>
       <c r="K29" s="32" t="s">
@@ -4751,7 +4749,7 @@
       <c r="B30" s="22"/>
       <c r="C30" s="22"/>
       <c r="D30" s="8" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E30" s="8"/>
       <c r="F30" s="8"/>
@@ -4900,65 +4898,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:57" s="26" customFormat="1" ht="38.25" customHeight="1" thickBot="1">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="98" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="60"/>
-      <c r="J1" s="60"/>
-      <c r="K1" s="60"/>
-      <c r="L1" s="60"/>
-      <c r="M1" s="60"/>
-      <c r="N1" s="60"/>
-      <c r="O1" s="60"/>
-      <c r="P1" s="60"/>
-      <c r="Q1" s="60"/>
-      <c r="R1" s="60"/>
-      <c r="S1" s="60"/>
-      <c r="T1" s="60"/>
-      <c r="U1" s="60"/>
-      <c r="V1" s="60"/>
-      <c r="W1" s="60"/>
-      <c r="X1" s="60"/>
-      <c r="Y1" s="60"/>
-      <c r="Z1" s="60"/>
-      <c r="AA1" s="60"/>
-      <c r="AB1" s="60"/>
-      <c r="AC1" s="60"/>
-      <c r="AD1" s="60"/>
-      <c r="AE1" s="60"/>
-      <c r="AF1" s="60"/>
-      <c r="AG1" s="60"/>
-      <c r="AH1" s="60"/>
-      <c r="AI1" s="60"/>
-      <c r="AJ1" s="60"/>
-      <c r="AK1" s="60"/>
-      <c r="AL1" s="60"/>
-      <c r="AM1" s="60"/>
-      <c r="AN1" s="60"/>
-      <c r="AO1" s="60"/>
-      <c r="AP1" s="60"/>
-      <c r="AQ1" s="60"/>
-      <c r="AR1" s="60"/>
-      <c r="AS1" s="60"/>
-      <c r="AT1" s="60"/>
-      <c r="AU1" s="60"/>
-      <c r="AV1" s="60"/>
-      <c r="AW1" s="60"/>
-      <c r="AX1" s="60"/>
-      <c r="AY1" s="60"/>
-      <c r="AZ1" s="60"/>
-      <c r="BA1" s="60"/>
-      <c r="BB1" s="60"/>
-      <c r="BC1" s="60"/>
-      <c r="BD1" s="60"/>
-      <c r="BE1" s="61"/>
+      <c r="B1" s="99"/>
+      <c r="C1" s="99"/>
+      <c r="D1" s="99"/>
+      <c r="E1" s="99"/>
+      <c r="F1" s="99"/>
+      <c r="G1" s="99"/>
+      <c r="H1" s="99"/>
+      <c r="I1" s="99"/>
+      <c r="J1" s="99"/>
+      <c r="K1" s="99"/>
+      <c r="L1" s="99"/>
+      <c r="M1" s="99"/>
+      <c r="N1" s="99"/>
+      <c r="O1" s="99"/>
+      <c r="P1" s="99"/>
+      <c r="Q1" s="99"/>
+      <c r="R1" s="99"/>
+      <c r="S1" s="99"/>
+      <c r="T1" s="99"/>
+      <c r="U1" s="99"/>
+      <c r="V1" s="99"/>
+      <c r="W1" s="99"/>
+      <c r="X1" s="99"/>
+      <c r="Y1" s="99"/>
+      <c r="Z1" s="99"/>
+      <c r="AA1" s="99"/>
+      <c r="AB1" s="99"/>
+      <c r="AC1" s="99"/>
+      <c r="AD1" s="99"/>
+      <c r="AE1" s="99"/>
+      <c r="AF1" s="99"/>
+      <c r="AG1" s="99"/>
+      <c r="AH1" s="99"/>
+      <c r="AI1" s="99"/>
+      <c r="AJ1" s="99"/>
+      <c r="AK1" s="99"/>
+      <c r="AL1" s="99"/>
+      <c r="AM1" s="99"/>
+      <c r="AN1" s="99"/>
+      <c r="AO1" s="99"/>
+      <c r="AP1" s="99"/>
+      <c r="AQ1" s="99"/>
+      <c r="AR1" s="99"/>
+      <c r="AS1" s="99"/>
+      <c r="AT1" s="99"/>
+      <c r="AU1" s="99"/>
+      <c r="AV1" s="99"/>
+      <c r="AW1" s="99"/>
+      <c r="AX1" s="99"/>
+      <c r="AY1" s="99"/>
+      <c r="AZ1" s="99"/>
+      <c r="BA1" s="99"/>
+      <c r="BB1" s="99"/>
+      <c r="BC1" s="99"/>
+      <c r="BD1" s="99"/>
+      <c r="BE1" s="100"/>
     </row>
     <row r="2" spans="1:57" s="26" customFormat="1" ht="12" customHeight="1" thickBot="1">
       <c r="A2" s="27"/>
@@ -5007,1997 +5005,2056 @@
       <c r="AR2" s="28"/>
     </row>
     <row r="3" spans="1:57" ht="15" customHeight="1" thickBot="1">
-      <c r="A3" s="100" t="s">
+      <c r="A3" s="73" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="63"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="62" t="s">
+      <c r="B3" s="74"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="101" t="s">
         <v>3</v>
       </c>
-      <c r="I3" s="63"/>
-      <c r="J3" s="63"/>
-      <c r="K3" s="63"/>
-      <c r="L3" s="63"/>
-      <c r="M3" s="63"/>
-      <c r="N3" s="64"/>
-      <c r="O3" s="62" t="s">
+      <c r="I3" s="74"/>
+      <c r="J3" s="74"/>
+      <c r="K3" s="74"/>
+      <c r="L3" s="74"/>
+      <c r="M3" s="74"/>
+      <c r="N3" s="75"/>
+      <c r="O3" s="101" t="s">
         <v>4</v>
       </c>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="65"/>
-      <c r="T3" s="65"/>
-      <c r="U3" s="65"/>
-      <c r="V3" s="65"/>
-      <c r="W3" s="65"/>
-      <c r="X3" s="65"/>
-      <c r="Y3" s="65"/>
-      <c r="Z3" s="65"/>
-      <c r="AA3" s="65"/>
-      <c r="AB3" s="65"/>
-      <c r="AC3" s="65"/>
-      <c r="AD3" s="65"/>
-      <c r="AE3" s="65"/>
-      <c r="AF3" s="65"/>
-      <c r="AG3" s="65"/>
-      <c r="AH3" s="65"/>
-      <c r="AI3" s="65"/>
-      <c r="AJ3" s="65"/>
-      <c r="AK3" s="65"/>
-      <c r="AL3" s="65"/>
-      <c r="AM3" s="65"/>
-      <c r="AN3" s="65"/>
-      <c r="AO3" s="65"/>
-      <c r="AP3" s="66"/>
-      <c r="AQ3" s="67" t="s">
+      <c r="P3" s="102"/>
+      <c r="Q3" s="102"/>
+      <c r="R3" s="102"/>
+      <c r="S3" s="102"/>
+      <c r="T3" s="102"/>
+      <c r="U3" s="102"/>
+      <c r="V3" s="102"/>
+      <c r="W3" s="102"/>
+      <c r="X3" s="102"/>
+      <c r="Y3" s="102"/>
+      <c r="Z3" s="102"/>
+      <c r="AA3" s="102"/>
+      <c r="AB3" s="102"/>
+      <c r="AC3" s="102"/>
+      <c r="AD3" s="102"/>
+      <c r="AE3" s="102"/>
+      <c r="AF3" s="102"/>
+      <c r="AG3" s="102"/>
+      <c r="AH3" s="102"/>
+      <c r="AI3" s="102"/>
+      <c r="AJ3" s="102"/>
+      <c r="AK3" s="102"/>
+      <c r="AL3" s="102"/>
+      <c r="AM3" s="102"/>
+      <c r="AN3" s="102"/>
+      <c r="AO3" s="102"/>
+      <c r="AP3" s="103"/>
+      <c r="AQ3" s="104" t="s">
         <v>5</v>
       </c>
-      <c r="AR3" s="68"/>
-      <c r="AS3" s="68"/>
-      <c r="AT3" s="68"/>
-      <c r="AU3" s="68"/>
-      <c r="AV3" s="68"/>
-      <c r="AW3" s="68"/>
-      <c r="AX3" s="68"/>
-      <c r="AY3" s="68"/>
-      <c r="AZ3" s="68"/>
-      <c r="BA3" s="68"/>
-      <c r="BB3" s="68"/>
-      <c r="BC3" s="68"/>
-      <c r="BD3" s="68"/>
-      <c r="BE3" s="69"/>
+      <c r="AR3" s="105"/>
+      <c r="AS3" s="105"/>
+      <c r="AT3" s="105"/>
+      <c r="AU3" s="105"/>
+      <c r="AV3" s="105"/>
+      <c r="AW3" s="105"/>
+      <c r="AX3" s="105"/>
+      <c r="AY3" s="105"/>
+      <c r="AZ3" s="105"/>
+      <c r="BA3" s="105"/>
+      <c r="BB3" s="105"/>
+      <c r="BC3" s="105"/>
+      <c r="BD3" s="105"/>
+      <c r="BE3" s="106"/>
     </row>
     <row r="4" spans="1:57" ht="15" customHeight="1">
-      <c r="A4" s="90">
+      <c r="A4" s="85">
         <v>1</v>
       </c>
-      <c r="B4" s="91"/>
-      <c r="C4" s="91"/>
-      <c r="D4" s="91"/>
-      <c r="E4" s="91"/>
-      <c r="F4" s="91"/>
-      <c r="G4" s="92"/>
-      <c r="H4" s="93"/>
-      <c r="I4" s="94"/>
-      <c r="J4" s="94"/>
-      <c r="K4" s="94"/>
-      <c r="L4" s="94"/>
-      <c r="M4" s="94"/>
-      <c r="N4" s="95"/>
-      <c r="O4" s="93" t="s">
+      <c r="B4" s="86"/>
+      <c r="C4" s="86"/>
+      <c r="D4" s="86"/>
+      <c r="E4" s="86"/>
+      <c r="F4" s="86"/>
+      <c r="G4" s="87"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="67"/>
+      <c r="K4" s="67"/>
+      <c r="L4" s="67"/>
+      <c r="M4" s="67"/>
+      <c r="N4" s="68"/>
+      <c r="O4" s="66" t="s">
         <v>6</v>
       </c>
-      <c r="P4" s="96"/>
-      <c r="Q4" s="96"/>
-      <c r="R4" s="96"/>
-      <c r="S4" s="96"/>
-      <c r="T4" s="96"/>
-      <c r="U4" s="96"/>
-      <c r="V4" s="96"/>
-      <c r="W4" s="96"/>
-      <c r="X4" s="96"/>
-      <c r="Y4" s="96"/>
-      <c r="Z4" s="96"/>
-      <c r="AA4" s="96"/>
-      <c r="AB4" s="96"/>
-      <c r="AC4" s="96"/>
-      <c r="AD4" s="96"/>
-      <c r="AE4" s="96"/>
-      <c r="AF4" s="96"/>
-      <c r="AG4" s="96"/>
-      <c r="AH4" s="96"/>
-      <c r="AI4" s="96"/>
-      <c r="AJ4" s="96"/>
-      <c r="AK4" s="96"/>
-      <c r="AL4" s="96"/>
-      <c r="AM4" s="96"/>
-      <c r="AN4" s="96"/>
-      <c r="AO4" s="96"/>
-      <c r="AP4" s="97"/>
-      <c r="AQ4" s="98"/>
-      <c r="AR4" s="96"/>
-      <c r="AS4" s="96"/>
-      <c r="AT4" s="96"/>
-      <c r="AU4" s="96"/>
-      <c r="AV4" s="96"/>
-      <c r="AW4" s="96"/>
-      <c r="AX4" s="96"/>
-      <c r="AY4" s="96"/>
-      <c r="AZ4" s="96"/>
-      <c r="BA4" s="96"/>
-      <c r="BB4" s="96"/>
-      <c r="BC4" s="96"/>
-      <c r="BD4" s="96"/>
-      <c r="BE4" s="99"/>
+      <c r="P4" s="69"/>
+      <c r="Q4" s="69"/>
+      <c r="R4" s="69"/>
+      <c r="S4" s="69"/>
+      <c r="T4" s="69"/>
+      <c r="U4" s="69"/>
+      <c r="V4" s="69"/>
+      <c r="W4" s="69"/>
+      <c r="X4" s="69"/>
+      <c r="Y4" s="69"/>
+      <c r="Z4" s="69"/>
+      <c r="AA4" s="69"/>
+      <c r="AB4" s="69"/>
+      <c r="AC4" s="69"/>
+      <c r="AD4" s="69"/>
+      <c r="AE4" s="69"/>
+      <c r="AF4" s="69"/>
+      <c r="AG4" s="69"/>
+      <c r="AH4" s="69"/>
+      <c r="AI4" s="69"/>
+      <c r="AJ4" s="69"/>
+      <c r="AK4" s="69"/>
+      <c r="AL4" s="69"/>
+      <c r="AM4" s="69"/>
+      <c r="AN4" s="69"/>
+      <c r="AO4" s="69"/>
+      <c r="AP4" s="70"/>
+      <c r="AQ4" s="71"/>
+      <c r="AR4" s="69"/>
+      <c r="AS4" s="69"/>
+      <c r="AT4" s="69"/>
+      <c r="AU4" s="69"/>
+      <c r="AV4" s="69"/>
+      <c r="AW4" s="69"/>
+      <c r="AX4" s="69"/>
+      <c r="AY4" s="69"/>
+      <c r="AZ4" s="69"/>
+      <c r="BA4" s="69"/>
+      <c r="BB4" s="69"/>
+      <c r="BC4" s="69"/>
+      <c r="BD4" s="69"/>
+      <c r="BE4" s="72"/>
     </row>
     <row r="5" spans="1:57" ht="15" customHeight="1">
-      <c r="A5" s="70">
+      <c r="A5" s="88">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B5" s="71"/>
-      <c r="C5" s="71"/>
-      <c r="D5" s="71"/>
-      <c r="E5" s="71"/>
-      <c r="F5" s="71"/>
-      <c r="G5" s="72"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="79"/>
-      <c r="J5" s="79"/>
-      <c r="K5" s="79"/>
-      <c r="L5" s="79"/>
-      <c r="M5" s="79"/>
-      <c r="N5" s="80"/>
-      <c r="O5" s="101" t="s">
-        <v>181</v>
-      </c>
-      <c r="P5" s="102"/>
-      <c r="Q5" s="102"/>
-      <c r="R5" s="102"/>
-      <c r="S5" s="102"/>
-      <c r="T5" s="102"/>
-      <c r="U5" s="102"/>
-      <c r="V5" s="102"/>
-      <c r="W5" s="102"/>
-      <c r="X5" s="102"/>
-      <c r="Y5" s="102"/>
-      <c r="Z5" s="102"/>
-      <c r="AA5" s="102"/>
-      <c r="AB5" s="102"/>
-      <c r="AC5" s="102"/>
-      <c r="AD5" s="102"/>
-      <c r="AE5" s="102"/>
-      <c r="AF5" s="102"/>
-      <c r="AG5" s="102"/>
-      <c r="AH5" s="102"/>
-      <c r="AI5" s="102"/>
-      <c r="AJ5" s="102"/>
-      <c r="AK5" s="102"/>
-      <c r="AL5" s="102"/>
-      <c r="AM5" s="102"/>
-      <c r="AN5" s="102"/>
-      <c r="AO5" s="102"/>
-      <c r="AP5" s="103"/>
-      <c r="AQ5" s="104" t="s">
-        <v>182</v>
-      </c>
-      <c r="AR5" s="105"/>
-      <c r="AS5" s="105"/>
-      <c r="AT5" s="105"/>
-      <c r="AU5" s="105"/>
-      <c r="AV5" s="105"/>
-      <c r="AW5" s="105"/>
-      <c r="AX5" s="105"/>
-      <c r="AY5" s="105"/>
-      <c r="AZ5" s="105"/>
-      <c r="BA5" s="105"/>
-      <c r="BB5" s="105"/>
-      <c r="BC5" s="105"/>
-      <c r="BD5" s="105"/>
-      <c r="BE5" s="106"/>
+      <c r="B5" s="89"/>
+      <c r="C5" s="89"/>
+      <c r="D5" s="89"/>
+      <c r="E5" s="89"/>
+      <c r="F5" s="89"/>
+      <c r="G5" s="90"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="64"/>
+      <c r="J5" s="64"/>
+      <c r="K5" s="64"/>
+      <c r="L5" s="64"/>
+      <c r="M5" s="64"/>
+      <c r="N5" s="65"/>
+      <c r="O5" s="76" t="s">
+        <v>179</v>
+      </c>
+      <c r="P5" s="77"/>
+      <c r="Q5" s="77"/>
+      <c r="R5" s="77"/>
+      <c r="S5" s="77"/>
+      <c r="T5" s="77"/>
+      <c r="U5" s="77"/>
+      <c r="V5" s="77"/>
+      <c r="W5" s="77"/>
+      <c r="X5" s="77"/>
+      <c r="Y5" s="77"/>
+      <c r="Z5" s="77"/>
+      <c r="AA5" s="77"/>
+      <c r="AB5" s="77"/>
+      <c r="AC5" s="77"/>
+      <c r="AD5" s="77"/>
+      <c r="AE5" s="77"/>
+      <c r="AF5" s="77"/>
+      <c r="AG5" s="77"/>
+      <c r="AH5" s="77"/>
+      <c r="AI5" s="77"/>
+      <c r="AJ5" s="77"/>
+      <c r="AK5" s="77"/>
+      <c r="AL5" s="77"/>
+      <c r="AM5" s="77"/>
+      <c r="AN5" s="77"/>
+      <c r="AO5" s="77"/>
+      <c r="AP5" s="78"/>
+      <c r="AQ5" s="79" t="s">
+        <v>180</v>
+      </c>
+      <c r="AR5" s="80"/>
+      <c r="AS5" s="80"/>
+      <c r="AT5" s="80"/>
+      <c r="AU5" s="80"/>
+      <c r="AV5" s="80"/>
+      <c r="AW5" s="80"/>
+      <c r="AX5" s="80"/>
+      <c r="AY5" s="80"/>
+      <c r="AZ5" s="80"/>
+      <c r="BA5" s="80"/>
+      <c r="BB5" s="80"/>
+      <c r="BC5" s="80"/>
+      <c r="BD5" s="80"/>
+      <c r="BE5" s="81"/>
     </row>
     <row r="6" spans="1:57" ht="15" customHeight="1">
-      <c r="A6" s="70"/>
-      <c r="B6" s="71"/>
-      <c r="C6" s="71"/>
-      <c r="D6" s="71"/>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="72"/>
-      <c r="H6" s="78"/>
-      <c r="I6" s="79"/>
-      <c r="J6" s="79"/>
-      <c r="K6" s="79"/>
-      <c r="L6" s="79"/>
-      <c r="M6" s="79"/>
-      <c r="N6" s="80"/>
-      <c r="O6" s="78"/>
-      <c r="P6" s="81"/>
-      <c r="Q6" s="81"/>
-      <c r="R6" s="81"/>
-      <c r="S6" s="81"/>
-      <c r="T6" s="81"/>
-      <c r="U6" s="81"/>
-      <c r="V6" s="81"/>
-      <c r="W6" s="81"/>
-      <c r="X6" s="81"/>
-      <c r="Y6" s="81"/>
-      <c r="Z6" s="81"/>
-      <c r="AA6" s="81"/>
-      <c r="AB6" s="81"/>
-      <c r="AC6" s="81"/>
-      <c r="AD6" s="81"/>
-      <c r="AE6" s="81"/>
-      <c r="AF6" s="81"/>
-      <c r="AG6" s="81"/>
-      <c r="AH6" s="81"/>
-      <c r="AI6" s="81"/>
-      <c r="AJ6" s="81"/>
-      <c r="AK6" s="81"/>
-      <c r="AL6" s="81"/>
-      <c r="AM6" s="81"/>
-      <c r="AN6" s="81"/>
-      <c r="AO6" s="81"/>
-      <c r="AP6" s="82"/>
-      <c r="AQ6" s="86"/>
-      <c r="AR6" s="81"/>
-      <c r="AS6" s="81"/>
-      <c r="AT6" s="81"/>
-      <c r="AU6" s="81"/>
-      <c r="AV6" s="81"/>
-      <c r="AW6" s="81"/>
-      <c r="AX6" s="81"/>
-      <c r="AY6" s="81"/>
-      <c r="AZ6" s="81"/>
-      <c r="BA6" s="81"/>
-      <c r="BB6" s="81"/>
-      <c r="BC6" s="81"/>
-      <c r="BD6" s="81"/>
-      <c r="BE6" s="87"/>
+      <c r="A6" s="88"/>
+      <c r="B6" s="89"/>
+      <c r="C6" s="89"/>
+      <c r="D6" s="89"/>
+      <c r="E6" s="89"/>
+      <c r="F6" s="89"/>
+      <c r="G6" s="90"/>
+      <c r="H6" s="62"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="64"/>
+      <c r="L6" s="64"/>
+      <c r="M6" s="64"/>
+      <c r="N6" s="65"/>
+      <c r="O6" s="62"/>
+      <c r="P6" s="60"/>
+      <c r="Q6" s="60"/>
+      <c r="R6" s="60"/>
+      <c r="S6" s="60"/>
+      <c r="T6" s="60"/>
+      <c r="U6" s="60"/>
+      <c r="V6" s="60"/>
+      <c r="W6" s="60"/>
+      <c r="X6" s="60"/>
+      <c r="Y6" s="60"/>
+      <c r="Z6" s="60"/>
+      <c r="AA6" s="60"/>
+      <c r="AB6" s="60"/>
+      <c r="AC6" s="60"/>
+      <c r="AD6" s="60"/>
+      <c r="AE6" s="60"/>
+      <c r="AF6" s="60"/>
+      <c r="AG6" s="60"/>
+      <c r="AH6" s="60"/>
+      <c r="AI6" s="60"/>
+      <c r="AJ6" s="60"/>
+      <c r="AK6" s="60"/>
+      <c r="AL6" s="60"/>
+      <c r="AM6" s="60"/>
+      <c r="AN6" s="60"/>
+      <c r="AO6" s="60"/>
+      <c r="AP6" s="63"/>
+      <c r="AQ6" s="59"/>
+      <c r="AR6" s="60"/>
+      <c r="AS6" s="60"/>
+      <c r="AT6" s="60"/>
+      <c r="AU6" s="60"/>
+      <c r="AV6" s="60"/>
+      <c r="AW6" s="60"/>
+      <c r="AX6" s="60"/>
+      <c r="AY6" s="60"/>
+      <c r="AZ6" s="60"/>
+      <c r="BA6" s="60"/>
+      <c r="BB6" s="60"/>
+      <c r="BC6" s="60"/>
+      <c r="BD6" s="60"/>
+      <c r="BE6" s="61"/>
     </row>
     <row r="7" spans="1:57" ht="15" customHeight="1">
-      <c r="A7" s="70"/>
-      <c r="B7" s="71"/>
-      <c r="C7" s="71"/>
-      <c r="D7" s="71"/>
-      <c r="E7" s="71"/>
-      <c r="F7" s="71"/>
-      <c r="G7" s="72"/>
-      <c r="H7" s="78"/>
-      <c r="I7" s="79"/>
-      <c r="J7" s="79"/>
-      <c r="K7" s="79"/>
-      <c r="L7" s="79"/>
-      <c r="M7" s="79"/>
-      <c r="N7" s="80"/>
-      <c r="O7" s="78"/>
-      <c r="P7" s="81"/>
-      <c r="Q7" s="81"/>
-      <c r="R7" s="81"/>
-      <c r="S7" s="81"/>
-      <c r="T7" s="81"/>
-      <c r="U7" s="81"/>
-      <c r="V7" s="81"/>
-      <c r="W7" s="81"/>
-      <c r="X7" s="81"/>
-      <c r="Y7" s="81"/>
-      <c r="Z7" s="81"/>
-      <c r="AA7" s="81"/>
-      <c r="AB7" s="81"/>
-      <c r="AC7" s="81"/>
-      <c r="AD7" s="81"/>
-      <c r="AE7" s="81"/>
-      <c r="AF7" s="81"/>
-      <c r="AG7" s="81"/>
-      <c r="AH7" s="81"/>
-      <c r="AI7" s="81"/>
-      <c r="AJ7" s="81"/>
-      <c r="AK7" s="81"/>
-      <c r="AL7" s="81"/>
-      <c r="AM7" s="81"/>
-      <c r="AN7" s="81"/>
-      <c r="AO7" s="81"/>
-      <c r="AP7" s="82"/>
-      <c r="AQ7" s="86"/>
-      <c r="AR7" s="81"/>
-      <c r="AS7" s="81"/>
-      <c r="AT7" s="81"/>
-      <c r="AU7" s="81"/>
-      <c r="AV7" s="81"/>
-      <c r="AW7" s="81"/>
-      <c r="AX7" s="81"/>
-      <c r="AY7" s="81"/>
-      <c r="AZ7" s="81"/>
-      <c r="BA7" s="81"/>
-      <c r="BB7" s="81"/>
-      <c r="BC7" s="81"/>
-      <c r="BD7" s="81"/>
-      <c r="BE7" s="87"/>
+      <c r="A7" s="88"/>
+      <c r="B7" s="89"/>
+      <c r="C7" s="89"/>
+      <c r="D7" s="89"/>
+      <c r="E7" s="89"/>
+      <c r="F7" s="89"/>
+      <c r="G7" s="90"/>
+      <c r="H7" s="62"/>
+      <c r="I7" s="64"/>
+      <c r="J7" s="64"/>
+      <c r="K7" s="64"/>
+      <c r="L7" s="64"/>
+      <c r="M7" s="64"/>
+      <c r="N7" s="65"/>
+      <c r="O7" s="62"/>
+      <c r="P7" s="60"/>
+      <c r="Q7" s="60"/>
+      <c r="R7" s="60"/>
+      <c r="S7" s="60"/>
+      <c r="T7" s="60"/>
+      <c r="U7" s="60"/>
+      <c r="V7" s="60"/>
+      <c r="W7" s="60"/>
+      <c r="X7" s="60"/>
+      <c r="Y7" s="60"/>
+      <c r="Z7" s="60"/>
+      <c r="AA7" s="60"/>
+      <c r="AB7" s="60"/>
+      <c r="AC7" s="60"/>
+      <c r="AD7" s="60"/>
+      <c r="AE7" s="60"/>
+      <c r="AF7" s="60"/>
+      <c r="AG7" s="60"/>
+      <c r="AH7" s="60"/>
+      <c r="AI7" s="60"/>
+      <c r="AJ7" s="60"/>
+      <c r="AK7" s="60"/>
+      <c r="AL7" s="60"/>
+      <c r="AM7" s="60"/>
+      <c r="AN7" s="60"/>
+      <c r="AO7" s="60"/>
+      <c r="AP7" s="63"/>
+      <c r="AQ7" s="59"/>
+      <c r="AR7" s="60"/>
+      <c r="AS7" s="60"/>
+      <c r="AT7" s="60"/>
+      <c r="AU7" s="60"/>
+      <c r="AV7" s="60"/>
+      <c r="AW7" s="60"/>
+      <c r="AX7" s="60"/>
+      <c r="AY7" s="60"/>
+      <c r="AZ7" s="60"/>
+      <c r="BA7" s="60"/>
+      <c r="BB7" s="60"/>
+      <c r="BC7" s="60"/>
+      <c r="BD7" s="60"/>
+      <c r="BE7" s="61"/>
     </row>
     <row r="8" spans="1:57" ht="15" customHeight="1">
-      <c r="A8" s="70"/>
-      <c r="B8" s="71"/>
-      <c r="C8" s="71"/>
-      <c r="D8" s="71"/>
-      <c r="E8" s="71"/>
-      <c r="F8" s="71"/>
-      <c r="G8" s="72"/>
-      <c r="H8" s="78"/>
-      <c r="I8" s="79"/>
-      <c r="J8" s="79"/>
-      <c r="K8" s="79"/>
-      <c r="L8" s="79"/>
-      <c r="M8" s="79"/>
-      <c r="N8" s="80"/>
-      <c r="O8" s="78"/>
-      <c r="P8" s="81"/>
-      <c r="Q8" s="81"/>
-      <c r="R8" s="81"/>
-      <c r="S8" s="81"/>
-      <c r="T8" s="81"/>
-      <c r="U8" s="81"/>
-      <c r="V8" s="81"/>
-      <c r="W8" s="81"/>
-      <c r="X8" s="81"/>
-      <c r="Y8" s="81"/>
-      <c r="Z8" s="81"/>
-      <c r="AA8" s="81"/>
-      <c r="AB8" s="81"/>
-      <c r="AC8" s="81"/>
-      <c r="AD8" s="81"/>
-      <c r="AE8" s="81"/>
-      <c r="AF8" s="81"/>
-      <c r="AG8" s="81"/>
-      <c r="AH8" s="81"/>
-      <c r="AI8" s="81"/>
-      <c r="AJ8" s="81"/>
-      <c r="AK8" s="81"/>
-      <c r="AL8" s="81"/>
-      <c r="AM8" s="81"/>
-      <c r="AN8" s="81"/>
-      <c r="AO8" s="81"/>
-      <c r="AP8" s="82"/>
-      <c r="AQ8" s="86"/>
-      <c r="AR8" s="81"/>
-      <c r="AS8" s="81"/>
-      <c r="AT8" s="81"/>
-      <c r="AU8" s="81"/>
-      <c r="AV8" s="81"/>
-      <c r="AW8" s="81"/>
-      <c r="AX8" s="81"/>
-      <c r="AY8" s="81"/>
-      <c r="AZ8" s="81"/>
-      <c r="BA8" s="81"/>
-      <c r="BB8" s="81"/>
-      <c r="BC8" s="81"/>
-      <c r="BD8" s="81"/>
-      <c r="BE8" s="87"/>
+      <c r="A8" s="88"/>
+      <c r="B8" s="89"/>
+      <c r="C8" s="89"/>
+      <c r="D8" s="89"/>
+      <c r="E8" s="89"/>
+      <c r="F8" s="89"/>
+      <c r="G8" s="90"/>
+      <c r="H8" s="62"/>
+      <c r="I8" s="64"/>
+      <c r="J8" s="64"/>
+      <c r="K8" s="64"/>
+      <c r="L8" s="64"/>
+      <c r="M8" s="64"/>
+      <c r="N8" s="65"/>
+      <c r="O8" s="62"/>
+      <c r="P8" s="60"/>
+      <c r="Q8" s="60"/>
+      <c r="R8" s="60"/>
+      <c r="S8" s="60"/>
+      <c r="T8" s="60"/>
+      <c r="U8" s="60"/>
+      <c r="V8" s="60"/>
+      <c r="W8" s="60"/>
+      <c r="X8" s="60"/>
+      <c r="Y8" s="60"/>
+      <c r="Z8" s="60"/>
+      <c r="AA8" s="60"/>
+      <c r="AB8" s="60"/>
+      <c r="AC8" s="60"/>
+      <c r="AD8" s="60"/>
+      <c r="AE8" s="60"/>
+      <c r="AF8" s="60"/>
+      <c r="AG8" s="60"/>
+      <c r="AH8" s="60"/>
+      <c r="AI8" s="60"/>
+      <c r="AJ8" s="60"/>
+      <c r="AK8" s="60"/>
+      <c r="AL8" s="60"/>
+      <c r="AM8" s="60"/>
+      <c r="AN8" s="60"/>
+      <c r="AO8" s="60"/>
+      <c r="AP8" s="63"/>
+      <c r="AQ8" s="59"/>
+      <c r="AR8" s="60"/>
+      <c r="AS8" s="60"/>
+      <c r="AT8" s="60"/>
+      <c r="AU8" s="60"/>
+      <c r="AV8" s="60"/>
+      <c r="AW8" s="60"/>
+      <c r="AX8" s="60"/>
+      <c r="AY8" s="60"/>
+      <c r="AZ8" s="60"/>
+      <c r="BA8" s="60"/>
+      <c r="BB8" s="60"/>
+      <c r="BC8" s="60"/>
+      <c r="BD8" s="60"/>
+      <c r="BE8" s="61"/>
     </row>
     <row r="9" spans="1:57" ht="15" customHeight="1">
-      <c r="A9" s="70"/>
-      <c r="B9" s="71"/>
-      <c r="C9" s="71"/>
-      <c r="D9" s="71"/>
-      <c r="E9" s="71"/>
-      <c r="F9" s="71"/>
-      <c r="G9" s="72"/>
-      <c r="H9" s="78"/>
-      <c r="I9" s="79"/>
-      <c r="J9" s="79"/>
-      <c r="K9" s="79"/>
-      <c r="L9" s="79"/>
-      <c r="M9" s="79"/>
-      <c r="N9" s="80"/>
-      <c r="O9" s="78"/>
-      <c r="P9" s="81"/>
-      <c r="Q9" s="81"/>
-      <c r="R9" s="81"/>
-      <c r="S9" s="81"/>
-      <c r="T9" s="81"/>
-      <c r="U9" s="81"/>
-      <c r="V9" s="81"/>
-      <c r="W9" s="81"/>
-      <c r="X9" s="81"/>
-      <c r="Y9" s="81"/>
-      <c r="Z9" s="81"/>
-      <c r="AA9" s="81"/>
-      <c r="AB9" s="81"/>
-      <c r="AC9" s="81"/>
-      <c r="AD9" s="81"/>
-      <c r="AE9" s="81"/>
-      <c r="AF9" s="81"/>
-      <c r="AG9" s="81"/>
-      <c r="AH9" s="81"/>
-      <c r="AI9" s="81"/>
-      <c r="AJ9" s="81"/>
-      <c r="AK9" s="81"/>
-      <c r="AL9" s="81"/>
-      <c r="AM9" s="81"/>
-      <c r="AN9" s="81"/>
-      <c r="AO9" s="81"/>
-      <c r="AP9" s="82"/>
-      <c r="AQ9" s="86"/>
-      <c r="AR9" s="81"/>
-      <c r="AS9" s="81"/>
-      <c r="AT9" s="81"/>
-      <c r="AU9" s="81"/>
-      <c r="AV9" s="81"/>
-      <c r="AW9" s="81"/>
-      <c r="AX9" s="81"/>
-      <c r="AY9" s="81"/>
-      <c r="AZ9" s="81"/>
-      <c r="BA9" s="81"/>
-      <c r="BB9" s="81"/>
-      <c r="BC9" s="81"/>
-      <c r="BD9" s="81"/>
-      <c r="BE9" s="87"/>
+      <c r="A9" s="88"/>
+      <c r="B9" s="89"/>
+      <c r="C9" s="89"/>
+      <c r="D9" s="89"/>
+      <c r="E9" s="89"/>
+      <c r="F9" s="89"/>
+      <c r="G9" s="90"/>
+      <c r="H9" s="62"/>
+      <c r="I9" s="64"/>
+      <c r="J9" s="64"/>
+      <c r="K9" s="64"/>
+      <c r="L9" s="64"/>
+      <c r="M9" s="64"/>
+      <c r="N9" s="65"/>
+      <c r="O9" s="62"/>
+      <c r="P9" s="60"/>
+      <c r="Q9" s="60"/>
+      <c r="R9" s="60"/>
+      <c r="S9" s="60"/>
+      <c r="T9" s="60"/>
+      <c r="U9" s="60"/>
+      <c r="V9" s="60"/>
+      <c r="W9" s="60"/>
+      <c r="X9" s="60"/>
+      <c r="Y9" s="60"/>
+      <c r="Z9" s="60"/>
+      <c r="AA9" s="60"/>
+      <c r="AB9" s="60"/>
+      <c r="AC9" s="60"/>
+      <c r="AD9" s="60"/>
+      <c r="AE9" s="60"/>
+      <c r="AF9" s="60"/>
+      <c r="AG9" s="60"/>
+      <c r="AH9" s="60"/>
+      <c r="AI9" s="60"/>
+      <c r="AJ9" s="60"/>
+      <c r="AK9" s="60"/>
+      <c r="AL9" s="60"/>
+      <c r="AM9" s="60"/>
+      <c r="AN9" s="60"/>
+      <c r="AO9" s="60"/>
+      <c r="AP9" s="63"/>
+      <c r="AQ9" s="59"/>
+      <c r="AR9" s="60"/>
+      <c r="AS9" s="60"/>
+      <c r="AT9" s="60"/>
+      <c r="AU9" s="60"/>
+      <c r="AV9" s="60"/>
+      <c r="AW9" s="60"/>
+      <c r="AX9" s="60"/>
+      <c r="AY9" s="60"/>
+      <c r="AZ9" s="60"/>
+      <c r="BA9" s="60"/>
+      <c r="BB9" s="60"/>
+      <c r="BC9" s="60"/>
+      <c r="BD9" s="60"/>
+      <c r="BE9" s="61"/>
     </row>
     <row r="10" spans="1:57" ht="15" customHeight="1">
-      <c r="A10" s="70"/>
-      <c r="B10" s="71"/>
-      <c r="C10" s="71"/>
-      <c r="D10" s="71"/>
-      <c r="E10" s="71"/>
-      <c r="F10" s="71"/>
-      <c r="G10" s="72"/>
-      <c r="H10" s="78"/>
-      <c r="I10" s="79"/>
-      <c r="J10" s="79"/>
-      <c r="K10" s="79"/>
-      <c r="L10" s="79"/>
-      <c r="M10" s="79"/>
-      <c r="N10" s="80"/>
-      <c r="O10" s="78"/>
-      <c r="P10" s="81"/>
-      <c r="Q10" s="81"/>
-      <c r="R10" s="81"/>
-      <c r="S10" s="81"/>
-      <c r="T10" s="81"/>
-      <c r="U10" s="81"/>
-      <c r="V10" s="81"/>
-      <c r="W10" s="81"/>
-      <c r="X10" s="81"/>
-      <c r="Y10" s="81"/>
-      <c r="Z10" s="81"/>
-      <c r="AA10" s="81"/>
-      <c r="AB10" s="81"/>
-      <c r="AC10" s="81"/>
-      <c r="AD10" s="81"/>
-      <c r="AE10" s="81"/>
-      <c r="AF10" s="81"/>
-      <c r="AG10" s="81"/>
-      <c r="AH10" s="81"/>
-      <c r="AI10" s="81"/>
-      <c r="AJ10" s="81"/>
-      <c r="AK10" s="81"/>
-      <c r="AL10" s="81"/>
-      <c r="AM10" s="81"/>
-      <c r="AN10" s="81"/>
-      <c r="AO10" s="81"/>
-      <c r="AP10" s="82"/>
-      <c r="AQ10" s="86"/>
-      <c r="AR10" s="81"/>
-      <c r="AS10" s="81"/>
-      <c r="AT10" s="81"/>
-      <c r="AU10" s="81"/>
-      <c r="AV10" s="81"/>
-      <c r="AW10" s="81"/>
-      <c r="AX10" s="81"/>
-      <c r="AY10" s="81"/>
-      <c r="AZ10" s="81"/>
-      <c r="BA10" s="81"/>
-      <c r="BB10" s="81"/>
-      <c r="BC10" s="81"/>
-      <c r="BD10" s="81"/>
-      <c r="BE10" s="87"/>
+      <c r="A10" s="88"/>
+      <c r="B10" s="89"/>
+      <c r="C10" s="89"/>
+      <c r="D10" s="89"/>
+      <c r="E10" s="89"/>
+      <c r="F10" s="89"/>
+      <c r="G10" s="90"/>
+      <c r="H10" s="62"/>
+      <c r="I10" s="64"/>
+      <c r="J10" s="64"/>
+      <c r="K10" s="64"/>
+      <c r="L10" s="64"/>
+      <c r="M10" s="64"/>
+      <c r="N10" s="65"/>
+      <c r="O10" s="62"/>
+      <c r="P10" s="60"/>
+      <c r="Q10" s="60"/>
+      <c r="R10" s="60"/>
+      <c r="S10" s="60"/>
+      <c r="T10" s="60"/>
+      <c r="U10" s="60"/>
+      <c r="V10" s="60"/>
+      <c r="W10" s="60"/>
+      <c r="X10" s="60"/>
+      <c r="Y10" s="60"/>
+      <c r="Z10" s="60"/>
+      <c r="AA10" s="60"/>
+      <c r="AB10" s="60"/>
+      <c r="AC10" s="60"/>
+      <c r="AD10" s="60"/>
+      <c r="AE10" s="60"/>
+      <c r="AF10" s="60"/>
+      <c r="AG10" s="60"/>
+      <c r="AH10" s="60"/>
+      <c r="AI10" s="60"/>
+      <c r="AJ10" s="60"/>
+      <c r="AK10" s="60"/>
+      <c r="AL10" s="60"/>
+      <c r="AM10" s="60"/>
+      <c r="AN10" s="60"/>
+      <c r="AO10" s="60"/>
+      <c r="AP10" s="63"/>
+      <c r="AQ10" s="59"/>
+      <c r="AR10" s="60"/>
+      <c r="AS10" s="60"/>
+      <c r="AT10" s="60"/>
+      <c r="AU10" s="60"/>
+      <c r="AV10" s="60"/>
+      <c r="AW10" s="60"/>
+      <c r="AX10" s="60"/>
+      <c r="AY10" s="60"/>
+      <c r="AZ10" s="60"/>
+      <c r="BA10" s="60"/>
+      <c r="BB10" s="60"/>
+      <c r="BC10" s="60"/>
+      <c r="BD10" s="60"/>
+      <c r="BE10" s="61"/>
     </row>
     <row r="11" spans="1:57" ht="15" customHeight="1">
-      <c r="A11" s="70"/>
-      <c r="B11" s="71"/>
-      <c r="C11" s="71"/>
-      <c r="D11" s="71"/>
-      <c r="E11" s="71"/>
-      <c r="F11" s="71"/>
-      <c r="G11" s="72"/>
-      <c r="H11" s="78"/>
-      <c r="I11" s="79"/>
-      <c r="J11" s="79"/>
-      <c r="K11" s="79"/>
-      <c r="L11" s="79"/>
-      <c r="M11" s="79"/>
-      <c r="N11" s="80"/>
-      <c r="O11" s="78"/>
-      <c r="P11" s="81"/>
-      <c r="Q11" s="81"/>
-      <c r="R11" s="81"/>
-      <c r="S11" s="81"/>
-      <c r="T11" s="81"/>
-      <c r="U11" s="81"/>
-      <c r="V11" s="81"/>
-      <c r="W11" s="81"/>
-      <c r="X11" s="81"/>
-      <c r="Y11" s="81"/>
-      <c r="Z11" s="81"/>
-      <c r="AA11" s="81"/>
-      <c r="AB11" s="81"/>
-      <c r="AC11" s="81"/>
-      <c r="AD11" s="81"/>
-      <c r="AE11" s="81"/>
-      <c r="AF11" s="81"/>
-      <c r="AG11" s="81"/>
-      <c r="AH11" s="81"/>
-      <c r="AI11" s="81"/>
-      <c r="AJ11" s="81"/>
-      <c r="AK11" s="81"/>
-      <c r="AL11" s="81"/>
-      <c r="AM11" s="81"/>
-      <c r="AN11" s="81"/>
-      <c r="AO11" s="81"/>
-      <c r="AP11" s="82"/>
-      <c r="AQ11" s="86"/>
-      <c r="AR11" s="81"/>
-      <c r="AS11" s="81"/>
-      <c r="AT11" s="81"/>
-      <c r="AU11" s="81"/>
-      <c r="AV11" s="81"/>
-      <c r="AW11" s="81"/>
-      <c r="AX11" s="81"/>
-      <c r="AY11" s="81"/>
-      <c r="AZ11" s="81"/>
-      <c r="BA11" s="81"/>
-      <c r="BB11" s="81"/>
-      <c r="BC11" s="81"/>
-      <c r="BD11" s="81"/>
-      <c r="BE11" s="87"/>
+      <c r="A11" s="88"/>
+      <c r="B11" s="89"/>
+      <c r="C11" s="89"/>
+      <c r="D11" s="89"/>
+      <c r="E11" s="89"/>
+      <c r="F11" s="89"/>
+      <c r="G11" s="90"/>
+      <c r="H11" s="62"/>
+      <c r="I11" s="64"/>
+      <c r="J11" s="64"/>
+      <c r="K11" s="64"/>
+      <c r="L11" s="64"/>
+      <c r="M11" s="64"/>
+      <c r="N11" s="65"/>
+      <c r="O11" s="62"/>
+      <c r="P11" s="60"/>
+      <c r="Q11" s="60"/>
+      <c r="R11" s="60"/>
+      <c r="S11" s="60"/>
+      <c r="T11" s="60"/>
+      <c r="U11" s="60"/>
+      <c r="V11" s="60"/>
+      <c r="W11" s="60"/>
+      <c r="X11" s="60"/>
+      <c r="Y11" s="60"/>
+      <c r="Z11" s="60"/>
+      <c r="AA11" s="60"/>
+      <c r="AB11" s="60"/>
+      <c r="AC11" s="60"/>
+      <c r="AD11" s="60"/>
+      <c r="AE11" s="60"/>
+      <c r="AF11" s="60"/>
+      <c r="AG11" s="60"/>
+      <c r="AH11" s="60"/>
+      <c r="AI11" s="60"/>
+      <c r="AJ11" s="60"/>
+      <c r="AK11" s="60"/>
+      <c r="AL11" s="60"/>
+      <c r="AM11" s="60"/>
+      <c r="AN11" s="60"/>
+      <c r="AO11" s="60"/>
+      <c r="AP11" s="63"/>
+      <c r="AQ11" s="59"/>
+      <c r="AR11" s="60"/>
+      <c r="AS11" s="60"/>
+      <c r="AT11" s="60"/>
+      <c r="AU11" s="60"/>
+      <c r="AV11" s="60"/>
+      <c r="AW11" s="60"/>
+      <c r="AX11" s="60"/>
+      <c r="AY11" s="60"/>
+      <c r="AZ11" s="60"/>
+      <c r="BA11" s="60"/>
+      <c r="BB11" s="60"/>
+      <c r="BC11" s="60"/>
+      <c r="BD11" s="60"/>
+      <c r="BE11" s="61"/>
     </row>
     <row r="12" spans="1:57" ht="15" customHeight="1">
-      <c r="A12" s="70"/>
-      <c r="B12" s="71"/>
-      <c r="C12" s="71"/>
-      <c r="D12" s="71"/>
-      <c r="E12" s="71"/>
-      <c r="F12" s="71"/>
-      <c r="G12" s="72"/>
-      <c r="H12" s="78"/>
-      <c r="I12" s="79"/>
-      <c r="J12" s="79"/>
-      <c r="K12" s="79"/>
-      <c r="L12" s="79"/>
-      <c r="M12" s="79"/>
-      <c r="N12" s="80"/>
-      <c r="O12" s="78"/>
-      <c r="P12" s="81"/>
-      <c r="Q12" s="81"/>
-      <c r="R12" s="81"/>
-      <c r="S12" s="81"/>
-      <c r="T12" s="81"/>
-      <c r="U12" s="81"/>
-      <c r="V12" s="81"/>
-      <c r="W12" s="81"/>
-      <c r="X12" s="81"/>
-      <c r="Y12" s="81"/>
-      <c r="Z12" s="81"/>
-      <c r="AA12" s="81"/>
-      <c r="AB12" s="81"/>
-      <c r="AC12" s="81"/>
-      <c r="AD12" s="81"/>
-      <c r="AE12" s="81"/>
-      <c r="AF12" s="81"/>
-      <c r="AG12" s="81"/>
-      <c r="AH12" s="81"/>
-      <c r="AI12" s="81"/>
-      <c r="AJ12" s="81"/>
-      <c r="AK12" s="81"/>
-      <c r="AL12" s="81"/>
-      <c r="AM12" s="81"/>
-      <c r="AN12" s="81"/>
-      <c r="AO12" s="81"/>
-      <c r="AP12" s="82"/>
-      <c r="AQ12" s="86"/>
-      <c r="AR12" s="81"/>
-      <c r="AS12" s="81"/>
-      <c r="AT12" s="81"/>
-      <c r="AU12" s="81"/>
-      <c r="AV12" s="81"/>
-      <c r="AW12" s="81"/>
-      <c r="AX12" s="81"/>
-      <c r="AY12" s="81"/>
-      <c r="AZ12" s="81"/>
-      <c r="BA12" s="81"/>
-      <c r="BB12" s="81"/>
-      <c r="BC12" s="81"/>
-      <c r="BD12" s="81"/>
-      <c r="BE12" s="87"/>
+      <c r="A12" s="88"/>
+      <c r="B12" s="89"/>
+      <c r="C12" s="89"/>
+      <c r="D12" s="89"/>
+      <c r="E12" s="89"/>
+      <c r="F12" s="89"/>
+      <c r="G12" s="90"/>
+      <c r="H12" s="62"/>
+      <c r="I12" s="64"/>
+      <c r="J12" s="64"/>
+      <c r="K12" s="64"/>
+      <c r="L12" s="64"/>
+      <c r="M12" s="64"/>
+      <c r="N12" s="65"/>
+      <c r="O12" s="62"/>
+      <c r="P12" s="60"/>
+      <c r="Q12" s="60"/>
+      <c r="R12" s="60"/>
+      <c r="S12" s="60"/>
+      <c r="T12" s="60"/>
+      <c r="U12" s="60"/>
+      <c r="V12" s="60"/>
+      <c r="W12" s="60"/>
+      <c r="X12" s="60"/>
+      <c r="Y12" s="60"/>
+      <c r="Z12" s="60"/>
+      <c r="AA12" s="60"/>
+      <c r="AB12" s="60"/>
+      <c r="AC12" s="60"/>
+      <c r="AD12" s="60"/>
+      <c r="AE12" s="60"/>
+      <c r="AF12" s="60"/>
+      <c r="AG12" s="60"/>
+      <c r="AH12" s="60"/>
+      <c r="AI12" s="60"/>
+      <c r="AJ12" s="60"/>
+      <c r="AK12" s="60"/>
+      <c r="AL12" s="60"/>
+      <c r="AM12" s="60"/>
+      <c r="AN12" s="60"/>
+      <c r="AO12" s="60"/>
+      <c r="AP12" s="63"/>
+      <c r="AQ12" s="59"/>
+      <c r="AR12" s="60"/>
+      <c r="AS12" s="60"/>
+      <c r="AT12" s="60"/>
+      <c r="AU12" s="60"/>
+      <c r="AV12" s="60"/>
+      <c r="AW12" s="60"/>
+      <c r="AX12" s="60"/>
+      <c r="AY12" s="60"/>
+      <c r="AZ12" s="60"/>
+      <c r="BA12" s="60"/>
+      <c r="BB12" s="60"/>
+      <c r="BC12" s="60"/>
+      <c r="BD12" s="60"/>
+      <c r="BE12" s="61"/>
     </row>
     <row r="13" spans="1:57" ht="15" customHeight="1">
-      <c r="A13" s="70"/>
-      <c r="B13" s="71"/>
-      <c r="C13" s="71"/>
-      <c r="D13" s="71"/>
-      <c r="E13" s="71"/>
-      <c r="F13" s="71"/>
-      <c r="G13" s="72"/>
-      <c r="H13" s="78"/>
-      <c r="I13" s="79"/>
-      <c r="J13" s="79"/>
-      <c r="K13" s="79"/>
-      <c r="L13" s="79"/>
-      <c r="M13" s="79"/>
-      <c r="N13" s="80"/>
-      <c r="O13" s="78"/>
-      <c r="P13" s="81"/>
-      <c r="Q13" s="81"/>
-      <c r="R13" s="81"/>
-      <c r="S13" s="81"/>
-      <c r="T13" s="81"/>
-      <c r="U13" s="81"/>
-      <c r="V13" s="81"/>
-      <c r="W13" s="81"/>
-      <c r="X13" s="81"/>
-      <c r="Y13" s="81"/>
-      <c r="Z13" s="81"/>
-      <c r="AA13" s="81"/>
-      <c r="AB13" s="81"/>
-      <c r="AC13" s="81"/>
-      <c r="AD13" s="81"/>
-      <c r="AE13" s="81"/>
-      <c r="AF13" s="81"/>
-      <c r="AG13" s="81"/>
-      <c r="AH13" s="81"/>
-      <c r="AI13" s="81"/>
-      <c r="AJ13" s="81"/>
-      <c r="AK13" s="81"/>
-      <c r="AL13" s="81"/>
-      <c r="AM13" s="81"/>
-      <c r="AN13" s="81"/>
-      <c r="AO13" s="81"/>
-      <c r="AP13" s="82"/>
-      <c r="AQ13" s="86"/>
-      <c r="AR13" s="81"/>
-      <c r="AS13" s="81"/>
-      <c r="AT13" s="81"/>
-      <c r="AU13" s="81"/>
-      <c r="AV13" s="81"/>
-      <c r="AW13" s="81"/>
-      <c r="AX13" s="81"/>
-      <c r="AY13" s="81"/>
-      <c r="AZ13" s="81"/>
-      <c r="BA13" s="81"/>
-      <c r="BB13" s="81"/>
-      <c r="BC13" s="81"/>
-      <c r="BD13" s="81"/>
-      <c r="BE13" s="87"/>
+      <c r="A13" s="88"/>
+      <c r="B13" s="89"/>
+      <c r="C13" s="89"/>
+      <c r="D13" s="89"/>
+      <c r="E13" s="89"/>
+      <c r="F13" s="89"/>
+      <c r="G13" s="90"/>
+      <c r="H13" s="62"/>
+      <c r="I13" s="64"/>
+      <c r="J13" s="64"/>
+      <c r="K13" s="64"/>
+      <c r="L13" s="64"/>
+      <c r="M13" s="64"/>
+      <c r="N13" s="65"/>
+      <c r="O13" s="62"/>
+      <c r="P13" s="60"/>
+      <c r="Q13" s="60"/>
+      <c r="R13" s="60"/>
+      <c r="S13" s="60"/>
+      <c r="T13" s="60"/>
+      <c r="U13" s="60"/>
+      <c r="V13" s="60"/>
+      <c r="W13" s="60"/>
+      <c r="X13" s="60"/>
+      <c r="Y13" s="60"/>
+      <c r="Z13" s="60"/>
+      <c r="AA13" s="60"/>
+      <c r="AB13" s="60"/>
+      <c r="AC13" s="60"/>
+      <c r="AD13" s="60"/>
+      <c r="AE13" s="60"/>
+      <c r="AF13" s="60"/>
+      <c r="AG13" s="60"/>
+      <c r="AH13" s="60"/>
+      <c r="AI13" s="60"/>
+      <c r="AJ13" s="60"/>
+      <c r="AK13" s="60"/>
+      <c r="AL13" s="60"/>
+      <c r="AM13" s="60"/>
+      <c r="AN13" s="60"/>
+      <c r="AO13" s="60"/>
+      <c r="AP13" s="63"/>
+      <c r="AQ13" s="59"/>
+      <c r="AR13" s="60"/>
+      <c r="AS13" s="60"/>
+      <c r="AT13" s="60"/>
+      <c r="AU13" s="60"/>
+      <c r="AV13" s="60"/>
+      <c r="AW13" s="60"/>
+      <c r="AX13" s="60"/>
+      <c r="AY13" s="60"/>
+      <c r="AZ13" s="60"/>
+      <c r="BA13" s="60"/>
+      <c r="BB13" s="60"/>
+      <c r="BC13" s="60"/>
+      <c r="BD13" s="60"/>
+      <c r="BE13" s="61"/>
     </row>
     <row r="14" spans="1:57" ht="15" customHeight="1">
-      <c r="A14" s="70"/>
-      <c r="B14" s="71"/>
-      <c r="C14" s="71"/>
-      <c r="D14" s="71"/>
-      <c r="E14" s="71"/>
-      <c r="F14" s="71"/>
-      <c r="G14" s="72"/>
-      <c r="H14" s="78"/>
-      <c r="I14" s="79"/>
-      <c r="J14" s="79"/>
-      <c r="K14" s="79"/>
-      <c r="L14" s="79"/>
-      <c r="M14" s="79"/>
-      <c r="N14" s="80"/>
-      <c r="O14" s="78"/>
-      <c r="P14" s="81"/>
-      <c r="Q14" s="81"/>
-      <c r="R14" s="81"/>
-      <c r="S14" s="81"/>
-      <c r="T14" s="81"/>
-      <c r="U14" s="81"/>
-      <c r="V14" s="81"/>
-      <c r="W14" s="81"/>
-      <c r="X14" s="81"/>
-      <c r="Y14" s="81"/>
-      <c r="Z14" s="81"/>
-      <c r="AA14" s="81"/>
-      <c r="AB14" s="81"/>
-      <c r="AC14" s="81"/>
-      <c r="AD14" s="81"/>
-      <c r="AE14" s="81"/>
-      <c r="AF14" s="81"/>
-      <c r="AG14" s="81"/>
-      <c r="AH14" s="81"/>
-      <c r="AI14" s="81"/>
-      <c r="AJ14" s="81"/>
-      <c r="AK14" s="81"/>
-      <c r="AL14" s="81"/>
-      <c r="AM14" s="81"/>
-      <c r="AN14" s="81"/>
-      <c r="AO14" s="81"/>
-      <c r="AP14" s="82"/>
-      <c r="AQ14" s="86"/>
-      <c r="AR14" s="81"/>
-      <c r="AS14" s="81"/>
-      <c r="AT14" s="81"/>
-      <c r="AU14" s="81"/>
-      <c r="AV14" s="81"/>
-      <c r="AW14" s="81"/>
-      <c r="AX14" s="81"/>
-      <c r="AY14" s="81"/>
-      <c r="AZ14" s="81"/>
-      <c r="BA14" s="81"/>
-      <c r="BB14" s="81"/>
-      <c r="BC14" s="81"/>
-      <c r="BD14" s="81"/>
-      <c r="BE14" s="87"/>
+      <c r="A14" s="88"/>
+      <c r="B14" s="89"/>
+      <c r="C14" s="89"/>
+      <c r="D14" s="89"/>
+      <c r="E14" s="89"/>
+      <c r="F14" s="89"/>
+      <c r="G14" s="90"/>
+      <c r="H14" s="62"/>
+      <c r="I14" s="64"/>
+      <c r="J14" s="64"/>
+      <c r="K14" s="64"/>
+      <c r="L14" s="64"/>
+      <c r="M14" s="64"/>
+      <c r="N14" s="65"/>
+      <c r="O14" s="62"/>
+      <c r="P14" s="60"/>
+      <c r="Q14" s="60"/>
+      <c r="R14" s="60"/>
+      <c r="S14" s="60"/>
+      <c r="T14" s="60"/>
+      <c r="U14" s="60"/>
+      <c r="V14" s="60"/>
+      <c r="W14" s="60"/>
+      <c r="X14" s="60"/>
+      <c r="Y14" s="60"/>
+      <c r="Z14" s="60"/>
+      <c r="AA14" s="60"/>
+      <c r="AB14" s="60"/>
+      <c r="AC14" s="60"/>
+      <c r="AD14" s="60"/>
+      <c r="AE14" s="60"/>
+      <c r="AF14" s="60"/>
+      <c r="AG14" s="60"/>
+      <c r="AH14" s="60"/>
+      <c r="AI14" s="60"/>
+      <c r="AJ14" s="60"/>
+      <c r="AK14" s="60"/>
+      <c r="AL14" s="60"/>
+      <c r="AM14" s="60"/>
+      <c r="AN14" s="60"/>
+      <c r="AO14" s="60"/>
+      <c r="AP14" s="63"/>
+      <c r="AQ14" s="59"/>
+      <c r="AR14" s="60"/>
+      <c r="AS14" s="60"/>
+      <c r="AT14" s="60"/>
+      <c r="AU14" s="60"/>
+      <c r="AV14" s="60"/>
+      <c r="AW14" s="60"/>
+      <c r="AX14" s="60"/>
+      <c r="AY14" s="60"/>
+      <c r="AZ14" s="60"/>
+      <c r="BA14" s="60"/>
+      <c r="BB14" s="60"/>
+      <c r="BC14" s="60"/>
+      <c r="BD14" s="60"/>
+      <c r="BE14" s="61"/>
     </row>
     <row r="15" spans="1:57" ht="15" customHeight="1">
-      <c r="A15" s="70"/>
-      <c r="B15" s="71"/>
-      <c r="C15" s="71"/>
-      <c r="D15" s="71"/>
-      <c r="E15" s="71"/>
-      <c r="F15" s="71"/>
-      <c r="G15" s="72"/>
-      <c r="H15" s="78"/>
-      <c r="I15" s="79"/>
-      <c r="J15" s="79"/>
-      <c r="K15" s="79"/>
-      <c r="L15" s="79"/>
-      <c r="M15" s="79"/>
-      <c r="N15" s="80"/>
-      <c r="O15" s="78"/>
-      <c r="P15" s="81"/>
-      <c r="Q15" s="81"/>
-      <c r="R15" s="81"/>
-      <c r="S15" s="81"/>
-      <c r="T15" s="81"/>
-      <c r="U15" s="81"/>
-      <c r="V15" s="81"/>
-      <c r="W15" s="81"/>
-      <c r="X15" s="81"/>
-      <c r="Y15" s="81"/>
-      <c r="Z15" s="81"/>
-      <c r="AA15" s="81"/>
-      <c r="AB15" s="81"/>
-      <c r="AC15" s="81"/>
-      <c r="AD15" s="81"/>
-      <c r="AE15" s="81"/>
-      <c r="AF15" s="81"/>
-      <c r="AG15" s="81"/>
-      <c r="AH15" s="81"/>
-      <c r="AI15" s="81"/>
-      <c r="AJ15" s="81"/>
-      <c r="AK15" s="81"/>
-      <c r="AL15" s="81"/>
-      <c r="AM15" s="81"/>
-      <c r="AN15" s="81"/>
-      <c r="AO15" s="81"/>
-      <c r="AP15" s="82"/>
-      <c r="AQ15" s="86"/>
-      <c r="AR15" s="81"/>
-      <c r="AS15" s="81"/>
-      <c r="AT15" s="81"/>
-      <c r="AU15" s="81"/>
-      <c r="AV15" s="81"/>
-      <c r="AW15" s="81"/>
-      <c r="AX15" s="81"/>
-      <c r="AY15" s="81"/>
-      <c r="AZ15" s="81"/>
-      <c r="BA15" s="81"/>
-      <c r="BB15" s="81"/>
-      <c r="BC15" s="81"/>
-      <c r="BD15" s="81"/>
-      <c r="BE15" s="87"/>
+      <c r="A15" s="88"/>
+      <c r="B15" s="89"/>
+      <c r="C15" s="89"/>
+      <c r="D15" s="89"/>
+      <c r="E15" s="89"/>
+      <c r="F15" s="89"/>
+      <c r="G15" s="90"/>
+      <c r="H15" s="62"/>
+      <c r="I15" s="64"/>
+      <c r="J15" s="64"/>
+      <c r="K15" s="64"/>
+      <c r="L15" s="64"/>
+      <c r="M15" s="64"/>
+      <c r="N15" s="65"/>
+      <c r="O15" s="62"/>
+      <c r="P15" s="60"/>
+      <c r="Q15" s="60"/>
+      <c r="R15" s="60"/>
+      <c r="S15" s="60"/>
+      <c r="T15" s="60"/>
+      <c r="U15" s="60"/>
+      <c r="V15" s="60"/>
+      <c r="W15" s="60"/>
+      <c r="X15" s="60"/>
+      <c r="Y15" s="60"/>
+      <c r="Z15" s="60"/>
+      <c r="AA15" s="60"/>
+      <c r="AB15" s="60"/>
+      <c r="AC15" s="60"/>
+      <c r="AD15" s="60"/>
+      <c r="AE15" s="60"/>
+      <c r="AF15" s="60"/>
+      <c r="AG15" s="60"/>
+      <c r="AH15" s="60"/>
+      <c r="AI15" s="60"/>
+      <c r="AJ15" s="60"/>
+      <c r="AK15" s="60"/>
+      <c r="AL15" s="60"/>
+      <c r="AM15" s="60"/>
+      <c r="AN15" s="60"/>
+      <c r="AO15" s="60"/>
+      <c r="AP15" s="63"/>
+      <c r="AQ15" s="59"/>
+      <c r="AR15" s="60"/>
+      <c r="AS15" s="60"/>
+      <c r="AT15" s="60"/>
+      <c r="AU15" s="60"/>
+      <c r="AV15" s="60"/>
+      <c r="AW15" s="60"/>
+      <c r="AX15" s="60"/>
+      <c r="AY15" s="60"/>
+      <c r="AZ15" s="60"/>
+      <c r="BA15" s="60"/>
+      <c r="BB15" s="60"/>
+      <c r="BC15" s="60"/>
+      <c r="BD15" s="60"/>
+      <c r="BE15" s="61"/>
     </row>
     <row r="16" spans="1:57" ht="15" customHeight="1">
-      <c r="A16" s="70"/>
-      <c r="B16" s="71"/>
-      <c r="C16" s="71"/>
-      <c r="D16" s="71"/>
-      <c r="E16" s="71"/>
-      <c r="F16" s="71"/>
-      <c r="G16" s="72"/>
-      <c r="H16" s="78"/>
-      <c r="I16" s="79"/>
-      <c r="J16" s="79"/>
-      <c r="K16" s="79"/>
-      <c r="L16" s="79"/>
-      <c r="M16" s="79"/>
-      <c r="N16" s="80"/>
-      <c r="O16" s="78"/>
-      <c r="P16" s="81"/>
-      <c r="Q16" s="81"/>
-      <c r="R16" s="81"/>
-      <c r="S16" s="81"/>
-      <c r="T16" s="81"/>
-      <c r="U16" s="81"/>
-      <c r="V16" s="81"/>
-      <c r="W16" s="81"/>
-      <c r="X16" s="81"/>
-      <c r="Y16" s="81"/>
-      <c r="Z16" s="81"/>
-      <c r="AA16" s="81"/>
-      <c r="AB16" s="81"/>
-      <c r="AC16" s="81"/>
-      <c r="AD16" s="81"/>
-      <c r="AE16" s="81"/>
-      <c r="AF16" s="81"/>
-      <c r="AG16" s="81"/>
-      <c r="AH16" s="81"/>
-      <c r="AI16" s="81"/>
-      <c r="AJ16" s="81"/>
-      <c r="AK16" s="81"/>
-      <c r="AL16" s="81"/>
-      <c r="AM16" s="81"/>
-      <c r="AN16" s="81"/>
-      <c r="AO16" s="81"/>
-      <c r="AP16" s="82"/>
-      <c r="AQ16" s="86"/>
-      <c r="AR16" s="81"/>
-      <c r="AS16" s="81"/>
-      <c r="AT16" s="81"/>
-      <c r="AU16" s="81"/>
-      <c r="AV16" s="81"/>
-      <c r="AW16" s="81"/>
-      <c r="AX16" s="81"/>
-      <c r="AY16" s="81"/>
-      <c r="AZ16" s="81"/>
-      <c r="BA16" s="81"/>
-      <c r="BB16" s="81"/>
-      <c r="BC16" s="81"/>
-      <c r="BD16" s="81"/>
-      <c r="BE16" s="87"/>
+      <c r="A16" s="88"/>
+      <c r="B16" s="89"/>
+      <c r="C16" s="89"/>
+      <c r="D16" s="89"/>
+      <c r="E16" s="89"/>
+      <c r="F16" s="89"/>
+      <c r="G16" s="90"/>
+      <c r="H16" s="62"/>
+      <c r="I16" s="64"/>
+      <c r="J16" s="64"/>
+      <c r="K16" s="64"/>
+      <c r="L16" s="64"/>
+      <c r="M16" s="64"/>
+      <c r="N16" s="65"/>
+      <c r="O16" s="62"/>
+      <c r="P16" s="60"/>
+      <c r="Q16" s="60"/>
+      <c r="R16" s="60"/>
+      <c r="S16" s="60"/>
+      <c r="T16" s="60"/>
+      <c r="U16" s="60"/>
+      <c r="V16" s="60"/>
+      <c r="W16" s="60"/>
+      <c r="X16" s="60"/>
+      <c r="Y16" s="60"/>
+      <c r="Z16" s="60"/>
+      <c r="AA16" s="60"/>
+      <c r="AB16" s="60"/>
+      <c r="AC16" s="60"/>
+      <c r="AD16" s="60"/>
+      <c r="AE16" s="60"/>
+      <c r="AF16" s="60"/>
+      <c r="AG16" s="60"/>
+      <c r="AH16" s="60"/>
+      <c r="AI16" s="60"/>
+      <c r="AJ16" s="60"/>
+      <c r="AK16" s="60"/>
+      <c r="AL16" s="60"/>
+      <c r="AM16" s="60"/>
+      <c r="AN16" s="60"/>
+      <c r="AO16" s="60"/>
+      <c r="AP16" s="63"/>
+      <c r="AQ16" s="59"/>
+      <c r="AR16" s="60"/>
+      <c r="AS16" s="60"/>
+      <c r="AT16" s="60"/>
+      <c r="AU16" s="60"/>
+      <c r="AV16" s="60"/>
+      <c r="AW16" s="60"/>
+      <c r="AX16" s="60"/>
+      <c r="AY16" s="60"/>
+      <c r="AZ16" s="60"/>
+      <c r="BA16" s="60"/>
+      <c r="BB16" s="60"/>
+      <c r="BC16" s="60"/>
+      <c r="BD16" s="60"/>
+      <c r="BE16" s="61"/>
     </row>
     <row r="17" spans="1:57" ht="15" customHeight="1">
-      <c r="A17" s="70"/>
-      <c r="B17" s="71"/>
-      <c r="C17" s="71"/>
-      <c r="D17" s="71"/>
-      <c r="E17" s="71"/>
-      <c r="F17" s="71"/>
-      <c r="G17" s="72"/>
-      <c r="H17" s="78"/>
-      <c r="I17" s="79"/>
-      <c r="J17" s="79"/>
-      <c r="K17" s="79"/>
-      <c r="L17" s="79"/>
-      <c r="M17" s="79"/>
-      <c r="N17" s="80"/>
-      <c r="O17" s="78"/>
-      <c r="P17" s="81"/>
-      <c r="Q17" s="81"/>
-      <c r="R17" s="81"/>
-      <c r="S17" s="81"/>
-      <c r="T17" s="81"/>
-      <c r="U17" s="81"/>
-      <c r="V17" s="81"/>
-      <c r="W17" s="81"/>
-      <c r="X17" s="81"/>
-      <c r="Y17" s="81"/>
-      <c r="Z17" s="81"/>
-      <c r="AA17" s="81"/>
-      <c r="AB17" s="81"/>
-      <c r="AC17" s="81"/>
-      <c r="AD17" s="81"/>
-      <c r="AE17" s="81"/>
-      <c r="AF17" s="81"/>
-      <c r="AG17" s="81"/>
-      <c r="AH17" s="81"/>
-      <c r="AI17" s="81"/>
-      <c r="AJ17" s="81"/>
-      <c r="AK17" s="81"/>
-      <c r="AL17" s="81"/>
-      <c r="AM17" s="81"/>
-      <c r="AN17" s="81"/>
-      <c r="AO17" s="81"/>
-      <c r="AP17" s="82"/>
-      <c r="AQ17" s="86"/>
-      <c r="AR17" s="81"/>
-      <c r="AS17" s="81"/>
-      <c r="AT17" s="81"/>
-      <c r="AU17" s="81"/>
-      <c r="AV17" s="81"/>
-      <c r="AW17" s="81"/>
-      <c r="AX17" s="81"/>
-      <c r="AY17" s="81"/>
-      <c r="AZ17" s="81"/>
-      <c r="BA17" s="81"/>
-      <c r="BB17" s="81"/>
-      <c r="BC17" s="81"/>
-      <c r="BD17" s="81"/>
-      <c r="BE17" s="87"/>
+      <c r="A17" s="88"/>
+      <c r="B17" s="89"/>
+      <c r="C17" s="89"/>
+      <c r="D17" s="89"/>
+      <c r="E17" s="89"/>
+      <c r="F17" s="89"/>
+      <c r="G17" s="90"/>
+      <c r="H17" s="62"/>
+      <c r="I17" s="64"/>
+      <c r="J17" s="64"/>
+      <c r="K17" s="64"/>
+      <c r="L17" s="64"/>
+      <c r="M17" s="64"/>
+      <c r="N17" s="65"/>
+      <c r="O17" s="62"/>
+      <c r="P17" s="60"/>
+      <c r="Q17" s="60"/>
+      <c r="R17" s="60"/>
+      <c r="S17" s="60"/>
+      <c r="T17" s="60"/>
+      <c r="U17" s="60"/>
+      <c r="V17" s="60"/>
+      <c r="W17" s="60"/>
+      <c r="X17" s="60"/>
+      <c r="Y17" s="60"/>
+      <c r="Z17" s="60"/>
+      <c r="AA17" s="60"/>
+      <c r="AB17" s="60"/>
+      <c r="AC17" s="60"/>
+      <c r="AD17" s="60"/>
+      <c r="AE17" s="60"/>
+      <c r="AF17" s="60"/>
+      <c r="AG17" s="60"/>
+      <c r="AH17" s="60"/>
+      <c r="AI17" s="60"/>
+      <c r="AJ17" s="60"/>
+      <c r="AK17" s="60"/>
+      <c r="AL17" s="60"/>
+      <c r="AM17" s="60"/>
+      <c r="AN17" s="60"/>
+      <c r="AO17" s="60"/>
+      <c r="AP17" s="63"/>
+      <c r="AQ17" s="59"/>
+      <c r="AR17" s="60"/>
+      <c r="AS17" s="60"/>
+      <c r="AT17" s="60"/>
+      <c r="AU17" s="60"/>
+      <c r="AV17" s="60"/>
+      <c r="AW17" s="60"/>
+      <c r="AX17" s="60"/>
+      <c r="AY17" s="60"/>
+      <c r="AZ17" s="60"/>
+      <c r="BA17" s="60"/>
+      <c r="BB17" s="60"/>
+      <c r="BC17" s="60"/>
+      <c r="BD17" s="60"/>
+      <c r="BE17" s="61"/>
     </row>
     <row r="18" spans="1:57" ht="15" customHeight="1">
-      <c r="A18" s="70"/>
-      <c r="B18" s="71"/>
-      <c r="C18" s="71"/>
-      <c r="D18" s="71"/>
-      <c r="E18" s="71"/>
-      <c r="F18" s="71"/>
-      <c r="G18" s="72"/>
-      <c r="H18" s="78"/>
-      <c r="I18" s="79"/>
-      <c r="J18" s="79"/>
-      <c r="K18" s="79"/>
-      <c r="L18" s="79"/>
-      <c r="M18" s="79"/>
-      <c r="N18" s="80"/>
-      <c r="O18" s="78"/>
-      <c r="P18" s="81"/>
-      <c r="Q18" s="81"/>
-      <c r="R18" s="81"/>
-      <c r="S18" s="81"/>
-      <c r="T18" s="81"/>
-      <c r="U18" s="81"/>
-      <c r="V18" s="81"/>
-      <c r="W18" s="81"/>
-      <c r="X18" s="81"/>
-      <c r="Y18" s="81"/>
-      <c r="Z18" s="81"/>
-      <c r="AA18" s="81"/>
-      <c r="AB18" s="81"/>
-      <c r="AC18" s="81"/>
-      <c r="AD18" s="81"/>
-      <c r="AE18" s="81"/>
-      <c r="AF18" s="81"/>
-      <c r="AG18" s="81"/>
-      <c r="AH18" s="81"/>
-      <c r="AI18" s="81"/>
-      <c r="AJ18" s="81"/>
-      <c r="AK18" s="81"/>
-      <c r="AL18" s="81"/>
-      <c r="AM18" s="81"/>
-      <c r="AN18" s="81"/>
-      <c r="AO18" s="81"/>
-      <c r="AP18" s="82"/>
-      <c r="AQ18" s="86"/>
-      <c r="AR18" s="81"/>
-      <c r="AS18" s="81"/>
-      <c r="AT18" s="81"/>
-      <c r="AU18" s="81"/>
-      <c r="AV18" s="81"/>
-      <c r="AW18" s="81"/>
-      <c r="AX18" s="81"/>
-      <c r="AY18" s="81"/>
-      <c r="AZ18" s="81"/>
-      <c r="BA18" s="81"/>
-      <c r="BB18" s="81"/>
-      <c r="BC18" s="81"/>
-      <c r="BD18" s="81"/>
-      <c r="BE18" s="87"/>
+      <c r="A18" s="88"/>
+      <c r="B18" s="89"/>
+      <c r="C18" s="89"/>
+      <c r="D18" s="89"/>
+      <c r="E18" s="89"/>
+      <c r="F18" s="89"/>
+      <c r="G18" s="90"/>
+      <c r="H18" s="62"/>
+      <c r="I18" s="64"/>
+      <c r="J18" s="64"/>
+      <c r="K18" s="64"/>
+      <c r="L18" s="64"/>
+      <c r="M18" s="64"/>
+      <c r="N18" s="65"/>
+      <c r="O18" s="62"/>
+      <c r="P18" s="60"/>
+      <c r="Q18" s="60"/>
+      <c r="R18" s="60"/>
+      <c r="S18" s="60"/>
+      <c r="T18" s="60"/>
+      <c r="U18" s="60"/>
+      <c r="V18" s="60"/>
+      <c r="W18" s="60"/>
+      <c r="X18" s="60"/>
+      <c r="Y18" s="60"/>
+      <c r="Z18" s="60"/>
+      <c r="AA18" s="60"/>
+      <c r="AB18" s="60"/>
+      <c r="AC18" s="60"/>
+      <c r="AD18" s="60"/>
+      <c r="AE18" s="60"/>
+      <c r="AF18" s="60"/>
+      <c r="AG18" s="60"/>
+      <c r="AH18" s="60"/>
+      <c r="AI18" s="60"/>
+      <c r="AJ18" s="60"/>
+      <c r="AK18" s="60"/>
+      <c r="AL18" s="60"/>
+      <c r="AM18" s="60"/>
+      <c r="AN18" s="60"/>
+      <c r="AO18" s="60"/>
+      <c r="AP18" s="63"/>
+      <c r="AQ18" s="59"/>
+      <c r="AR18" s="60"/>
+      <c r="AS18" s="60"/>
+      <c r="AT18" s="60"/>
+      <c r="AU18" s="60"/>
+      <c r="AV18" s="60"/>
+      <c r="AW18" s="60"/>
+      <c r="AX18" s="60"/>
+      <c r="AY18" s="60"/>
+      <c r="AZ18" s="60"/>
+      <c r="BA18" s="60"/>
+      <c r="BB18" s="60"/>
+      <c r="BC18" s="60"/>
+      <c r="BD18" s="60"/>
+      <c r="BE18" s="61"/>
     </row>
     <row r="19" spans="1:57" ht="15" customHeight="1">
-      <c r="A19" s="70"/>
-      <c r="B19" s="71"/>
-      <c r="C19" s="71"/>
-      <c r="D19" s="71"/>
-      <c r="E19" s="71"/>
-      <c r="F19" s="71"/>
-      <c r="G19" s="72"/>
-      <c r="H19" s="78"/>
-      <c r="I19" s="79"/>
-      <c r="J19" s="79"/>
-      <c r="K19" s="79"/>
-      <c r="L19" s="79"/>
-      <c r="M19" s="79"/>
-      <c r="N19" s="80"/>
-      <c r="O19" s="78"/>
-      <c r="P19" s="81"/>
-      <c r="Q19" s="81"/>
-      <c r="R19" s="81"/>
-      <c r="S19" s="81"/>
-      <c r="T19" s="81"/>
-      <c r="U19" s="81"/>
-      <c r="V19" s="81"/>
-      <c r="W19" s="81"/>
-      <c r="X19" s="81"/>
-      <c r="Y19" s="81"/>
-      <c r="Z19" s="81"/>
-      <c r="AA19" s="81"/>
-      <c r="AB19" s="81"/>
-      <c r="AC19" s="81"/>
-      <c r="AD19" s="81"/>
-      <c r="AE19" s="81"/>
-      <c r="AF19" s="81"/>
-      <c r="AG19" s="81"/>
-      <c r="AH19" s="81"/>
-      <c r="AI19" s="81"/>
-      <c r="AJ19" s="81"/>
-      <c r="AK19" s="81"/>
-      <c r="AL19" s="81"/>
-      <c r="AM19" s="81"/>
-      <c r="AN19" s="81"/>
-      <c r="AO19" s="81"/>
-      <c r="AP19" s="82"/>
-      <c r="AQ19" s="86"/>
-      <c r="AR19" s="81"/>
-      <c r="AS19" s="81"/>
-      <c r="AT19" s="81"/>
-      <c r="AU19" s="81"/>
-      <c r="AV19" s="81"/>
-      <c r="AW19" s="81"/>
-      <c r="AX19" s="81"/>
-      <c r="AY19" s="81"/>
-      <c r="AZ19" s="81"/>
-      <c r="BA19" s="81"/>
-      <c r="BB19" s="81"/>
-      <c r="BC19" s="81"/>
-      <c r="BD19" s="81"/>
-      <c r="BE19" s="87"/>
+      <c r="A19" s="88"/>
+      <c r="B19" s="89"/>
+      <c r="C19" s="89"/>
+      <c r="D19" s="89"/>
+      <c r="E19" s="89"/>
+      <c r="F19" s="89"/>
+      <c r="G19" s="90"/>
+      <c r="H19" s="62"/>
+      <c r="I19" s="64"/>
+      <c r="J19" s="64"/>
+      <c r="K19" s="64"/>
+      <c r="L19" s="64"/>
+      <c r="M19" s="64"/>
+      <c r="N19" s="65"/>
+      <c r="O19" s="62"/>
+      <c r="P19" s="60"/>
+      <c r="Q19" s="60"/>
+      <c r="R19" s="60"/>
+      <c r="S19" s="60"/>
+      <c r="T19" s="60"/>
+      <c r="U19" s="60"/>
+      <c r="V19" s="60"/>
+      <c r="W19" s="60"/>
+      <c r="X19" s="60"/>
+      <c r="Y19" s="60"/>
+      <c r="Z19" s="60"/>
+      <c r="AA19" s="60"/>
+      <c r="AB19" s="60"/>
+      <c r="AC19" s="60"/>
+      <c r="AD19" s="60"/>
+      <c r="AE19" s="60"/>
+      <c r="AF19" s="60"/>
+      <c r="AG19" s="60"/>
+      <c r="AH19" s="60"/>
+      <c r="AI19" s="60"/>
+      <c r="AJ19" s="60"/>
+      <c r="AK19" s="60"/>
+      <c r="AL19" s="60"/>
+      <c r="AM19" s="60"/>
+      <c r="AN19" s="60"/>
+      <c r="AO19" s="60"/>
+      <c r="AP19" s="63"/>
+      <c r="AQ19" s="59"/>
+      <c r="AR19" s="60"/>
+      <c r="AS19" s="60"/>
+      <c r="AT19" s="60"/>
+      <c r="AU19" s="60"/>
+      <c r="AV19" s="60"/>
+      <c r="AW19" s="60"/>
+      <c r="AX19" s="60"/>
+      <c r="AY19" s="60"/>
+      <c r="AZ19" s="60"/>
+      <c r="BA19" s="60"/>
+      <c r="BB19" s="60"/>
+      <c r="BC19" s="60"/>
+      <c r="BD19" s="60"/>
+      <c r="BE19" s="61"/>
     </row>
     <row r="20" spans="1:57" ht="15" customHeight="1">
-      <c r="A20" s="70"/>
-      <c r="B20" s="71"/>
-      <c r="C20" s="71"/>
-      <c r="D20" s="71"/>
-      <c r="E20" s="71"/>
-      <c r="F20" s="71"/>
-      <c r="G20" s="72"/>
-      <c r="H20" s="78"/>
-      <c r="I20" s="79"/>
-      <c r="J20" s="79"/>
-      <c r="K20" s="79"/>
-      <c r="L20" s="79"/>
-      <c r="M20" s="79"/>
-      <c r="N20" s="80"/>
-      <c r="O20" s="78"/>
-      <c r="P20" s="81"/>
-      <c r="Q20" s="81"/>
-      <c r="R20" s="81"/>
-      <c r="S20" s="81"/>
-      <c r="T20" s="81"/>
-      <c r="U20" s="81"/>
-      <c r="V20" s="81"/>
-      <c r="W20" s="81"/>
-      <c r="X20" s="81"/>
-      <c r="Y20" s="81"/>
-      <c r="Z20" s="81"/>
-      <c r="AA20" s="81"/>
-      <c r="AB20" s="81"/>
-      <c r="AC20" s="81"/>
-      <c r="AD20" s="81"/>
-      <c r="AE20" s="81"/>
-      <c r="AF20" s="81"/>
-      <c r="AG20" s="81"/>
-      <c r="AH20" s="81"/>
-      <c r="AI20" s="81"/>
-      <c r="AJ20" s="81"/>
-      <c r="AK20" s="81"/>
-      <c r="AL20" s="81"/>
-      <c r="AM20" s="81"/>
-      <c r="AN20" s="81"/>
-      <c r="AO20" s="81"/>
-      <c r="AP20" s="82"/>
-      <c r="AQ20" s="86"/>
-      <c r="AR20" s="81"/>
-      <c r="AS20" s="81"/>
-      <c r="AT20" s="81"/>
-      <c r="AU20" s="81"/>
-      <c r="AV20" s="81"/>
-      <c r="AW20" s="81"/>
-      <c r="AX20" s="81"/>
-      <c r="AY20" s="81"/>
-      <c r="AZ20" s="81"/>
-      <c r="BA20" s="81"/>
-      <c r="BB20" s="81"/>
-      <c r="BC20" s="81"/>
-      <c r="BD20" s="81"/>
-      <c r="BE20" s="87"/>
+      <c r="A20" s="88"/>
+      <c r="B20" s="89"/>
+      <c r="C20" s="89"/>
+      <c r="D20" s="89"/>
+      <c r="E20" s="89"/>
+      <c r="F20" s="89"/>
+      <c r="G20" s="90"/>
+      <c r="H20" s="62"/>
+      <c r="I20" s="64"/>
+      <c r="J20" s="64"/>
+      <c r="K20" s="64"/>
+      <c r="L20" s="64"/>
+      <c r="M20" s="64"/>
+      <c r="N20" s="65"/>
+      <c r="O20" s="62"/>
+      <c r="P20" s="60"/>
+      <c r="Q20" s="60"/>
+      <c r="R20" s="60"/>
+      <c r="S20" s="60"/>
+      <c r="T20" s="60"/>
+      <c r="U20" s="60"/>
+      <c r="V20" s="60"/>
+      <c r="W20" s="60"/>
+      <c r="X20" s="60"/>
+      <c r="Y20" s="60"/>
+      <c r="Z20" s="60"/>
+      <c r="AA20" s="60"/>
+      <c r="AB20" s="60"/>
+      <c r="AC20" s="60"/>
+      <c r="AD20" s="60"/>
+      <c r="AE20" s="60"/>
+      <c r="AF20" s="60"/>
+      <c r="AG20" s="60"/>
+      <c r="AH20" s="60"/>
+      <c r="AI20" s="60"/>
+      <c r="AJ20" s="60"/>
+      <c r="AK20" s="60"/>
+      <c r="AL20" s="60"/>
+      <c r="AM20" s="60"/>
+      <c r="AN20" s="60"/>
+      <c r="AO20" s="60"/>
+      <c r="AP20" s="63"/>
+      <c r="AQ20" s="59"/>
+      <c r="AR20" s="60"/>
+      <c r="AS20" s="60"/>
+      <c r="AT20" s="60"/>
+      <c r="AU20" s="60"/>
+      <c r="AV20" s="60"/>
+      <c r="AW20" s="60"/>
+      <c r="AX20" s="60"/>
+      <c r="AY20" s="60"/>
+      <c r="AZ20" s="60"/>
+      <c r="BA20" s="60"/>
+      <c r="BB20" s="60"/>
+      <c r="BC20" s="60"/>
+      <c r="BD20" s="60"/>
+      <c r="BE20" s="61"/>
     </row>
     <row r="21" spans="1:57" ht="15" customHeight="1">
-      <c r="A21" s="70"/>
-      <c r="B21" s="71"/>
-      <c r="C21" s="71"/>
-      <c r="D21" s="71"/>
-      <c r="E21" s="71"/>
-      <c r="F21" s="71"/>
-      <c r="G21" s="72"/>
-      <c r="H21" s="78"/>
-      <c r="I21" s="79"/>
-      <c r="J21" s="79"/>
-      <c r="K21" s="79"/>
-      <c r="L21" s="79"/>
-      <c r="M21" s="79"/>
-      <c r="N21" s="80"/>
-      <c r="O21" s="78"/>
-      <c r="P21" s="81"/>
-      <c r="Q21" s="81"/>
-      <c r="R21" s="81"/>
-      <c r="S21" s="81"/>
-      <c r="T21" s="81"/>
-      <c r="U21" s="81"/>
-      <c r="V21" s="81"/>
-      <c r="W21" s="81"/>
-      <c r="X21" s="81"/>
-      <c r="Y21" s="81"/>
-      <c r="Z21" s="81"/>
-      <c r="AA21" s="81"/>
-      <c r="AB21" s="81"/>
-      <c r="AC21" s="81"/>
-      <c r="AD21" s="81"/>
-      <c r="AE21" s="81"/>
-      <c r="AF21" s="81"/>
-      <c r="AG21" s="81"/>
-      <c r="AH21" s="81"/>
-      <c r="AI21" s="81"/>
-      <c r="AJ21" s="81"/>
-      <c r="AK21" s="81"/>
-      <c r="AL21" s="81"/>
-      <c r="AM21" s="81"/>
-      <c r="AN21" s="81"/>
-      <c r="AO21" s="81"/>
-      <c r="AP21" s="82"/>
-      <c r="AQ21" s="86"/>
-      <c r="AR21" s="81"/>
-      <c r="AS21" s="81"/>
-      <c r="AT21" s="81"/>
-      <c r="AU21" s="81"/>
-      <c r="AV21" s="81"/>
-      <c r="AW21" s="81"/>
-      <c r="AX21" s="81"/>
-      <c r="AY21" s="81"/>
-      <c r="AZ21" s="81"/>
-      <c r="BA21" s="81"/>
-      <c r="BB21" s="81"/>
-      <c r="BC21" s="81"/>
-      <c r="BD21" s="81"/>
-      <c r="BE21" s="87"/>
+      <c r="A21" s="88"/>
+      <c r="B21" s="89"/>
+      <c r="C21" s="89"/>
+      <c r="D21" s="89"/>
+      <c r="E21" s="89"/>
+      <c r="F21" s="89"/>
+      <c r="G21" s="90"/>
+      <c r="H21" s="62"/>
+      <c r="I21" s="64"/>
+      <c r="J21" s="64"/>
+      <c r="K21" s="64"/>
+      <c r="L21" s="64"/>
+      <c r="M21" s="64"/>
+      <c r="N21" s="65"/>
+      <c r="O21" s="62"/>
+      <c r="P21" s="60"/>
+      <c r="Q21" s="60"/>
+      <c r="R21" s="60"/>
+      <c r="S21" s="60"/>
+      <c r="T21" s="60"/>
+      <c r="U21" s="60"/>
+      <c r="V21" s="60"/>
+      <c r="W21" s="60"/>
+      <c r="X21" s="60"/>
+      <c r="Y21" s="60"/>
+      <c r="Z21" s="60"/>
+      <c r="AA21" s="60"/>
+      <c r="AB21" s="60"/>
+      <c r="AC21" s="60"/>
+      <c r="AD21" s="60"/>
+      <c r="AE21" s="60"/>
+      <c r="AF21" s="60"/>
+      <c r="AG21" s="60"/>
+      <c r="AH21" s="60"/>
+      <c r="AI21" s="60"/>
+      <c r="AJ21" s="60"/>
+      <c r="AK21" s="60"/>
+      <c r="AL21" s="60"/>
+      <c r="AM21" s="60"/>
+      <c r="AN21" s="60"/>
+      <c r="AO21" s="60"/>
+      <c r="AP21" s="63"/>
+      <c r="AQ21" s="59"/>
+      <c r="AR21" s="60"/>
+      <c r="AS21" s="60"/>
+      <c r="AT21" s="60"/>
+      <c r="AU21" s="60"/>
+      <c r="AV21" s="60"/>
+      <c r="AW21" s="60"/>
+      <c r="AX21" s="60"/>
+      <c r="AY21" s="60"/>
+      <c r="AZ21" s="60"/>
+      <c r="BA21" s="60"/>
+      <c r="BB21" s="60"/>
+      <c r="BC21" s="60"/>
+      <c r="BD21" s="60"/>
+      <c r="BE21" s="61"/>
     </row>
     <row r="22" spans="1:57" ht="15" customHeight="1">
-      <c r="A22" s="70"/>
-      <c r="B22" s="71"/>
-      <c r="C22" s="71"/>
-      <c r="D22" s="71"/>
-      <c r="E22" s="71"/>
-      <c r="F22" s="71"/>
-      <c r="G22" s="72"/>
-      <c r="H22" s="78"/>
-      <c r="I22" s="79"/>
-      <c r="J22" s="79"/>
-      <c r="K22" s="79"/>
-      <c r="L22" s="79"/>
-      <c r="M22" s="79"/>
-      <c r="N22" s="80"/>
-      <c r="O22" s="78"/>
-      <c r="P22" s="81"/>
-      <c r="Q22" s="81"/>
-      <c r="R22" s="81"/>
-      <c r="S22" s="81"/>
-      <c r="T22" s="81"/>
-      <c r="U22" s="81"/>
-      <c r="V22" s="81"/>
-      <c r="W22" s="81"/>
-      <c r="X22" s="81"/>
-      <c r="Y22" s="81"/>
-      <c r="Z22" s="81"/>
-      <c r="AA22" s="81"/>
-      <c r="AB22" s="81"/>
-      <c r="AC22" s="81"/>
-      <c r="AD22" s="81"/>
-      <c r="AE22" s="81"/>
-      <c r="AF22" s="81"/>
-      <c r="AG22" s="81"/>
-      <c r="AH22" s="81"/>
-      <c r="AI22" s="81"/>
-      <c r="AJ22" s="81"/>
-      <c r="AK22" s="81"/>
-      <c r="AL22" s="81"/>
-      <c r="AM22" s="81"/>
-      <c r="AN22" s="81"/>
-      <c r="AO22" s="81"/>
-      <c r="AP22" s="82"/>
-      <c r="AQ22" s="86"/>
-      <c r="AR22" s="81"/>
-      <c r="AS22" s="81"/>
-      <c r="AT22" s="81"/>
-      <c r="AU22" s="81"/>
-      <c r="AV22" s="81"/>
-      <c r="AW22" s="81"/>
-      <c r="AX22" s="81"/>
-      <c r="AY22" s="81"/>
-      <c r="AZ22" s="81"/>
-      <c r="BA22" s="81"/>
-      <c r="BB22" s="81"/>
-      <c r="BC22" s="81"/>
-      <c r="BD22" s="81"/>
-      <c r="BE22" s="87"/>
+      <c r="A22" s="88"/>
+      <c r="B22" s="89"/>
+      <c r="C22" s="89"/>
+      <c r="D22" s="89"/>
+      <c r="E22" s="89"/>
+      <c r="F22" s="89"/>
+      <c r="G22" s="90"/>
+      <c r="H22" s="62"/>
+      <c r="I22" s="64"/>
+      <c r="J22" s="64"/>
+      <c r="K22" s="64"/>
+      <c r="L22" s="64"/>
+      <c r="M22" s="64"/>
+      <c r="N22" s="65"/>
+      <c r="O22" s="62"/>
+      <c r="P22" s="60"/>
+      <c r="Q22" s="60"/>
+      <c r="R22" s="60"/>
+      <c r="S22" s="60"/>
+      <c r="T22" s="60"/>
+      <c r="U22" s="60"/>
+      <c r="V22" s="60"/>
+      <c r="W22" s="60"/>
+      <c r="X22" s="60"/>
+      <c r="Y22" s="60"/>
+      <c r="Z22" s="60"/>
+      <c r="AA22" s="60"/>
+      <c r="AB22" s="60"/>
+      <c r="AC22" s="60"/>
+      <c r="AD22" s="60"/>
+      <c r="AE22" s="60"/>
+      <c r="AF22" s="60"/>
+      <c r="AG22" s="60"/>
+      <c r="AH22" s="60"/>
+      <c r="AI22" s="60"/>
+      <c r="AJ22" s="60"/>
+      <c r="AK22" s="60"/>
+      <c r="AL22" s="60"/>
+      <c r="AM22" s="60"/>
+      <c r="AN22" s="60"/>
+      <c r="AO22" s="60"/>
+      <c r="AP22" s="63"/>
+      <c r="AQ22" s="59"/>
+      <c r="AR22" s="60"/>
+      <c r="AS22" s="60"/>
+      <c r="AT22" s="60"/>
+      <c r="AU22" s="60"/>
+      <c r="AV22" s="60"/>
+      <c r="AW22" s="60"/>
+      <c r="AX22" s="60"/>
+      <c r="AY22" s="60"/>
+      <c r="AZ22" s="60"/>
+      <c r="BA22" s="60"/>
+      <c r="BB22" s="60"/>
+      <c r="BC22" s="60"/>
+      <c r="BD22" s="60"/>
+      <c r="BE22" s="61"/>
     </row>
     <row r="23" spans="1:57" ht="15" customHeight="1">
-      <c r="A23" s="70"/>
-      <c r="B23" s="71"/>
-      <c r="C23" s="71"/>
-      <c r="D23" s="71"/>
-      <c r="E23" s="71"/>
-      <c r="F23" s="71"/>
-      <c r="G23" s="72"/>
-      <c r="H23" s="78"/>
-      <c r="I23" s="79"/>
-      <c r="J23" s="79"/>
-      <c r="K23" s="79"/>
-      <c r="L23" s="79"/>
-      <c r="M23" s="79"/>
-      <c r="N23" s="80"/>
-      <c r="O23" s="78"/>
-      <c r="P23" s="81"/>
-      <c r="Q23" s="81"/>
-      <c r="R23" s="81"/>
-      <c r="S23" s="81"/>
-      <c r="T23" s="81"/>
-      <c r="U23" s="81"/>
-      <c r="V23" s="81"/>
-      <c r="W23" s="81"/>
-      <c r="X23" s="81"/>
-      <c r="Y23" s="81"/>
-      <c r="Z23" s="81"/>
-      <c r="AA23" s="81"/>
-      <c r="AB23" s="81"/>
-      <c r="AC23" s="81"/>
-      <c r="AD23" s="81"/>
-      <c r="AE23" s="81"/>
-      <c r="AF23" s="81"/>
-      <c r="AG23" s="81"/>
-      <c r="AH23" s="81"/>
-      <c r="AI23" s="81"/>
-      <c r="AJ23" s="81"/>
-      <c r="AK23" s="81"/>
-      <c r="AL23" s="81"/>
-      <c r="AM23" s="81"/>
-      <c r="AN23" s="81"/>
-      <c r="AO23" s="81"/>
-      <c r="AP23" s="82"/>
-      <c r="AQ23" s="86"/>
-      <c r="AR23" s="81"/>
-      <c r="AS23" s="81"/>
-      <c r="AT23" s="81"/>
-      <c r="AU23" s="81"/>
-      <c r="AV23" s="81"/>
-      <c r="AW23" s="81"/>
-      <c r="AX23" s="81"/>
-      <c r="AY23" s="81"/>
-      <c r="AZ23" s="81"/>
-      <c r="BA23" s="81"/>
-      <c r="BB23" s="81"/>
-      <c r="BC23" s="81"/>
-      <c r="BD23" s="81"/>
-      <c r="BE23" s="87"/>
+      <c r="A23" s="88"/>
+      <c r="B23" s="89"/>
+      <c r="C23" s="89"/>
+      <c r="D23" s="89"/>
+      <c r="E23" s="89"/>
+      <c r="F23" s="89"/>
+      <c r="G23" s="90"/>
+      <c r="H23" s="62"/>
+      <c r="I23" s="64"/>
+      <c r="J23" s="64"/>
+      <c r="K23" s="64"/>
+      <c r="L23" s="64"/>
+      <c r="M23" s="64"/>
+      <c r="N23" s="65"/>
+      <c r="O23" s="62"/>
+      <c r="P23" s="60"/>
+      <c r="Q23" s="60"/>
+      <c r="R23" s="60"/>
+      <c r="S23" s="60"/>
+      <c r="T23" s="60"/>
+      <c r="U23" s="60"/>
+      <c r="V23" s="60"/>
+      <c r="W23" s="60"/>
+      <c r="X23" s="60"/>
+      <c r="Y23" s="60"/>
+      <c r="Z23" s="60"/>
+      <c r="AA23" s="60"/>
+      <c r="AB23" s="60"/>
+      <c r="AC23" s="60"/>
+      <c r="AD23" s="60"/>
+      <c r="AE23" s="60"/>
+      <c r="AF23" s="60"/>
+      <c r="AG23" s="60"/>
+      <c r="AH23" s="60"/>
+      <c r="AI23" s="60"/>
+      <c r="AJ23" s="60"/>
+      <c r="AK23" s="60"/>
+      <c r="AL23" s="60"/>
+      <c r="AM23" s="60"/>
+      <c r="AN23" s="60"/>
+      <c r="AO23" s="60"/>
+      <c r="AP23" s="63"/>
+      <c r="AQ23" s="59"/>
+      <c r="AR23" s="60"/>
+      <c r="AS23" s="60"/>
+      <c r="AT23" s="60"/>
+      <c r="AU23" s="60"/>
+      <c r="AV23" s="60"/>
+      <c r="AW23" s="60"/>
+      <c r="AX23" s="60"/>
+      <c r="AY23" s="60"/>
+      <c r="AZ23" s="60"/>
+      <c r="BA23" s="60"/>
+      <c r="BB23" s="60"/>
+      <c r="BC23" s="60"/>
+      <c r="BD23" s="60"/>
+      <c r="BE23" s="61"/>
     </row>
     <row r="24" spans="1:57" ht="15" customHeight="1">
-      <c r="A24" s="70"/>
-      <c r="B24" s="71"/>
-      <c r="C24" s="71"/>
-      <c r="D24" s="71"/>
-      <c r="E24" s="71"/>
-      <c r="F24" s="71"/>
-      <c r="G24" s="72"/>
-      <c r="H24" s="78"/>
-      <c r="I24" s="79"/>
-      <c r="J24" s="79"/>
-      <c r="K24" s="79"/>
-      <c r="L24" s="79"/>
-      <c r="M24" s="79"/>
-      <c r="N24" s="80"/>
-      <c r="O24" s="78"/>
-      <c r="P24" s="81"/>
-      <c r="Q24" s="81"/>
-      <c r="R24" s="81"/>
-      <c r="S24" s="81"/>
-      <c r="T24" s="81"/>
-      <c r="U24" s="81"/>
-      <c r="V24" s="81"/>
-      <c r="W24" s="81"/>
-      <c r="X24" s="81"/>
-      <c r="Y24" s="81"/>
-      <c r="Z24" s="81"/>
-      <c r="AA24" s="81"/>
-      <c r="AB24" s="81"/>
-      <c r="AC24" s="81"/>
-      <c r="AD24" s="81"/>
-      <c r="AE24" s="81"/>
-      <c r="AF24" s="81"/>
-      <c r="AG24" s="81"/>
-      <c r="AH24" s="81"/>
-      <c r="AI24" s="81"/>
-      <c r="AJ24" s="81"/>
-      <c r="AK24" s="81"/>
-      <c r="AL24" s="81"/>
-      <c r="AM24" s="81"/>
-      <c r="AN24" s="81"/>
-      <c r="AO24" s="81"/>
-      <c r="AP24" s="82"/>
-      <c r="AQ24" s="86"/>
-      <c r="AR24" s="81"/>
-      <c r="AS24" s="81"/>
-      <c r="AT24" s="81"/>
-      <c r="AU24" s="81"/>
-      <c r="AV24" s="81"/>
-      <c r="AW24" s="81"/>
-      <c r="AX24" s="81"/>
-      <c r="AY24" s="81"/>
-      <c r="AZ24" s="81"/>
-      <c r="BA24" s="81"/>
-      <c r="BB24" s="81"/>
-      <c r="BC24" s="81"/>
-      <c r="BD24" s="81"/>
-      <c r="BE24" s="87"/>
+      <c r="A24" s="88"/>
+      <c r="B24" s="89"/>
+      <c r="C24" s="89"/>
+      <c r="D24" s="89"/>
+      <c r="E24" s="89"/>
+      <c r="F24" s="89"/>
+      <c r="G24" s="90"/>
+      <c r="H24" s="62"/>
+      <c r="I24" s="64"/>
+      <c r="J24" s="64"/>
+      <c r="K24" s="64"/>
+      <c r="L24" s="64"/>
+      <c r="M24" s="64"/>
+      <c r="N24" s="65"/>
+      <c r="O24" s="62"/>
+      <c r="P24" s="60"/>
+      <c r="Q24" s="60"/>
+      <c r="R24" s="60"/>
+      <c r="S24" s="60"/>
+      <c r="T24" s="60"/>
+      <c r="U24" s="60"/>
+      <c r="V24" s="60"/>
+      <c r="W24" s="60"/>
+      <c r="X24" s="60"/>
+      <c r="Y24" s="60"/>
+      <c r="Z24" s="60"/>
+      <c r="AA24" s="60"/>
+      <c r="AB24" s="60"/>
+      <c r="AC24" s="60"/>
+      <c r="AD24" s="60"/>
+      <c r="AE24" s="60"/>
+      <c r="AF24" s="60"/>
+      <c r="AG24" s="60"/>
+      <c r="AH24" s="60"/>
+      <c r="AI24" s="60"/>
+      <c r="AJ24" s="60"/>
+      <c r="AK24" s="60"/>
+      <c r="AL24" s="60"/>
+      <c r="AM24" s="60"/>
+      <c r="AN24" s="60"/>
+      <c r="AO24" s="60"/>
+      <c r="AP24" s="63"/>
+      <c r="AQ24" s="59"/>
+      <c r="AR24" s="60"/>
+      <c r="AS24" s="60"/>
+      <c r="AT24" s="60"/>
+      <c r="AU24" s="60"/>
+      <c r="AV24" s="60"/>
+      <c r="AW24" s="60"/>
+      <c r="AX24" s="60"/>
+      <c r="AY24" s="60"/>
+      <c r="AZ24" s="60"/>
+      <c r="BA24" s="60"/>
+      <c r="BB24" s="60"/>
+      <c r="BC24" s="60"/>
+      <c r="BD24" s="60"/>
+      <c r="BE24" s="61"/>
     </row>
     <row r="25" spans="1:57" ht="15" customHeight="1">
-      <c r="A25" s="70"/>
-      <c r="B25" s="71"/>
-      <c r="C25" s="71"/>
-      <c r="D25" s="71"/>
-      <c r="E25" s="71"/>
-      <c r="F25" s="71"/>
-      <c r="G25" s="72"/>
-      <c r="H25" s="78"/>
-      <c r="I25" s="79"/>
-      <c r="J25" s="79"/>
-      <c r="K25" s="79"/>
-      <c r="L25" s="79"/>
-      <c r="M25" s="79"/>
-      <c r="N25" s="80"/>
-      <c r="O25" s="78"/>
-      <c r="P25" s="81"/>
-      <c r="Q25" s="81"/>
-      <c r="R25" s="81"/>
-      <c r="S25" s="81"/>
-      <c r="T25" s="81"/>
-      <c r="U25" s="81"/>
-      <c r="V25" s="81"/>
-      <c r="W25" s="81"/>
-      <c r="X25" s="81"/>
-      <c r="Y25" s="81"/>
-      <c r="Z25" s="81"/>
-      <c r="AA25" s="81"/>
-      <c r="AB25" s="81"/>
-      <c r="AC25" s="81"/>
-      <c r="AD25" s="81"/>
-      <c r="AE25" s="81"/>
-      <c r="AF25" s="81"/>
-      <c r="AG25" s="81"/>
-      <c r="AH25" s="81"/>
-      <c r="AI25" s="81"/>
-      <c r="AJ25" s="81"/>
-      <c r="AK25" s="81"/>
-      <c r="AL25" s="81"/>
-      <c r="AM25" s="81"/>
-      <c r="AN25" s="81"/>
-      <c r="AO25" s="81"/>
-      <c r="AP25" s="82"/>
-      <c r="AQ25" s="86"/>
-      <c r="AR25" s="81"/>
-      <c r="AS25" s="81"/>
-      <c r="AT25" s="81"/>
-      <c r="AU25" s="81"/>
-      <c r="AV25" s="81"/>
-      <c r="AW25" s="81"/>
-      <c r="AX25" s="81"/>
-      <c r="AY25" s="81"/>
-      <c r="AZ25" s="81"/>
-      <c r="BA25" s="81"/>
-      <c r="BB25" s="81"/>
-      <c r="BC25" s="81"/>
-      <c r="BD25" s="81"/>
-      <c r="BE25" s="87"/>
+      <c r="A25" s="88"/>
+      <c r="B25" s="89"/>
+      <c r="C25" s="89"/>
+      <c r="D25" s="89"/>
+      <c r="E25" s="89"/>
+      <c r="F25" s="89"/>
+      <c r="G25" s="90"/>
+      <c r="H25" s="62"/>
+      <c r="I25" s="64"/>
+      <c r="J25" s="64"/>
+      <c r="K25" s="64"/>
+      <c r="L25" s="64"/>
+      <c r="M25" s="64"/>
+      <c r="N25" s="65"/>
+      <c r="O25" s="62"/>
+      <c r="P25" s="60"/>
+      <c r="Q25" s="60"/>
+      <c r="R25" s="60"/>
+      <c r="S25" s="60"/>
+      <c r="T25" s="60"/>
+      <c r="U25" s="60"/>
+      <c r="V25" s="60"/>
+      <c r="W25" s="60"/>
+      <c r="X25" s="60"/>
+      <c r="Y25" s="60"/>
+      <c r="Z25" s="60"/>
+      <c r="AA25" s="60"/>
+      <c r="AB25" s="60"/>
+      <c r="AC25" s="60"/>
+      <c r="AD25" s="60"/>
+      <c r="AE25" s="60"/>
+      <c r="AF25" s="60"/>
+      <c r="AG25" s="60"/>
+      <c r="AH25" s="60"/>
+      <c r="AI25" s="60"/>
+      <c r="AJ25" s="60"/>
+      <c r="AK25" s="60"/>
+      <c r="AL25" s="60"/>
+      <c r="AM25" s="60"/>
+      <c r="AN25" s="60"/>
+      <c r="AO25" s="60"/>
+      <c r="AP25" s="63"/>
+      <c r="AQ25" s="59"/>
+      <c r="AR25" s="60"/>
+      <c r="AS25" s="60"/>
+      <c r="AT25" s="60"/>
+      <c r="AU25" s="60"/>
+      <c r="AV25" s="60"/>
+      <c r="AW25" s="60"/>
+      <c r="AX25" s="60"/>
+      <c r="AY25" s="60"/>
+      <c r="AZ25" s="60"/>
+      <c r="BA25" s="60"/>
+      <c r="BB25" s="60"/>
+      <c r="BC25" s="60"/>
+      <c r="BD25" s="60"/>
+      <c r="BE25" s="61"/>
     </row>
     <row r="26" spans="1:57" ht="15" customHeight="1">
-      <c r="A26" s="70"/>
-      <c r="B26" s="71"/>
-      <c r="C26" s="71"/>
-      <c r="D26" s="71"/>
-      <c r="E26" s="71"/>
-      <c r="F26" s="71"/>
-      <c r="G26" s="72"/>
-      <c r="H26" s="78"/>
-      <c r="I26" s="79"/>
-      <c r="J26" s="79"/>
-      <c r="K26" s="79"/>
-      <c r="L26" s="79"/>
-      <c r="M26" s="79"/>
-      <c r="N26" s="80"/>
-      <c r="O26" s="78"/>
-      <c r="P26" s="81"/>
-      <c r="Q26" s="81"/>
-      <c r="R26" s="81"/>
-      <c r="S26" s="81"/>
-      <c r="T26" s="81"/>
-      <c r="U26" s="81"/>
-      <c r="V26" s="81"/>
-      <c r="W26" s="81"/>
-      <c r="X26" s="81"/>
-      <c r="Y26" s="81"/>
-      <c r="Z26" s="81"/>
-      <c r="AA26" s="81"/>
-      <c r="AB26" s="81"/>
-      <c r="AC26" s="81"/>
-      <c r="AD26" s="81"/>
-      <c r="AE26" s="81"/>
-      <c r="AF26" s="81"/>
-      <c r="AG26" s="81"/>
-      <c r="AH26" s="81"/>
-      <c r="AI26" s="81"/>
-      <c r="AJ26" s="81"/>
-      <c r="AK26" s="81"/>
-      <c r="AL26" s="81"/>
-      <c r="AM26" s="81"/>
-      <c r="AN26" s="81"/>
-      <c r="AO26" s="81"/>
-      <c r="AP26" s="82"/>
-      <c r="AQ26" s="86"/>
-      <c r="AR26" s="81"/>
-      <c r="AS26" s="81"/>
-      <c r="AT26" s="81"/>
-      <c r="AU26" s="81"/>
-      <c r="AV26" s="81"/>
-      <c r="AW26" s="81"/>
-      <c r="AX26" s="81"/>
-      <c r="AY26" s="81"/>
-      <c r="AZ26" s="81"/>
-      <c r="BA26" s="81"/>
-      <c r="BB26" s="81"/>
-      <c r="BC26" s="81"/>
-      <c r="BD26" s="81"/>
-      <c r="BE26" s="87"/>
+      <c r="A26" s="88"/>
+      <c r="B26" s="89"/>
+      <c r="C26" s="89"/>
+      <c r="D26" s="89"/>
+      <c r="E26" s="89"/>
+      <c r="F26" s="89"/>
+      <c r="G26" s="90"/>
+      <c r="H26" s="62"/>
+      <c r="I26" s="64"/>
+      <c r="J26" s="64"/>
+      <c r="K26" s="64"/>
+      <c r="L26" s="64"/>
+      <c r="M26" s="64"/>
+      <c r="N26" s="65"/>
+      <c r="O26" s="62"/>
+      <c r="P26" s="60"/>
+      <c r="Q26" s="60"/>
+      <c r="R26" s="60"/>
+      <c r="S26" s="60"/>
+      <c r="T26" s="60"/>
+      <c r="U26" s="60"/>
+      <c r="V26" s="60"/>
+      <c r="W26" s="60"/>
+      <c r="X26" s="60"/>
+      <c r="Y26" s="60"/>
+      <c r="Z26" s="60"/>
+      <c r="AA26" s="60"/>
+      <c r="AB26" s="60"/>
+      <c r="AC26" s="60"/>
+      <c r="AD26" s="60"/>
+      <c r="AE26" s="60"/>
+      <c r="AF26" s="60"/>
+      <c r="AG26" s="60"/>
+      <c r="AH26" s="60"/>
+      <c r="AI26" s="60"/>
+      <c r="AJ26" s="60"/>
+      <c r="AK26" s="60"/>
+      <c r="AL26" s="60"/>
+      <c r="AM26" s="60"/>
+      <c r="AN26" s="60"/>
+      <c r="AO26" s="60"/>
+      <c r="AP26" s="63"/>
+      <c r="AQ26" s="59"/>
+      <c r="AR26" s="60"/>
+      <c r="AS26" s="60"/>
+      <c r="AT26" s="60"/>
+      <c r="AU26" s="60"/>
+      <c r="AV26" s="60"/>
+      <c r="AW26" s="60"/>
+      <c r="AX26" s="60"/>
+      <c r="AY26" s="60"/>
+      <c r="AZ26" s="60"/>
+      <c r="BA26" s="60"/>
+      <c r="BB26" s="60"/>
+      <c r="BC26" s="60"/>
+      <c r="BD26" s="60"/>
+      <c r="BE26" s="61"/>
     </row>
     <row r="27" spans="1:57" ht="15" customHeight="1">
-      <c r="A27" s="70"/>
-      <c r="B27" s="71"/>
-      <c r="C27" s="71"/>
-      <c r="D27" s="71"/>
-      <c r="E27" s="71"/>
-      <c r="F27" s="71"/>
-      <c r="G27" s="72"/>
-      <c r="H27" s="78"/>
-      <c r="I27" s="79"/>
-      <c r="J27" s="79"/>
-      <c r="K27" s="79"/>
-      <c r="L27" s="79"/>
-      <c r="M27" s="79"/>
-      <c r="N27" s="80"/>
-      <c r="O27" s="78"/>
-      <c r="P27" s="81"/>
-      <c r="Q27" s="81"/>
-      <c r="R27" s="81"/>
-      <c r="S27" s="81"/>
-      <c r="T27" s="81"/>
-      <c r="U27" s="81"/>
-      <c r="V27" s="81"/>
-      <c r="W27" s="81"/>
-      <c r="X27" s="81"/>
-      <c r="Y27" s="81"/>
-      <c r="Z27" s="81"/>
-      <c r="AA27" s="81"/>
-      <c r="AB27" s="81"/>
-      <c r="AC27" s="81"/>
-      <c r="AD27" s="81"/>
-      <c r="AE27" s="81"/>
-      <c r="AF27" s="81"/>
-      <c r="AG27" s="81"/>
-      <c r="AH27" s="81"/>
-      <c r="AI27" s="81"/>
-      <c r="AJ27" s="81"/>
-      <c r="AK27" s="81"/>
-      <c r="AL27" s="81"/>
-      <c r="AM27" s="81"/>
-      <c r="AN27" s="81"/>
-      <c r="AO27" s="81"/>
-      <c r="AP27" s="82"/>
-      <c r="AQ27" s="86"/>
-      <c r="AR27" s="81"/>
-      <c r="AS27" s="81"/>
-      <c r="AT27" s="81"/>
-      <c r="AU27" s="81"/>
-      <c r="AV27" s="81"/>
-      <c r="AW27" s="81"/>
-      <c r="AX27" s="81"/>
-      <c r="AY27" s="81"/>
-      <c r="AZ27" s="81"/>
-      <c r="BA27" s="81"/>
-      <c r="BB27" s="81"/>
-      <c r="BC27" s="81"/>
-      <c r="BD27" s="81"/>
-      <c r="BE27" s="87"/>
+      <c r="A27" s="88"/>
+      <c r="B27" s="89"/>
+      <c r="C27" s="89"/>
+      <c r="D27" s="89"/>
+      <c r="E27" s="89"/>
+      <c r="F27" s="89"/>
+      <c r="G27" s="90"/>
+      <c r="H27" s="62"/>
+      <c r="I27" s="64"/>
+      <c r="J27" s="64"/>
+      <c r="K27" s="64"/>
+      <c r="L27" s="64"/>
+      <c r="M27" s="64"/>
+      <c r="N27" s="65"/>
+      <c r="O27" s="62"/>
+      <c r="P27" s="60"/>
+      <c r="Q27" s="60"/>
+      <c r="R27" s="60"/>
+      <c r="S27" s="60"/>
+      <c r="T27" s="60"/>
+      <c r="U27" s="60"/>
+      <c r="V27" s="60"/>
+      <c r="W27" s="60"/>
+      <c r="X27" s="60"/>
+      <c r="Y27" s="60"/>
+      <c r="Z27" s="60"/>
+      <c r="AA27" s="60"/>
+      <c r="AB27" s="60"/>
+      <c r="AC27" s="60"/>
+      <c r="AD27" s="60"/>
+      <c r="AE27" s="60"/>
+      <c r="AF27" s="60"/>
+      <c r="AG27" s="60"/>
+      <c r="AH27" s="60"/>
+      <c r="AI27" s="60"/>
+      <c r="AJ27" s="60"/>
+      <c r="AK27" s="60"/>
+      <c r="AL27" s="60"/>
+      <c r="AM27" s="60"/>
+      <c r="AN27" s="60"/>
+      <c r="AO27" s="60"/>
+      <c r="AP27" s="63"/>
+      <c r="AQ27" s="59"/>
+      <c r="AR27" s="60"/>
+      <c r="AS27" s="60"/>
+      <c r="AT27" s="60"/>
+      <c r="AU27" s="60"/>
+      <c r="AV27" s="60"/>
+      <c r="AW27" s="60"/>
+      <c r="AX27" s="60"/>
+      <c r="AY27" s="60"/>
+      <c r="AZ27" s="60"/>
+      <c r="BA27" s="60"/>
+      <c r="BB27" s="60"/>
+      <c r="BC27" s="60"/>
+      <c r="BD27" s="60"/>
+      <c r="BE27" s="61"/>
     </row>
     <row r="28" spans="1:57" ht="15" customHeight="1">
-      <c r="A28" s="70"/>
-      <c r="B28" s="71"/>
-      <c r="C28" s="71"/>
-      <c r="D28" s="71"/>
-      <c r="E28" s="71"/>
-      <c r="F28" s="71"/>
-      <c r="G28" s="72"/>
-      <c r="H28" s="78"/>
-      <c r="I28" s="79"/>
-      <c r="J28" s="79"/>
-      <c r="K28" s="79"/>
-      <c r="L28" s="79"/>
-      <c r="M28" s="79"/>
-      <c r="N28" s="80"/>
-      <c r="O28" s="78"/>
-      <c r="P28" s="81"/>
-      <c r="Q28" s="81"/>
-      <c r="R28" s="81"/>
-      <c r="S28" s="81"/>
-      <c r="T28" s="81"/>
-      <c r="U28" s="81"/>
-      <c r="V28" s="81"/>
-      <c r="W28" s="81"/>
-      <c r="X28" s="81"/>
-      <c r="Y28" s="81"/>
-      <c r="Z28" s="81"/>
-      <c r="AA28" s="81"/>
-      <c r="AB28" s="81"/>
-      <c r="AC28" s="81"/>
-      <c r="AD28" s="81"/>
-      <c r="AE28" s="81"/>
-      <c r="AF28" s="81"/>
-      <c r="AG28" s="81"/>
-      <c r="AH28" s="81"/>
-      <c r="AI28" s="81"/>
-      <c r="AJ28" s="81"/>
-      <c r="AK28" s="81"/>
-      <c r="AL28" s="81"/>
-      <c r="AM28" s="81"/>
-      <c r="AN28" s="81"/>
-      <c r="AO28" s="81"/>
-      <c r="AP28" s="82"/>
-      <c r="AQ28" s="86"/>
-      <c r="AR28" s="81"/>
-      <c r="AS28" s="81"/>
-      <c r="AT28" s="81"/>
-      <c r="AU28" s="81"/>
-      <c r="AV28" s="81"/>
-      <c r="AW28" s="81"/>
-      <c r="AX28" s="81"/>
-      <c r="AY28" s="81"/>
-      <c r="AZ28" s="81"/>
-      <c r="BA28" s="81"/>
-      <c r="BB28" s="81"/>
-      <c r="BC28" s="81"/>
-      <c r="BD28" s="81"/>
-      <c r="BE28" s="87"/>
+      <c r="A28" s="88"/>
+      <c r="B28" s="89"/>
+      <c r="C28" s="89"/>
+      <c r="D28" s="89"/>
+      <c r="E28" s="89"/>
+      <c r="F28" s="89"/>
+      <c r="G28" s="90"/>
+      <c r="H28" s="62"/>
+      <c r="I28" s="64"/>
+      <c r="J28" s="64"/>
+      <c r="K28" s="64"/>
+      <c r="L28" s="64"/>
+      <c r="M28" s="64"/>
+      <c r="N28" s="65"/>
+      <c r="O28" s="62"/>
+      <c r="P28" s="60"/>
+      <c r="Q28" s="60"/>
+      <c r="R28" s="60"/>
+      <c r="S28" s="60"/>
+      <c r="T28" s="60"/>
+      <c r="U28" s="60"/>
+      <c r="V28" s="60"/>
+      <c r="W28" s="60"/>
+      <c r="X28" s="60"/>
+      <c r="Y28" s="60"/>
+      <c r="Z28" s="60"/>
+      <c r="AA28" s="60"/>
+      <c r="AB28" s="60"/>
+      <c r="AC28" s="60"/>
+      <c r="AD28" s="60"/>
+      <c r="AE28" s="60"/>
+      <c r="AF28" s="60"/>
+      <c r="AG28" s="60"/>
+      <c r="AH28" s="60"/>
+      <c r="AI28" s="60"/>
+      <c r="AJ28" s="60"/>
+      <c r="AK28" s="60"/>
+      <c r="AL28" s="60"/>
+      <c r="AM28" s="60"/>
+      <c r="AN28" s="60"/>
+      <c r="AO28" s="60"/>
+      <c r="AP28" s="63"/>
+      <c r="AQ28" s="59"/>
+      <c r="AR28" s="60"/>
+      <c r="AS28" s="60"/>
+      <c r="AT28" s="60"/>
+      <c r="AU28" s="60"/>
+      <c r="AV28" s="60"/>
+      <c r="AW28" s="60"/>
+      <c r="AX28" s="60"/>
+      <c r="AY28" s="60"/>
+      <c r="AZ28" s="60"/>
+      <c r="BA28" s="60"/>
+      <c r="BB28" s="60"/>
+      <c r="BC28" s="60"/>
+      <c r="BD28" s="60"/>
+      <c r="BE28" s="61"/>
     </row>
     <row r="29" spans="1:57" ht="15" customHeight="1">
-      <c r="A29" s="70"/>
-      <c r="B29" s="71"/>
-      <c r="C29" s="71"/>
-      <c r="D29" s="71"/>
-      <c r="E29" s="71"/>
-      <c r="F29" s="71"/>
-      <c r="G29" s="72"/>
-      <c r="H29" s="78"/>
-      <c r="I29" s="79"/>
-      <c r="J29" s="79"/>
-      <c r="K29" s="79"/>
-      <c r="L29" s="79"/>
-      <c r="M29" s="79"/>
-      <c r="N29" s="80"/>
-      <c r="O29" s="78"/>
-      <c r="P29" s="81"/>
-      <c r="Q29" s="81"/>
-      <c r="R29" s="81"/>
-      <c r="S29" s="81"/>
-      <c r="T29" s="81"/>
-      <c r="U29" s="81"/>
-      <c r="V29" s="81"/>
-      <c r="W29" s="81"/>
-      <c r="X29" s="81"/>
-      <c r="Y29" s="81"/>
-      <c r="Z29" s="81"/>
-      <c r="AA29" s="81"/>
-      <c r="AB29" s="81"/>
-      <c r="AC29" s="81"/>
-      <c r="AD29" s="81"/>
-      <c r="AE29" s="81"/>
-      <c r="AF29" s="81"/>
-      <c r="AG29" s="81"/>
-      <c r="AH29" s="81"/>
-      <c r="AI29" s="81"/>
-      <c r="AJ29" s="81"/>
-      <c r="AK29" s="81"/>
-      <c r="AL29" s="81"/>
-      <c r="AM29" s="81"/>
-      <c r="AN29" s="81"/>
-      <c r="AO29" s="81"/>
-      <c r="AP29" s="82"/>
-      <c r="AQ29" s="86"/>
-      <c r="AR29" s="81"/>
-      <c r="AS29" s="81"/>
-      <c r="AT29" s="81"/>
-      <c r="AU29" s="81"/>
-      <c r="AV29" s="81"/>
-      <c r="AW29" s="81"/>
-      <c r="AX29" s="81"/>
-      <c r="AY29" s="81"/>
-      <c r="AZ29" s="81"/>
-      <c r="BA29" s="81"/>
-      <c r="BB29" s="81"/>
-      <c r="BC29" s="81"/>
-      <c r="BD29" s="81"/>
-      <c r="BE29" s="87"/>
+      <c r="A29" s="88"/>
+      <c r="B29" s="89"/>
+      <c r="C29" s="89"/>
+      <c r="D29" s="89"/>
+      <c r="E29" s="89"/>
+      <c r="F29" s="89"/>
+      <c r="G29" s="90"/>
+      <c r="H29" s="62"/>
+      <c r="I29" s="64"/>
+      <c r="J29" s="64"/>
+      <c r="K29" s="64"/>
+      <c r="L29" s="64"/>
+      <c r="M29" s="64"/>
+      <c r="N29" s="65"/>
+      <c r="O29" s="62"/>
+      <c r="P29" s="60"/>
+      <c r="Q29" s="60"/>
+      <c r="R29" s="60"/>
+      <c r="S29" s="60"/>
+      <c r="T29" s="60"/>
+      <c r="U29" s="60"/>
+      <c r="V29" s="60"/>
+      <c r="W29" s="60"/>
+      <c r="X29" s="60"/>
+      <c r="Y29" s="60"/>
+      <c r="Z29" s="60"/>
+      <c r="AA29" s="60"/>
+      <c r="AB29" s="60"/>
+      <c r="AC29" s="60"/>
+      <c r="AD29" s="60"/>
+      <c r="AE29" s="60"/>
+      <c r="AF29" s="60"/>
+      <c r="AG29" s="60"/>
+      <c r="AH29" s="60"/>
+      <c r="AI29" s="60"/>
+      <c r="AJ29" s="60"/>
+      <c r="AK29" s="60"/>
+      <c r="AL29" s="60"/>
+      <c r="AM29" s="60"/>
+      <c r="AN29" s="60"/>
+      <c r="AO29" s="60"/>
+      <c r="AP29" s="63"/>
+      <c r="AQ29" s="59"/>
+      <c r="AR29" s="60"/>
+      <c r="AS29" s="60"/>
+      <c r="AT29" s="60"/>
+      <c r="AU29" s="60"/>
+      <c r="AV29" s="60"/>
+      <c r="AW29" s="60"/>
+      <c r="AX29" s="60"/>
+      <c r="AY29" s="60"/>
+      <c r="AZ29" s="60"/>
+      <c r="BA29" s="60"/>
+      <c r="BB29" s="60"/>
+      <c r="BC29" s="60"/>
+      <c r="BD29" s="60"/>
+      <c r="BE29" s="61"/>
     </row>
     <row r="30" spans="1:57" ht="15" customHeight="1">
-      <c r="A30" s="70"/>
-      <c r="B30" s="71"/>
-      <c r="C30" s="71"/>
-      <c r="D30" s="71"/>
-      <c r="E30" s="71"/>
-      <c r="F30" s="71"/>
-      <c r="G30" s="72"/>
-      <c r="H30" s="78"/>
-      <c r="I30" s="79"/>
-      <c r="J30" s="79"/>
-      <c r="K30" s="79"/>
-      <c r="L30" s="79"/>
-      <c r="M30" s="79"/>
-      <c r="N30" s="80"/>
-      <c r="O30" s="78"/>
-      <c r="P30" s="81"/>
-      <c r="Q30" s="81"/>
-      <c r="R30" s="81"/>
-      <c r="S30" s="81"/>
-      <c r="T30" s="81"/>
-      <c r="U30" s="81"/>
-      <c r="V30" s="81"/>
-      <c r="W30" s="81"/>
-      <c r="X30" s="81"/>
-      <c r="Y30" s="81"/>
-      <c r="Z30" s="81"/>
-      <c r="AA30" s="81"/>
-      <c r="AB30" s="81"/>
-      <c r="AC30" s="81"/>
-      <c r="AD30" s="81"/>
-      <c r="AE30" s="81"/>
-      <c r="AF30" s="81"/>
-      <c r="AG30" s="81"/>
-      <c r="AH30" s="81"/>
-      <c r="AI30" s="81"/>
-      <c r="AJ30" s="81"/>
-      <c r="AK30" s="81"/>
-      <c r="AL30" s="81"/>
-      <c r="AM30" s="81"/>
-      <c r="AN30" s="81"/>
-      <c r="AO30" s="81"/>
-      <c r="AP30" s="82"/>
-      <c r="AQ30" s="86"/>
-      <c r="AR30" s="81"/>
-      <c r="AS30" s="81"/>
-      <c r="AT30" s="81"/>
-      <c r="AU30" s="81"/>
-      <c r="AV30" s="81"/>
-      <c r="AW30" s="81"/>
-      <c r="AX30" s="81"/>
-      <c r="AY30" s="81"/>
-      <c r="AZ30" s="81"/>
-      <c r="BA30" s="81"/>
-      <c r="BB30" s="81"/>
-      <c r="BC30" s="81"/>
-      <c r="BD30" s="81"/>
-      <c r="BE30" s="87"/>
+      <c r="A30" s="88"/>
+      <c r="B30" s="89"/>
+      <c r="C30" s="89"/>
+      <c r="D30" s="89"/>
+      <c r="E30" s="89"/>
+      <c r="F30" s="89"/>
+      <c r="G30" s="90"/>
+      <c r="H30" s="62"/>
+      <c r="I30" s="64"/>
+      <c r="J30" s="64"/>
+      <c r="K30" s="64"/>
+      <c r="L30" s="64"/>
+      <c r="M30" s="64"/>
+      <c r="N30" s="65"/>
+      <c r="O30" s="62"/>
+      <c r="P30" s="60"/>
+      <c r="Q30" s="60"/>
+      <c r="R30" s="60"/>
+      <c r="S30" s="60"/>
+      <c r="T30" s="60"/>
+      <c r="U30" s="60"/>
+      <c r="V30" s="60"/>
+      <c r="W30" s="60"/>
+      <c r="X30" s="60"/>
+      <c r="Y30" s="60"/>
+      <c r="Z30" s="60"/>
+      <c r="AA30" s="60"/>
+      <c r="AB30" s="60"/>
+      <c r="AC30" s="60"/>
+      <c r="AD30" s="60"/>
+      <c r="AE30" s="60"/>
+      <c r="AF30" s="60"/>
+      <c r="AG30" s="60"/>
+      <c r="AH30" s="60"/>
+      <c r="AI30" s="60"/>
+      <c r="AJ30" s="60"/>
+      <c r="AK30" s="60"/>
+      <c r="AL30" s="60"/>
+      <c r="AM30" s="60"/>
+      <c r="AN30" s="60"/>
+      <c r="AO30" s="60"/>
+      <c r="AP30" s="63"/>
+      <c r="AQ30" s="59"/>
+      <c r="AR30" s="60"/>
+      <c r="AS30" s="60"/>
+      <c r="AT30" s="60"/>
+      <c r="AU30" s="60"/>
+      <c r="AV30" s="60"/>
+      <c r="AW30" s="60"/>
+      <c r="AX30" s="60"/>
+      <c r="AY30" s="60"/>
+      <c r="AZ30" s="60"/>
+      <c r="BA30" s="60"/>
+      <c r="BB30" s="60"/>
+      <c r="BC30" s="60"/>
+      <c r="BD30" s="60"/>
+      <c r="BE30" s="61"/>
     </row>
     <row r="31" spans="1:57" ht="15" customHeight="1">
-      <c r="A31" s="70"/>
-      <c r="B31" s="71"/>
-      <c r="C31" s="71"/>
-      <c r="D31" s="71"/>
-      <c r="E31" s="71"/>
-      <c r="F31" s="71"/>
-      <c r="G31" s="72"/>
-      <c r="H31" s="78"/>
-      <c r="I31" s="79"/>
-      <c r="J31" s="79"/>
-      <c r="K31" s="79"/>
-      <c r="L31" s="79"/>
-      <c r="M31" s="79"/>
-      <c r="N31" s="80"/>
-      <c r="O31" s="78"/>
-      <c r="P31" s="81"/>
-      <c r="Q31" s="81"/>
-      <c r="R31" s="81"/>
-      <c r="S31" s="81"/>
-      <c r="T31" s="81"/>
-      <c r="U31" s="81"/>
-      <c r="V31" s="81"/>
-      <c r="W31" s="81"/>
-      <c r="X31" s="81"/>
-      <c r="Y31" s="81"/>
-      <c r="Z31" s="81"/>
-      <c r="AA31" s="81"/>
-      <c r="AB31" s="81"/>
-      <c r="AC31" s="81"/>
-      <c r="AD31" s="81"/>
-      <c r="AE31" s="81"/>
-      <c r="AF31" s="81"/>
-      <c r="AG31" s="81"/>
-      <c r="AH31" s="81"/>
-      <c r="AI31" s="81"/>
-      <c r="AJ31" s="81"/>
-      <c r="AK31" s="81"/>
-      <c r="AL31" s="81"/>
-      <c r="AM31" s="81"/>
-      <c r="AN31" s="81"/>
-      <c r="AO31" s="81"/>
-      <c r="AP31" s="82"/>
-      <c r="AQ31" s="86"/>
-      <c r="AR31" s="81"/>
-      <c r="AS31" s="81"/>
-      <c r="AT31" s="81"/>
-      <c r="AU31" s="81"/>
-      <c r="AV31" s="81"/>
-      <c r="AW31" s="81"/>
-      <c r="AX31" s="81"/>
-      <c r="AY31" s="81"/>
-      <c r="AZ31" s="81"/>
-      <c r="BA31" s="81"/>
-      <c r="BB31" s="81"/>
-      <c r="BC31" s="81"/>
-      <c r="BD31" s="81"/>
-      <c r="BE31" s="87"/>
+      <c r="A31" s="88"/>
+      <c r="B31" s="89"/>
+      <c r="C31" s="89"/>
+      <c r="D31" s="89"/>
+      <c r="E31" s="89"/>
+      <c r="F31" s="89"/>
+      <c r="G31" s="90"/>
+      <c r="H31" s="62"/>
+      <c r="I31" s="64"/>
+      <c r="J31" s="64"/>
+      <c r="K31" s="64"/>
+      <c r="L31" s="64"/>
+      <c r="M31" s="64"/>
+      <c r="N31" s="65"/>
+      <c r="O31" s="62"/>
+      <c r="P31" s="60"/>
+      <c r="Q31" s="60"/>
+      <c r="R31" s="60"/>
+      <c r="S31" s="60"/>
+      <c r="T31" s="60"/>
+      <c r="U31" s="60"/>
+      <c r="V31" s="60"/>
+      <c r="W31" s="60"/>
+      <c r="X31" s="60"/>
+      <c r="Y31" s="60"/>
+      <c r="Z31" s="60"/>
+      <c r="AA31" s="60"/>
+      <c r="AB31" s="60"/>
+      <c r="AC31" s="60"/>
+      <c r="AD31" s="60"/>
+      <c r="AE31" s="60"/>
+      <c r="AF31" s="60"/>
+      <c r="AG31" s="60"/>
+      <c r="AH31" s="60"/>
+      <c r="AI31" s="60"/>
+      <c r="AJ31" s="60"/>
+      <c r="AK31" s="60"/>
+      <c r="AL31" s="60"/>
+      <c r="AM31" s="60"/>
+      <c r="AN31" s="60"/>
+      <c r="AO31" s="60"/>
+      <c r="AP31" s="63"/>
+      <c r="AQ31" s="59"/>
+      <c r="AR31" s="60"/>
+      <c r="AS31" s="60"/>
+      <c r="AT31" s="60"/>
+      <c r="AU31" s="60"/>
+      <c r="AV31" s="60"/>
+      <c r="AW31" s="60"/>
+      <c r="AX31" s="60"/>
+      <c r="AY31" s="60"/>
+      <c r="AZ31" s="60"/>
+      <c r="BA31" s="60"/>
+      <c r="BB31" s="60"/>
+      <c r="BC31" s="60"/>
+      <c r="BD31" s="60"/>
+      <c r="BE31" s="61"/>
     </row>
     <row r="32" spans="1:57" ht="15" customHeight="1">
-      <c r="A32" s="70"/>
-      <c r="B32" s="71"/>
-      <c r="C32" s="71"/>
-      <c r="D32" s="71"/>
-      <c r="E32" s="71"/>
-      <c r="F32" s="71"/>
-      <c r="G32" s="72"/>
-      <c r="H32" s="78"/>
-      <c r="I32" s="79"/>
-      <c r="J32" s="79"/>
-      <c r="K32" s="79"/>
-      <c r="L32" s="79"/>
-      <c r="M32" s="79"/>
-      <c r="N32" s="80"/>
-      <c r="O32" s="78"/>
-      <c r="P32" s="81"/>
-      <c r="Q32" s="81"/>
-      <c r="R32" s="81"/>
-      <c r="S32" s="81"/>
-      <c r="T32" s="81"/>
-      <c r="U32" s="81"/>
-      <c r="V32" s="81"/>
-      <c r="W32" s="81"/>
-      <c r="X32" s="81"/>
-      <c r="Y32" s="81"/>
-      <c r="Z32" s="81"/>
-      <c r="AA32" s="81"/>
-      <c r="AB32" s="81"/>
-      <c r="AC32" s="81"/>
-      <c r="AD32" s="81"/>
-      <c r="AE32" s="81"/>
-      <c r="AF32" s="81"/>
-      <c r="AG32" s="81"/>
-      <c r="AH32" s="81"/>
-      <c r="AI32" s="81"/>
-      <c r="AJ32" s="81"/>
-      <c r="AK32" s="81"/>
-      <c r="AL32" s="81"/>
-      <c r="AM32" s="81"/>
-      <c r="AN32" s="81"/>
-      <c r="AO32" s="81"/>
-      <c r="AP32" s="82"/>
-      <c r="AQ32" s="86"/>
-      <c r="AR32" s="81"/>
-      <c r="AS32" s="81"/>
-      <c r="AT32" s="81"/>
-      <c r="AU32" s="81"/>
-      <c r="AV32" s="81"/>
-      <c r="AW32" s="81"/>
-      <c r="AX32" s="81"/>
-      <c r="AY32" s="81"/>
-      <c r="AZ32" s="81"/>
-      <c r="BA32" s="81"/>
-      <c r="BB32" s="81"/>
-      <c r="BC32" s="81"/>
-      <c r="BD32" s="81"/>
-      <c r="BE32" s="87"/>
+      <c r="A32" s="88"/>
+      <c r="B32" s="89"/>
+      <c r="C32" s="89"/>
+      <c r="D32" s="89"/>
+      <c r="E32" s="89"/>
+      <c r="F32" s="89"/>
+      <c r="G32" s="90"/>
+      <c r="H32" s="62"/>
+      <c r="I32" s="64"/>
+      <c r="J32" s="64"/>
+      <c r="K32" s="64"/>
+      <c r="L32" s="64"/>
+      <c r="M32" s="64"/>
+      <c r="N32" s="65"/>
+      <c r="O32" s="62"/>
+      <c r="P32" s="60"/>
+      <c r="Q32" s="60"/>
+      <c r="R32" s="60"/>
+      <c r="S32" s="60"/>
+      <c r="T32" s="60"/>
+      <c r="U32" s="60"/>
+      <c r="V32" s="60"/>
+      <c r="W32" s="60"/>
+      <c r="X32" s="60"/>
+      <c r="Y32" s="60"/>
+      <c r="Z32" s="60"/>
+      <c r="AA32" s="60"/>
+      <c r="AB32" s="60"/>
+      <c r="AC32" s="60"/>
+      <c r="AD32" s="60"/>
+      <c r="AE32" s="60"/>
+      <c r="AF32" s="60"/>
+      <c r="AG32" s="60"/>
+      <c r="AH32" s="60"/>
+      <c r="AI32" s="60"/>
+      <c r="AJ32" s="60"/>
+      <c r="AK32" s="60"/>
+      <c r="AL32" s="60"/>
+      <c r="AM32" s="60"/>
+      <c r="AN32" s="60"/>
+      <c r="AO32" s="60"/>
+      <c r="AP32" s="63"/>
+      <c r="AQ32" s="59"/>
+      <c r="AR32" s="60"/>
+      <c r="AS32" s="60"/>
+      <c r="AT32" s="60"/>
+      <c r="AU32" s="60"/>
+      <c r="AV32" s="60"/>
+      <c r="AW32" s="60"/>
+      <c r="AX32" s="60"/>
+      <c r="AY32" s="60"/>
+      <c r="AZ32" s="60"/>
+      <c r="BA32" s="60"/>
+      <c r="BB32" s="60"/>
+      <c r="BC32" s="60"/>
+      <c r="BD32" s="60"/>
+      <c r="BE32" s="61"/>
     </row>
     <row r="33" spans="1:57" ht="15" customHeight="1">
-      <c r="A33" s="70"/>
-      <c r="B33" s="71"/>
-      <c r="C33" s="71"/>
-      <c r="D33" s="71"/>
-      <c r="E33" s="71"/>
-      <c r="F33" s="71"/>
-      <c r="G33" s="72"/>
-      <c r="H33" s="78"/>
-      <c r="I33" s="79"/>
-      <c r="J33" s="79"/>
-      <c r="K33" s="79"/>
-      <c r="L33" s="79"/>
-      <c r="M33" s="79"/>
-      <c r="N33" s="80"/>
-      <c r="O33" s="78"/>
-      <c r="P33" s="81"/>
-      <c r="Q33" s="81"/>
-      <c r="R33" s="81"/>
-      <c r="S33" s="81"/>
-      <c r="T33" s="81"/>
-      <c r="U33" s="81"/>
-      <c r="V33" s="81"/>
-      <c r="W33" s="81"/>
-      <c r="X33" s="81"/>
-      <c r="Y33" s="81"/>
-      <c r="Z33" s="81"/>
-      <c r="AA33" s="81"/>
-      <c r="AB33" s="81"/>
-      <c r="AC33" s="81"/>
-      <c r="AD33" s="81"/>
-      <c r="AE33" s="81"/>
-      <c r="AF33" s="81"/>
-      <c r="AG33" s="81"/>
-      <c r="AH33" s="81"/>
-      <c r="AI33" s="81"/>
-      <c r="AJ33" s="81"/>
-      <c r="AK33" s="81"/>
-      <c r="AL33" s="81"/>
-      <c r="AM33" s="81"/>
-      <c r="AN33" s="81"/>
-      <c r="AO33" s="81"/>
-      <c r="AP33" s="82"/>
-      <c r="AQ33" s="86"/>
-      <c r="AR33" s="81"/>
-      <c r="AS33" s="81"/>
-      <c r="AT33" s="81"/>
-      <c r="AU33" s="81"/>
-      <c r="AV33" s="81"/>
-      <c r="AW33" s="81"/>
-      <c r="AX33" s="81"/>
-      <c r="AY33" s="81"/>
-      <c r="AZ33" s="81"/>
-      <c r="BA33" s="81"/>
-      <c r="BB33" s="81"/>
-      <c r="BC33" s="81"/>
-      <c r="BD33" s="81"/>
-      <c r="BE33" s="87"/>
+      <c r="A33" s="88"/>
+      <c r="B33" s="89"/>
+      <c r="C33" s="89"/>
+      <c r="D33" s="89"/>
+      <c r="E33" s="89"/>
+      <c r="F33" s="89"/>
+      <c r="G33" s="90"/>
+      <c r="H33" s="62"/>
+      <c r="I33" s="64"/>
+      <c r="J33" s="64"/>
+      <c r="K33" s="64"/>
+      <c r="L33" s="64"/>
+      <c r="M33" s="64"/>
+      <c r="N33" s="65"/>
+      <c r="O33" s="62"/>
+      <c r="P33" s="60"/>
+      <c r="Q33" s="60"/>
+      <c r="R33" s="60"/>
+      <c r="S33" s="60"/>
+      <c r="T33" s="60"/>
+      <c r="U33" s="60"/>
+      <c r="V33" s="60"/>
+      <c r="W33" s="60"/>
+      <c r="X33" s="60"/>
+      <c r="Y33" s="60"/>
+      <c r="Z33" s="60"/>
+      <c r="AA33" s="60"/>
+      <c r="AB33" s="60"/>
+      <c r="AC33" s="60"/>
+      <c r="AD33" s="60"/>
+      <c r="AE33" s="60"/>
+      <c r="AF33" s="60"/>
+      <c r="AG33" s="60"/>
+      <c r="AH33" s="60"/>
+      <c r="AI33" s="60"/>
+      <c r="AJ33" s="60"/>
+      <c r="AK33" s="60"/>
+      <c r="AL33" s="60"/>
+      <c r="AM33" s="60"/>
+      <c r="AN33" s="60"/>
+      <c r="AO33" s="60"/>
+      <c r="AP33" s="63"/>
+      <c r="AQ33" s="59"/>
+      <c r="AR33" s="60"/>
+      <c r="AS33" s="60"/>
+      <c r="AT33" s="60"/>
+      <c r="AU33" s="60"/>
+      <c r="AV33" s="60"/>
+      <c r="AW33" s="60"/>
+      <c r="AX33" s="60"/>
+      <c r="AY33" s="60"/>
+      <c r="AZ33" s="60"/>
+      <c r="BA33" s="60"/>
+      <c r="BB33" s="60"/>
+      <c r="BC33" s="60"/>
+      <c r="BD33" s="60"/>
+      <c r="BE33" s="61"/>
     </row>
     <row r="34" spans="1:57" ht="15" customHeight="1">
-      <c r="A34" s="70"/>
-      <c r="B34" s="71"/>
-      <c r="C34" s="71"/>
-      <c r="D34" s="71"/>
-      <c r="E34" s="71"/>
-      <c r="F34" s="71"/>
-      <c r="G34" s="72"/>
-      <c r="H34" s="78"/>
-      <c r="I34" s="79"/>
-      <c r="J34" s="79"/>
-      <c r="K34" s="79"/>
-      <c r="L34" s="79"/>
-      <c r="M34" s="79"/>
-      <c r="N34" s="80"/>
-      <c r="O34" s="78"/>
-      <c r="P34" s="81"/>
-      <c r="Q34" s="81"/>
-      <c r="R34" s="81"/>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="81"/>
-      <c r="V34" s="81"/>
-      <c r="W34" s="81"/>
-      <c r="X34" s="81"/>
-      <c r="Y34" s="81"/>
-      <c r="Z34" s="81"/>
-      <c r="AA34" s="81"/>
-      <c r="AB34" s="81"/>
-      <c r="AC34" s="81"/>
-      <c r="AD34" s="81"/>
-      <c r="AE34" s="81"/>
-      <c r="AF34" s="81"/>
-      <c r="AG34" s="81"/>
-      <c r="AH34" s="81"/>
-      <c r="AI34" s="81"/>
-      <c r="AJ34" s="81"/>
-      <c r="AK34" s="81"/>
-      <c r="AL34" s="81"/>
-      <c r="AM34" s="81"/>
-      <c r="AN34" s="81"/>
-      <c r="AO34" s="81"/>
-      <c r="AP34" s="82"/>
-      <c r="AQ34" s="86"/>
-      <c r="AR34" s="81"/>
-      <c r="AS34" s="81"/>
-      <c r="AT34" s="81"/>
-      <c r="AU34" s="81"/>
-      <c r="AV34" s="81"/>
-      <c r="AW34" s="81"/>
-      <c r="AX34" s="81"/>
-      <c r="AY34" s="81"/>
-      <c r="AZ34" s="81"/>
-      <c r="BA34" s="81"/>
-      <c r="BB34" s="81"/>
-      <c r="BC34" s="81"/>
-      <c r="BD34" s="81"/>
-      <c r="BE34" s="87"/>
+      <c r="A34" s="88"/>
+      <c r="B34" s="89"/>
+      <c r="C34" s="89"/>
+      <c r="D34" s="89"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="89"/>
+      <c r="G34" s="90"/>
+      <c r="H34" s="62"/>
+      <c r="I34" s="64"/>
+      <c r="J34" s="64"/>
+      <c r="K34" s="64"/>
+      <c r="L34" s="64"/>
+      <c r="M34" s="64"/>
+      <c r="N34" s="65"/>
+      <c r="O34" s="62"/>
+      <c r="P34" s="60"/>
+      <c r="Q34" s="60"/>
+      <c r="R34" s="60"/>
+      <c r="S34" s="60"/>
+      <c r="T34" s="60"/>
+      <c r="U34" s="60"/>
+      <c r="V34" s="60"/>
+      <c r="W34" s="60"/>
+      <c r="X34" s="60"/>
+      <c r="Y34" s="60"/>
+      <c r="Z34" s="60"/>
+      <c r="AA34" s="60"/>
+      <c r="AB34" s="60"/>
+      <c r="AC34" s="60"/>
+      <c r="AD34" s="60"/>
+      <c r="AE34" s="60"/>
+      <c r="AF34" s="60"/>
+      <c r="AG34" s="60"/>
+      <c r="AH34" s="60"/>
+      <c r="AI34" s="60"/>
+      <c r="AJ34" s="60"/>
+      <c r="AK34" s="60"/>
+      <c r="AL34" s="60"/>
+      <c r="AM34" s="60"/>
+      <c r="AN34" s="60"/>
+      <c r="AO34" s="60"/>
+      <c r="AP34" s="63"/>
+      <c r="AQ34" s="59"/>
+      <c r="AR34" s="60"/>
+      <c r="AS34" s="60"/>
+      <c r="AT34" s="60"/>
+      <c r="AU34" s="60"/>
+      <c r="AV34" s="60"/>
+      <c r="AW34" s="60"/>
+      <c r="AX34" s="60"/>
+      <c r="AY34" s="60"/>
+      <c r="AZ34" s="60"/>
+      <c r="BA34" s="60"/>
+      <c r="BB34" s="60"/>
+      <c r="BC34" s="60"/>
+      <c r="BD34" s="60"/>
+      <c r="BE34" s="61"/>
     </row>
     <row r="35" spans="1:57" ht="15" customHeight="1" thickBot="1">
-      <c r="A35" s="83"/>
-      <c r="B35" s="84"/>
-      <c r="C35" s="84"/>
-      <c r="D35" s="84"/>
-      <c r="E35" s="84"/>
-      <c r="F35" s="84"/>
-      <c r="G35" s="85"/>
-      <c r="H35" s="73"/>
-      <c r="I35" s="74"/>
-      <c r="J35" s="74"/>
-      <c r="K35" s="74"/>
-      <c r="L35" s="74"/>
-      <c r="M35" s="74"/>
-      <c r="N35" s="75"/>
-      <c r="O35" s="73"/>
-      <c r="P35" s="76"/>
-      <c r="Q35" s="76"/>
-      <c r="R35" s="76"/>
-      <c r="S35" s="76"/>
-      <c r="T35" s="76"/>
-      <c r="U35" s="76"/>
-      <c r="V35" s="76"/>
-      <c r="W35" s="76"/>
-      <c r="X35" s="76"/>
-      <c r="Y35" s="76"/>
-      <c r="Z35" s="76"/>
-      <c r="AA35" s="76"/>
-      <c r="AB35" s="76"/>
-      <c r="AC35" s="76"/>
-      <c r="AD35" s="76"/>
-      <c r="AE35" s="76"/>
-      <c r="AF35" s="76"/>
-      <c r="AG35" s="76"/>
-      <c r="AH35" s="76"/>
-      <c r="AI35" s="76"/>
-      <c r="AJ35" s="76"/>
-      <c r="AK35" s="76"/>
-      <c r="AL35" s="76"/>
-      <c r="AM35" s="76"/>
-      <c r="AN35" s="76"/>
-      <c r="AO35" s="76"/>
-      <c r="AP35" s="77"/>
-      <c r="AQ35" s="88"/>
-      <c r="AR35" s="76"/>
-      <c r="AS35" s="76"/>
-      <c r="AT35" s="76"/>
-      <c r="AU35" s="76"/>
-      <c r="AV35" s="76"/>
-      <c r="AW35" s="76"/>
-      <c r="AX35" s="76"/>
-      <c r="AY35" s="76"/>
-      <c r="AZ35" s="76"/>
-      <c r="BA35" s="76"/>
-      <c r="BB35" s="76"/>
-      <c r="BC35" s="76"/>
-      <c r="BD35" s="76"/>
-      <c r="BE35" s="89"/>
+      <c r="A35" s="95"/>
+      <c r="B35" s="96"/>
+      <c r="C35" s="96"/>
+      <c r="D35" s="96"/>
+      <c r="E35" s="96"/>
+      <c r="F35" s="96"/>
+      <c r="G35" s="97"/>
+      <c r="H35" s="91"/>
+      <c r="I35" s="92"/>
+      <c r="J35" s="92"/>
+      <c r="K35" s="92"/>
+      <c r="L35" s="92"/>
+      <c r="M35" s="92"/>
+      <c r="N35" s="93"/>
+      <c r="O35" s="91"/>
+      <c r="P35" s="83"/>
+      <c r="Q35" s="83"/>
+      <c r="R35" s="83"/>
+      <c r="S35" s="83"/>
+      <c r="T35" s="83"/>
+      <c r="U35" s="83"/>
+      <c r="V35" s="83"/>
+      <c r="W35" s="83"/>
+      <c r="X35" s="83"/>
+      <c r="Y35" s="83"/>
+      <c r="Z35" s="83"/>
+      <c r="AA35" s="83"/>
+      <c r="AB35" s="83"/>
+      <c r="AC35" s="83"/>
+      <c r="AD35" s="83"/>
+      <c r="AE35" s="83"/>
+      <c r="AF35" s="83"/>
+      <c r="AG35" s="83"/>
+      <c r="AH35" s="83"/>
+      <c r="AI35" s="83"/>
+      <c r="AJ35" s="83"/>
+      <c r="AK35" s="83"/>
+      <c r="AL35" s="83"/>
+      <c r="AM35" s="83"/>
+      <c r="AN35" s="83"/>
+      <c r="AO35" s="83"/>
+      <c r="AP35" s="94"/>
+      <c r="AQ35" s="82"/>
+      <c r="AR35" s="83"/>
+      <c r="AS35" s="83"/>
+      <c r="AT35" s="83"/>
+      <c r="AU35" s="83"/>
+      <c r="AV35" s="83"/>
+      <c r="AW35" s="83"/>
+      <c r="AX35" s="83"/>
+      <c r="AY35" s="83"/>
+      <c r="AZ35" s="83"/>
+      <c r="BA35" s="83"/>
+      <c r="BB35" s="83"/>
+      <c r="BC35" s="83"/>
+      <c r="BD35" s="83"/>
+      <c r="BE35" s="84"/>
     </row>
   </sheetData>
   <mergeCells count="133">
-    <mergeCell ref="AQ28:BE28"/>
-    <mergeCell ref="O29:AP29"/>
-    <mergeCell ref="AQ29:BE29"/>
-    <mergeCell ref="H25:N25"/>
-    <mergeCell ref="O25:AP25"/>
-    <mergeCell ref="AQ25:BE25"/>
-    <mergeCell ref="H27:N27"/>
-    <mergeCell ref="O27:AP27"/>
-    <mergeCell ref="O26:AP26"/>
-    <mergeCell ref="AQ26:BE26"/>
-    <mergeCell ref="AQ27:BE27"/>
-    <mergeCell ref="H29:N29"/>
-    <mergeCell ref="H28:N28"/>
-    <mergeCell ref="AQ13:BE13"/>
-    <mergeCell ref="H14:N14"/>
-    <mergeCell ref="O14:AP14"/>
-    <mergeCell ref="AQ14:BE14"/>
-    <mergeCell ref="H21:N21"/>
-    <mergeCell ref="O21:AP21"/>
-    <mergeCell ref="AQ21:BE21"/>
-    <mergeCell ref="H22:N22"/>
-    <mergeCell ref="O22:AP22"/>
-    <mergeCell ref="AQ22:BE22"/>
-    <mergeCell ref="AQ18:BE18"/>
-    <mergeCell ref="AQ16:BE16"/>
+    <mergeCell ref="A1:BE1"/>
+    <mergeCell ref="H3:N3"/>
+    <mergeCell ref="O3:AP3"/>
+    <mergeCell ref="AQ3:BE3"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="H35:N35"/>
+    <mergeCell ref="O35:AP35"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="H13:N13"/>
+    <mergeCell ref="O13:AP13"/>
+    <mergeCell ref="O28:AP28"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="AQ34:BE34"/>
+    <mergeCell ref="H33:N33"/>
+    <mergeCell ref="H34:N34"/>
+    <mergeCell ref="O34:AP34"/>
+    <mergeCell ref="AQ35:BE35"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="H32:N32"/>
+    <mergeCell ref="O32:AP32"/>
+    <mergeCell ref="AQ32:BE32"/>
+    <mergeCell ref="H31:N31"/>
+    <mergeCell ref="O33:AP33"/>
+    <mergeCell ref="AQ33:BE33"/>
+    <mergeCell ref="H24:N24"/>
+    <mergeCell ref="O24:AP24"/>
+    <mergeCell ref="AQ24:BE24"/>
+    <mergeCell ref="H23:N23"/>
+    <mergeCell ref="O31:AP31"/>
+    <mergeCell ref="AQ31:BE31"/>
+    <mergeCell ref="H30:N30"/>
+    <mergeCell ref="O30:AP30"/>
+    <mergeCell ref="H8:N8"/>
+    <mergeCell ref="O8:AP8"/>
+    <mergeCell ref="H10:N10"/>
+    <mergeCell ref="O10:AP10"/>
+    <mergeCell ref="AQ30:BE30"/>
+    <mergeCell ref="H26:N26"/>
+    <mergeCell ref="O15:AP15"/>
+    <mergeCell ref="AQ15:BE15"/>
+    <mergeCell ref="H16:N16"/>
+    <mergeCell ref="O16:AP16"/>
+    <mergeCell ref="O23:AP23"/>
+    <mergeCell ref="AQ23:BE23"/>
+    <mergeCell ref="H20:N20"/>
+    <mergeCell ref="O20:AP20"/>
+    <mergeCell ref="AQ20:BE20"/>
+    <mergeCell ref="H19:N19"/>
+    <mergeCell ref="H15:N15"/>
+    <mergeCell ref="O19:AP19"/>
+    <mergeCell ref="AQ19:BE19"/>
+    <mergeCell ref="H17:N17"/>
+    <mergeCell ref="O17:AP17"/>
+    <mergeCell ref="AQ17:BE17"/>
+    <mergeCell ref="H18:N18"/>
+    <mergeCell ref="O18:AP18"/>
     <mergeCell ref="H4:N4"/>
     <mergeCell ref="O4:AP4"/>
     <mergeCell ref="AQ4:BE4"/>
@@ -7022,90 +7079,31 @@
     <mergeCell ref="AQ9:BE9"/>
     <mergeCell ref="O7:AP7"/>
     <mergeCell ref="AQ7:BE7"/>
-    <mergeCell ref="H8:N8"/>
-    <mergeCell ref="O8:AP8"/>
-    <mergeCell ref="H10:N10"/>
-    <mergeCell ref="O10:AP10"/>
-    <mergeCell ref="AQ30:BE30"/>
-    <mergeCell ref="H26:N26"/>
-    <mergeCell ref="O15:AP15"/>
-    <mergeCell ref="AQ15:BE15"/>
-    <mergeCell ref="H16:N16"/>
-    <mergeCell ref="O16:AP16"/>
-    <mergeCell ref="O23:AP23"/>
-    <mergeCell ref="AQ23:BE23"/>
-    <mergeCell ref="H20:N20"/>
-    <mergeCell ref="O20:AP20"/>
-    <mergeCell ref="AQ20:BE20"/>
-    <mergeCell ref="H19:N19"/>
-    <mergeCell ref="H15:N15"/>
-    <mergeCell ref="O19:AP19"/>
-    <mergeCell ref="AQ19:BE19"/>
-    <mergeCell ref="H17:N17"/>
-    <mergeCell ref="O17:AP17"/>
-    <mergeCell ref="AQ17:BE17"/>
-    <mergeCell ref="H18:N18"/>
-    <mergeCell ref="O18:AP18"/>
-    <mergeCell ref="AQ34:BE34"/>
-    <mergeCell ref="H33:N33"/>
-    <mergeCell ref="H34:N34"/>
-    <mergeCell ref="O34:AP34"/>
-    <mergeCell ref="AQ35:BE35"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="H32:N32"/>
-    <mergeCell ref="O32:AP32"/>
-    <mergeCell ref="AQ32:BE32"/>
-    <mergeCell ref="H31:N31"/>
-    <mergeCell ref="O33:AP33"/>
-    <mergeCell ref="AQ33:BE33"/>
-    <mergeCell ref="H24:N24"/>
-    <mergeCell ref="O24:AP24"/>
-    <mergeCell ref="AQ24:BE24"/>
-    <mergeCell ref="H23:N23"/>
-    <mergeCell ref="O31:AP31"/>
-    <mergeCell ref="AQ31:BE31"/>
-    <mergeCell ref="H30:N30"/>
-    <mergeCell ref="O30:AP30"/>
-    <mergeCell ref="H35:N35"/>
-    <mergeCell ref="O35:AP35"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="H13:N13"/>
-    <mergeCell ref="O13:AP13"/>
-    <mergeCell ref="O28:AP28"/>
-    <mergeCell ref="A35:G35"/>
-    <mergeCell ref="A1:BE1"/>
-    <mergeCell ref="H3:N3"/>
-    <mergeCell ref="O3:AP3"/>
-    <mergeCell ref="AQ3:BE3"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="A33:G33"/>
-    <mergeCell ref="A34:G34"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A28:G28"/>
-    <mergeCell ref="A29:G29"/>
-    <mergeCell ref="A30:G30"/>
-    <mergeCell ref="A23:G23"/>
-    <mergeCell ref="A24:G24"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="A20:G20"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A22:G22"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="AQ13:BE13"/>
+    <mergeCell ref="H14:N14"/>
+    <mergeCell ref="O14:AP14"/>
+    <mergeCell ref="AQ14:BE14"/>
+    <mergeCell ref="H21:N21"/>
+    <mergeCell ref="O21:AP21"/>
+    <mergeCell ref="AQ21:BE21"/>
+    <mergeCell ref="H22:N22"/>
+    <mergeCell ref="O22:AP22"/>
+    <mergeCell ref="AQ22:BE22"/>
+    <mergeCell ref="AQ18:BE18"/>
+    <mergeCell ref="AQ16:BE16"/>
+    <mergeCell ref="AQ28:BE28"/>
+    <mergeCell ref="O29:AP29"/>
+    <mergeCell ref="AQ29:BE29"/>
+    <mergeCell ref="H25:N25"/>
+    <mergeCell ref="O25:AP25"/>
+    <mergeCell ref="AQ25:BE25"/>
+    <mergeCell ref="H27:N27"/>
+    <mergeCell ref="O27:AP27"/>
+    <mergeCell ref="O26:AP26"/>
+    <mergeCell ref="AQ26:BE26"/>
+    <mergeCell ref="AQ27:BE27"/>
+    <mergeCell ref="H29:N29"/>
+    <mergeCell ref="H28:N28"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
